--- a/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
+++ b/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
@@ -2205,14 +2205,10 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>https://www.env.go.jp/garden/kokyogaien/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for this gate of the Imperial Palace; no account for it exists - the palace grounds are run by the Imperial Household Agency and the results were unrelated Kasumigaseki businesses.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -2263,14 +2259,10 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.kunaicho.go.jp/event/higashigyoen/higashigyoen.html</t>
-        </is>
-      </c>
+          <t>Searched Instagram for this gate of the Imperial Palace; no account for it exists, and the only name match was an unrelated takeaway service in Fukuoka's Otemon district.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -2321,7 +2313,7 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for this avenue in Marunouchi; it is a public street with no account of its own and the results were nearby restaurants.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2375,7 +2367,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the station plaza; it is a public space with no account of its own and the results were shops inside and around the station.</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
@@ -21552,17 +21544,21 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
-      <c r="M321" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M321" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N321" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O321" t="inlineStr"/>
+          <t>An account named Restaurant Glover-tei exists, but its profile gives no address and nothing in it places the shop in Mitaka; a second account of the same name is a Nagasaki champon shop in Niigata, so neither could be established as this shop's.</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gurabar111/</t>
+        </is>
+      </c>
       <c r="P321" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -21617,7 +21613,7 @@
       </c>
       <c r="N322" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Koiwa.</t>
         </is>
       </c>
       <c r="O322" t="inlineStr"/>
@@ -21668,17 +21664,21 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
-      <c r="M323" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M323" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O323" t="inlineStr"/>
+          <t>An account named Chuka Juhachiban exists and matches the name and category, but its profile gives only opening hours and no location, so it could not be tied to the Nogata shop; the other name matches are in Chuo-ku, Osaka and Wakayama.</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chuukayasan_18/</t>
+        </is>
+      </c>
       <c r="P323" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -21733,7 +21733,7 @@
       </c>
       <c r="N324" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Uguisudani.</t>
         </is>
       </c>
       <c r="O324" t="inlineStr"/>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="N325" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Kichijoji - the name matches were other Chinrai branches in Ariake, Hirai, Rokucho and Minami-Gyotoku.</t>
         </is>
       </c>
       <c r="O325" t="inlineStr"/>
@@ -21838,21 +21838,41 @@
           <t>https://www.google.com/maps/place/%E7%B4%AB%E9%87%91%E9%A3%AF%E5%BA%97%20%E5%8E%9F%E5%AE%BF%E5%BA%97/data=!4m2!3m1!1s0x60188cbc6805e4db:0x3fb4682a3063ac6d</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
-      <c r="J326" t="inlineStr"/>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shikinharajuku/</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>shikinharajuku</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M326" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N326" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O326" t="inlineStr"/>
+          <t>The account's own profile names the shop as the Harajuku main shop, gives its founding year of 1966 and states its delivery area as parts of Jingumae and Sendagaya, the neighbourhoods around Kita-Sando where this listing places it.</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shikinharajuku/</t>
+        </is>
+      </c>
       <c r="P326" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -21961,7 +21981,7 @@
       </c>
       <c r="N328" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Shibakoen - the nearest name match, Munch A Burger, is a different name with no stated location.</t>
         </is>
       </c>
       <c r="O328" t="inlineStr"/>
@@ -22015,7 +22035,7 @@
       </c>
       <c r="N329" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Jimbocho - the name matches are burger shops in Semarang, Indonesia and Barcelona.</t>
         </is>
       </c>
       <c r="O329" t="inlineStr"/>
@@ -22178,14 +22198,14 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr"/>
-      <c r="M332" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M332" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>The chain keeps separate branch accounts (Hokkaido, Okinawa and Miyakojima among them) but no account for the Shinjuku branch was found, and the brand-level account's profile gives no location, so none could be tied to this branch.</t>
         </is>
       </c>
       <c r="O332" t="inlineStr"/>
@@ -22239,7 +22259,7 @@
       </c>
       <c r="N333" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for it - the only related result is a steak restaurant opened by a chef who trained here.</t>
         </is>
       </c>
       <c r="O333" t="inlineStr"/>
@@ -22356,21 +22376,41 @@
           <t>https://www.google.com/maps/place/Peter%20Luger%20Tokyo/data=!4m2!3m1!1s0x60188bd28536402d:0x45eca5f988b97909</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/peterluger_steakhouse_tokyo/</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>peterluger_steakhouse_tokyo</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M335" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N335" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O335" t="inlineStr"/>
+          <t>The account's own profile names this restaurant as the Tokyo branch of the New York steakhouse and gives its lunch and dinner hours; the brand's main account lists Tokyo among its locations and this is its only Japanese restaurant, though the profile does not print the Ebisu address itself.</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/peterluger_steakhouse_tokyo/</t>
+        </is>
+      </c>
       <c r="P335" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -22488,21 +22528,17 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
-      <c r="M337" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M337" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N337" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O337" s="2" t="inlineStr">
-        <is>
-          <t>https://www.bifteck.co.jp/restaurant/ginza/</t>
-        </is>
-      </c>
+          <t>Several accounts of this steakhouse exist and two of them name the Ginza and Roppongi branches together in one profile; no account specific to the Ginza branch was found, so none is recorded.</t>
+        </is>
+      </c>
+      <c r="O337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -22542,23 +22578,39 @@
           <t>https://www.google.com/maps/place/Benjamin%20%E5%85%AD%E6%9C%AC%E6%9C%A8/data=!4m2!3m1!1s0x60188b7812bdc8a3:0x1397f620b04764f2</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
-      <c r="J338" t="inlineStr"/>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/benjaminsteakhouse_roppongi/</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>benjaminsteakhouse_roppongi</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M338" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N338" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The account's own profile names this restaurant as the Roppongi branch and the Japanese flagship of the Manhattan steakhouse, and the chain keeps separate accounts for its Kioicho, Kyoto and Osaka branches.</t>
         </is>
       </c>
       <c r="O338" s="2" t="inlineStr">
         <is>
-          <t>https://benjaminsteakhouse.jp/</t>
+          <t>https://www.instagram.com/benjaminsteakhouse_roppongi/</t>
         </is>
       </c>
       <c r="P338" t="inlineStr">
@@ -22600,21 +22652,41 @@
           <t>https://www.google.com/maps/place/Morton%27s%20%E4%B8%B8%E3%81%AE%E5%86%85/data=!4m2!3m1!1s0x60188b4577605a27:0x6313d8af21dbdac</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
-      <c r="J339" t="inlineStr"/>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mortonsthesteakhousejpn/</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>mortonsthesteakhousejpn</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M339" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N339" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O339" t="inlineStr"/>
+          <t>The account's own profile places the restaurant on the second floor of Nijubashi Square in Marunouchi, two minutes from exit B4 of Hibiya station, and names it the brand's first restaurant in Japan.</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mortonsthesteakhousejpn/</t>
+        </is>
+      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -22654,23 +22726,39 @@
           <t>https://www.google.com/maps/place/%E3%83%AB%E3%83%BC%E3%82%B9%E3%83%BB%E3%82%AF%E3%83%AA%E3%82%B9/data=!4m2!3m1!1s0x60188b8e6fe82499:0xb7a44d6615614ae9</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
-      <c r="J340" t="inlineStr"/>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ruthschrisjp/</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>ruthschrisjp</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M340" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N340" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The brand's own Japanese account; its profile names the New Orleans origin of 1965 and lists Tokyo and Osaka as its locations, and no account specific to the Toranomon restaurant exists, so this is recorded as the operator's account.</t>
         </is>
       </c>
       <c r="O340" s="2" t="inlineStr">
         <is>
-          <t>https://ruthschris.co.jp/</t>
+          <t>https://www.instagram.com/ruthschrisjp/</t>
         </is>
       </c>
       <c r="P340" t="inlineStr">
@@ -22797,7 +22885,7 @@
       </c>
       <c r="N342" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name in Akasaka or Akasaka-Mitsuke.</t>
         </is>
       </c>
       <c r="O342" t="inlineStr"/>
@@ -22851,7 +22939,7 @@
       </c>
       <c r="N343" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for it in Hongo - the only related result is a Yokohama restaurant supervised by this brand.</t>
         </is>
       </c>
       <c r="O343" t="inlineStr"/>
@@ -22898,17 +22986,21 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
-      <c r="M344" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M344" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O344" t="inlineStr"/>
+          <t>An account carrying this restaurant's name and its proprietor's name exists and its profile gives opening hours and the Tuesday-Wednesday closing, but no address or area, so it could not be tied to the Shikahama shop.</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sutaminaen/</t>
+        </is>
+      </c>
       <c r="P344" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -22952,17 +23044,21 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
-      <c r="M345" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M345" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N345" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O345" t="inlineStr"/>
+          <t>The brand's account exists but its profile places the restaurant at Azabudai Hills, not Ebisu where this listing places it, so it was not recorded; the sibling accounts are the Kanda and Taipei restaurants.</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vanne_yoroniku/</t>
+        </is>
+      </c>
       <c r="P345" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23129,7 +23225,7 @@
       </c>
       <c r="N348" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bakery with its area; no account of its own was found - only its sister bistro in Kagurazaka, which names this bakery as its parent.</t>
         </is>
       </c>
       <c r="O348" t="inlineStr"/>
@@ -23230,21 +23326,41 @@
           <t>https://www.google.com/maps/place/Think/data=!4m2!3m1!1s0x60188db1887a4c61:0x26726daaaba4fcbc</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr"/>
-      <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
-      <c r="M350" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/think_tokyo/</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>think_tokyo</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M350" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N350" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O350" t="inlineStr"/>
+          <t>The account's own profile gives the shop's address as Ueno-Sakuragi Atari building 2, ground floor, Taito-ku, with its hours and Monday-Tuesday closing, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/think_tokyo/</t>
+        </is>
+      </c>
       <c r="P350" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23342,21 +23458,41 @@
           <t>https://www.google.com/maps/place/%E3%83%91%E3%83%BC%E3%83%A9%E3%83%BC%E6%B1%9F%E5%8F%A4%E7%94%B0/data=!4m2!3m1!1s0x6018ed3ffbe98d4f:0x93fed3f17ed186eb</t>
         </is>
       </c>
-      <c r="I352" t="inlineStr"/>
-      <c r="J352" t="inlineStr"/>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/parlour_ekoda/</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>parlour_ekoda</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M352" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N352" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr"/>
+          <t>The account's own profile names the shop, gives its hours and Tuesday closing and names its sister shop Machino Parlour at Kotake-cho 2-40-4 in Nerima-ku, the neighbourhood adjoining Shin-Sakuradai where this listing places it; the profile does not print this shop's own address.</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/parlour_ekoda/</t>
+        </is>
+      </c>
       <c r="P352" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23407,7 +23543,7 @@
       </c>
       <c r="N353" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bakery with its area and category; no account found for this name in Takanawadai.</t>
         </is>
       </c>
       <c r="O353" t="inlineStr"/>
@@ -23461,7 +23597,7 @@
       </c>
       <c r="N354" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bakery with its area; no account found for this name in Kichijoji.</t>
         </is>
       </c>
       <c r="O354" t="inlineStr"/>
@@ -23504,21 +23640,41 @@
           <t>https://www.google.com/maps/place/%E4%B8%8B%E7%94%B0%E6%B5%81/data=!4m2!3m1!1s0x6018eb4b503932fb:0x35961ed50a323f72</t>
         </is>
       </c>
-      <c r="I355" t="inlineStr"/>
-      <c r="J355" t="inlineStr"/>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
-      <c r="M355" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shimodaryu/</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>shimodaryu</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M355" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N355" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O355" t="inlineStr"/>
+          <t>The account's own profile gives the bakery's address as Takashimadaira 7-26-4, Itabashi-ku, seven minutes from Takashimadaira station, the neighbourhood this listing places it in, together with its opening days and hours.</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shimodaryu/</t>
+        </is>
+      </c>
       <c r="P355" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23636,17 +23792,21 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
-      <c r="M357" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M357" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O357" t="inlineStr"/>
+          <t>The bakery's brand account exists and gives its hours, but neither it nor the sibling coffee account states any location, so the account could not be placed in Roppongi.</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bricolage_bread_and_company/</t>
+        </is>
+      </c>
       <c r="P357" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23690,21 +23850,41 @@
           <t>https://www.google.com/maps/place/KHAO/data=!4m2!3m1!1s0x60188dbf39c20935:0xc7a1a929260b1d88</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
-      <c r="J358" t="inlineStr"/>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
-      <c r="M358" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/khao.tokyo/</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>khao.tokyo</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M358" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N358" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O358" t="inlineStr"/>
+          <t>The account's own profile places the restaurant one minute from exit A4 of Jimbocho station, names it a Thai restaurant with an eight-seat counter and describes its monthly booking opening, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/khao.tokyo/</t>
+        </is>
+      </c>
       <c r="P358" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -23810,21 +23990,41 @@
           <t>https://www.google.com/maps/place/%E3%82%BF%E3%82%A4%E6%96%99%E7%90%86%20%E3%81%BF%E3%82%82%E3%81%A3%E3%81%A8/data=!4m2!3m1!1s0x6018f4debfc0fc37:0x4916a136c0dea89f</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
-      <c r="J360" t="inlineStr"/>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
-      <c r="M360" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mymot_thai/</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>mymot_thai</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M360" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N360" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O360" t="inlineStr"/>
+          <t>The account's own profile describes the shop's reservation-only monthly omakase menu of Thai regional cooking, and its sister daytime account names it as the Thai restaurant Mymot in Meguro, where this listing places it.</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mymot_thai/</t>
+        </is>
+      </c>
       <c r="P360" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -24081,7 +24281,7 @@
       </c>
       <c r="N364" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area; no account found for it in Kiba - the name matches are a ramen shop in Obu, Aichi and an izakaya in Kumagaya.</t>
         </is>
       </c>
       <c r="O364" t="inlineStr"/>
@@ -24139,7 +24339,7 @@
       </c>
       <c r="N365" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop and its Akihabara main branch; no account of its own was found, only a ramen writer's page listing the shop among his recommendations.</t>
         </is>
       </c>
       <c r="O365" t="inlineStr"/>
@@ -24259,7 +24459,7 @@
       </c>
       <c r="N367" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for it - the related shop Chuka Soba Katsumoto's account names only its Suidobashi main branch and no Kanda or Jimbocho branch.</t>
         </is>
       </c>
       <c r="O367" t="inlineStr"/>
@@ -24317,7 +24517,7 @@
       </c>
       <c r="N368" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Chitose-Funabashi.</t>
         </is>
       </c>
       <c r="O368" t="inlineStr"/>
@@ -24375,7 +24575,7 @@
       </c>
       <c r="N369" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Ochiai.</t>
         </is>
       </c>
       <c r="O369" t="inlineStr"/>
@@ -24488,17 +24688,21 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr"/>
-      <c r="M371" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M371" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N371" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O371" t="inlineStr"/>
+          <t>An account with this shop's exact and distinctive name exists and its profile gives the opening days and hours, but it states no address or area, so it could not be placed in Higashi-Ogu.</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ra_men_1.20/</t>
+        </is>
+      </c>
       <c r="P371" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -24553,7 +24757,7 @@
       </c>
       <c r="N372" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Bubaigawara.</t>
         </is>
       </c>
       <c r="O372" t="inlineStr"/>
@@ -24611,7 +24815,7 @@
       </c>
       <c r="N373" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Sakurajosui - the results were two other ramen shops by that station.</t>
         </is>
       </c>
       <c r="O373" t="inlineStr"/>
@@ -24669,7 +24873,7 @@
       </c>
       <c r="N374" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Nakano-Fujimicho - the name matches are in Nagano, Kobe, Nagasaki and Osaka.</t>
         </is>
       </c>
       <c r="O374" t="inlineStr"/>
@@ -24720,17 +24924,21 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
-      <c r="M375" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M375" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N375" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O375" t="inlineStr"/>
+          <t>An account with this shop's exact name exists and its profile describes its own noodles and use of no chemical seasonings, but it states no address or area, so it could not be placed in Kameido.</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/men_fujisaki/</t>
+        </is>
+      </c>
       <c r="P375" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -24785,7 +24993,7 @@
       </c>
       <c r="N376" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Jujo.</t>
         </is>
       </c>
       <c r="O376" t="inlineStr"/>
@@ -24843,7 +25051,7 @@
       </c>
       <c r="N377" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Higashi-Nakano - the name match is a century-old eel restaurant at Yunotsuru onsen.</t>
         </is>
       </c>
       <c r="O377" t="inlineStr"/>
@@ -24901,7 +25109,7 @@
       </c>
       <c r="N378" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for it in Honmoku - the name match is a ramen shop in Ube, Yamaguchi.</t>
         </is>
       </c>
       <c r="O378" t="inlineStr"/>
@@ -25075,7 +25283,7 @@
       </c>
       <c r="N381" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for this neighbourhood of Sakyo-ku; it is a residential district with no account of its own and the results were local businesses.</t>
         </is>
       </c>
       <c r="O381" t="inlineStr"/>
@@ -25211,14 +25419,10 @@
       </c>
       <c r="N383" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O383" s="2" t="inlineStr">
-        <is>
-          <t>https://www.shokoku-ji.jp/ginkakuji/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the temple under both its names; it keeps no account of its own and the results were shops along its approach.</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -25585,7 +25789,7 @@
       </c>
       <c r="N388" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the temple with its ward; it keeps no account of its own - the only mention is an artist's post about an exhibition held there.</t>
         </is>
       </c>
       <c r="O388" t="inlineStr"/>
@@ -25632,23 +25836,39 @@
           <t>https://www.google.com/maps/place/%E9%BE%8D%E5%AE%89%E5%AF%BA/data=!4m2!3m1!1s0x6001a82a301cbaa7:0xe1ab173e46d78542</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
-      <c r="J389" t="inlineStr"/>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
-      <c r="M389" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ryoanji_/</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>ryoanji_</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M389" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N389" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site could not be read, so no link could be confirmed (https://www.ryoanji.jp/ -&gt; ConnectError).</t>
+          <t>The temple's own account, marked official in its name; its profile gives the founding year of 1450 and its World Heritage listing among the cultural properties of ancient Kyoto, matching this listing.</t>
         </is>
       </c>
       <c r="O389" s="2" t="inlineStr">
         <is>
-          <t>https://www.ryoanji.jp/</t>
+          <t>https://www.instagram.com/ryoanji_/</t>
         </is>
       </c>
       <c r="P389" t="inlineStr">
@@ -25861,14 +26081,10 @@
       </c>
       <c r="N392" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O392" s="2" t="inlineStr">
-        <is>
-          <t>https://www.shokoku-ji.jp/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the temple with its ward; it keeps no account of its own - the only related account belongs to a touring exhibition about the temple, and its sub-temple Kinkaku-ji keeps a separate account.</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -25923,7 +26139,7 @@
       </c>
       <c r="N393" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bridge; it is a public structure with no account of its own and the results were ryokan and shops beside it.</t>
         </is>
       </c>
       <c r="O393" t="inlineStr"/>
@@ -25970,23 +26186,39 @@
           <t>https://www.google.com/maps/place/%E5%A4%A7%E8%A6%9A%E5%AF%BA/data=!4m2!3m1!1s0x6001a9f5c1515dcf:0x95b9251e85d96323</t>
         </is>
       </c>
-      <c r="I394" t="inlineStr"/>
-      <c r="J394" t="inlineStr"/>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
-      <c r="M394" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/daikakuji_official/</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>daikakuji_official</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M394" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N394" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site could not be read, so no link could be confirmed (https://www.daikakuji.or.jp/ -&gt; 503).</t>
+          <t>The temple's own account, marked official in its name; its profile names it as the Shingon head temple formerly the Saga Imperial Palace, with 1200 years of history, matching this listing in Ukyo-ku.</t>
         </is>
       </c>
       <c r="O394" s="2" t="inlineStr">
         <is>
-          <t>https://www.daikakuji.or.jp/</t>
+          <t>https://www.instagram.com/daikakuji_official/</t>
         </is>
       </c>
       <c r="P394" t="inlineStr">
@@ -26234,23 +26466,39 @@
           <t>https://www.google.com/maps/place/%E5%8D%97%E5%BA%A7/data=!4m2!3m1!1s0x600108c03d0f278d:0x3f80dd5c373613e</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
-      <c r="J398" t="inlineStr"/>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
-      <c r="M398" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyoto_minamiza_theater/</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>kyoto_minamiza_theater</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M398" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N398" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The theatre's own account, marked official in its name; its profile names it as the theatre standing at the birthplace of kabuki with a history reaching back to the Keicho era, and a notice on the account places it at the east end of Shijo-Ohashi in Higashiyama-ku, where this listing places it.</t>
         </is>
       </c>
       <c r="O398" s="2" t="inlineStr">
         <is>
-          <t>https://www.shochiku.co.jp/play/theater/minamiza/</t>
+          <t>https://www.instagram.com/kyoto_minamiza_theater/</t>
         </is>
       </c>
       <c r="P398" t="inlineStr">
@@ -26385,7 +26633,7 @@
       </c>
       <c r="N400" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area; no account found for it - the results were other shops near Ginkaku-ji.</t>
         </is>
       </c>
       <c r="O400" t="inlineStr"/>
@@ -26432,21 +26680,41 @@
           <t>https://www.google.com/maps/place/%E7%84%BC%E8%82%89%E3%83%BB%E5%A1%A9%E3%83%9B%E3%83%AB%E3%83%A2%E3%83%B3+%E3%82%A2%E3%82%B8%E3%82%A7+%E6%9D%BE%E5%8E%9F%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x600108bee658eef9:0xbb11a4283ab1ffad</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr"/>
-      <c r="J401" t="inlineStr"/>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aje_kyoto_hoso/</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>aje_kyoto_hoso</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M401" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N401" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O401" t="inlineStr"/>
+          <t>The restaurant's own Kyoto account; its profile names its three Kyoto branches - Matsubara main shop, Kiyamachi-Donguri and Kita - and its three consecutive years in Tabelog's hundred best, but it is shared across the branches, so it is recorded as the operator's account rather than this branch's.</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aje_kyoto_hoso/</t>
+        </is>
+      </c>
       <c r="P401" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -26614,23 +26882,39 @@
           <t>https://www.google.com/maps/place/%E6%9C%AC%E5%AE%B6+%E7%AC%AC%E4%B8%80%E6%97%AD+%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x600108b1f3db0001:0xa5ed2c875338968b</t>
         </is>
       </c>
-      <c r="I404" t="inlineStr"/>
-      <c r="J404" t="inlineStr"/>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
-      <c r="M404" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/honke_daiichiasahi/</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>honke_daiichiasahi</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M404" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N404" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site could not be read, so no link could be confirmed (https://www.honke-daiichiasahi.com/shop.html -&gt; 403, https://www.honke-daiichiasahi.com/ -&gt; 403).</t>
+          <t>The account's own profile names the main shop, gives its founding year of 1947, places it five minutes' walk from Kyoto station in Shimogyo-ku where this listing places it, and gives its hours and Thursday closing.</t>
         </is>
       </c>
       <c r="O404" s="2" t="inlineStr">
         <is>
-          <t>https://www.honke-daiichiasahi.com/shop.html</t>
+          <t>https://www.instagram.com/honke_daiichiasahi/</t>
         </is>
       </c>
       <c r="P404" t="inlineStr">
@@ -26687,7 +26971,7 @@
       </c>
       <c r="N405" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its ward and category; no account found for this name in Sakyo-ku.</t>
         </is>
       </c>
       <c r="O405" t="inlineStr"/>
@@ -26745,7 +27029,7 @@
       </c>
       <c r="N406" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its ward and category; no account found for this name in Kamigyo-ku.</t>
         </is>
       </c>
       <c r="O406" t="inlineStr"/>
@@ -26877,7 +27161,7 @@
       </c>
       <c r="N408" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its ward and category; no account found for this name in Higashiyama-ku.</t>
         </is>
       </c>
       <c r="O408" t="inlineStr"/>
@@ -26924,21 +27208,41 @@
           <t>https://www.google.com/maps/place/%E3%82%B5%E3%82%A6%E3%83%8A%E3%81%AE%E6%A2%85%E6%B9%AF/data=!4m2!3m1!1s0x600108ba1add88f5:0xb51c556954ec8f8</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
-      <c r="J409" t="inlineStr"/>
-      <c r="K409" t="inlineStr"/>
-      <c r="L409" t="inlineStr"/>
-      <c r="M409" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/umeyu_rakuen/</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>umeyu_rakuen</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M409" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N409" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O409" t="inlineStr"/>
+          <t>The bathhouse's own account; its profile names it as a Kyoto sento heated with wood and fed by natural groundwater, run by Yutonami-sha, and gives its hours and Thursday closing. The profile names the city but not the ward.</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/umeyu_rakuen/</t>
+        </is>
+      </c>
       <c r="P409" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -26993,7 +27297,7 @@
       </c>
       <c r="N410" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bathhouse with its city; no account found for this name in Kyoto.</t>
         </is>
       </c>
       <c r="O410" t="inlineStr"/>
@@ -27051,7 +27355,7 @@
       </c>
       <c r="N411" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bathhouse and its Takatsuji branch; no account found for it.</t>
         </is>
       </c>
       <c r="O411" t="inlineStr"/>
@@ -27098,21 +27402,41 @@
           <t>https://www.google.com/maps/place/%E4%B8%80%E4%BF%9D%E5%A0%82%E8%8C%B6%E8%88%97+%E4%BA%AC%E9%83%BD%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x6001088c136aa771:0xd15e0ef5d39417d8</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
-      <c r="J412" t="inlineStr"/>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ippodotea/</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>ippodotea</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M412" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N412" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O412" t="inlineStr"/>
+          <t>The company's own account; its profile gives the Kyoto main shop's hours and its closing on the second Wednesday of the month, and states the firm has traded in Kyoto since 1717. It also covers the other shops, so it is recorded as the company's account.</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ippodotea/</t>
+        </is>
+      </c>
       <c r="P412" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -27167,7 +27491,7 @@
       </c>
       <c r="N413" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city and its best-known sweet; no account of its own was found - the name match is a different mochi shop, Kouda Futaba.</t>
         </is>
       </c>
       <c r="O413" t="inlineStr"/>
@@ -27276,23 +27600,39 @@
           <t>https://www.google.com/maps/place/Le+Petit+Mec+%E5%BE%A1%E6%B1%A0%E5%BA%97/data=!4m2!3m1!1s0x60010886b38bffff:0x18fc325f4363c800</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
-      <c r="J415" t="inlineStr"/>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lepetitmec/</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>lepetitmec</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M415" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N415" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The bakery's own brand account; its profile describes it as a French-style bakery with shops in Kyoto, Tokyo and Osaka but names no branch, so it is recorded as the brand account shared by its Kyoto branches.</t>
         </is>
       </c>
       <c r="O415" s="2" t="inlineStr">
         <is>
-          <t>https://lepetitmec.com/</t>
+          <t>https://www.instagram.com/lepetitmec/</t>
         </is>
       </c>
       <c r="P415" t="inlineStr">
@@ -27427,7 +27767,7 @@
       </c>
       <c r="N417" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name near Marutamachi.</t>
         </is>
       </c>
       <c r="O417" t="inlineStr"/>
@@ -27738,23 +28078,39 @@
           <t>https://www.google.com/maps/place/Le+Petit+Mec+%E4%BB%8A%E5%87%BA%E5%B7%9D%E5%BA%97/data=!4m2!3m1!1s0x600107e0cfb15aeb:0x8ef67c9fae793d7</t>
         </is>
       </c>
-      <c r="I422" t="inlineStr"/>
-      <c r="J422" t="inlineStr"/>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
-      <c r="M422" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lepetitmec/</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>lepetitmec</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M422" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N422" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The bakery's own brand account; its profile describes it as a French-style bakery with shops in Kyoto, Tokyo and Osaka but names no branch, so it is recorded as the brand account shared by its Kyoto branches.</t>
         </is>
       </c>
       <c r="O422" s="2" t="inlineStr">
         <is>
-          <t>https://lepetitmec.com/</t>
+          <t>https://www.instagram.com/lepetitmec/</t>
         </is>
       </c>
       <c r="P422" t="inlineStr">
@@ -27811,7 +28167,7 @@
       </c>
       <c r="N423" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Kyoto.</t>
         </is>
       </c>
       <c r="O423" t="inlineStr"/>
@@ -27858,21 +28214,41 @@
           <t>https://www.google.com/maps/place/%E3%81%A8%E3%82%8D%E3%82%8A%E5%A4%A9%E4%BD%BF%E3%81%AE%E3%82%8F%E3%82%89%E3%81%B3%E3%82%82%E3%81%A1+%E4%BA%AC%E9%83%BD%E6%B2%B3%E5%8E%9F%E7%94%BA%E5%BA%97/data=!4m2!3m1!1s0x600109c73726bf09:0xca6bb5368a6ea6cd</t>
         </is>
       </c>
-      <c r="I424" t="inlineStr"/>
-      <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
-      <c r="M424" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tenshino_warabi_kawaramachi/</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>tenshino_warabi_kawaramachi</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M424" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N424" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O424" t="inlineStr"/>
+          <t>The account's own profile names this branch, places it one minute from exit 1A of Kyoto-Kawaramachi station and two minutes from Gion-Shijo, and gives its daily hours of 12:00 to 21:00, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tenshino_warabi_kawaramachi/</t>
+        </is>
+      </c>
       <c r="P424" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -27927,7 +28303,7 @@
       </c>
       <c r="N425" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its ward and category; no account found for this name in Kita-ku.</t>
         </is>
       </c>
       <c r="O425" t="inlineStr"/>
@@ -27985,7 +28361,7 @@
       </c>
       <c r="N426" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop's counter in this department store; the shop keeps no account of its own and the only related account is the department store's own food-hall account, not this shop's.</t>
         </is>
       </c>
       <c r="O426" t="inlineStr"/>
@@ -28032,21 +28408,41 @@
           <t>https://www.google.com/maps/place/%E3%83%80%E3%83%96%E3%83%AB%E3%83%84%E3%83%AA%E3%83%BCby%E3%83%92%E3%83%AB%E3%83%88%E3%83%B3%E4%BA%AC%E9%83%BD%E6%9D%B1%E5%B1%B1/data=!4m2!3m1!1s0x600109ba395faed1:0xd0181aaa9468d594</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
-      <c r="J427" t="inlineStr"/>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
-      <c r="M427" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/doubletree.kyotohigashiyama/</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>doubletree.kyotohigashiyama</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M427" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N427" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O427" t="inlineStr"/>
+          <t>The hotel's own account, naming it in both Japanese and English; its profile states the hotel opened in Kyoto in August 2023, matching this listing in Higashiyama-ku.</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/doubletree.kyotohigashiyama/</t>
+        </is>
+      </c>
       <c r="P427" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -28168,17 +28564,21 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
-      <c r="M429" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M429" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N429" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O429" t="inlineStr"/>
+          <t>The only account tying this name to Kyoto is the proprietor's personal account, whose profile describes him as the owner of Yakiniku Yamachan in Kyoto and a wine sommelier; it is a personal account, not the restaurant's own, and gives no address, so it is not recorded.</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yakiniku.yamachan.1122/</t>
+        </is>
+      </c>
       <c r="P429" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -28855,14 +29255,10 @@
       </c>
       <c r="N439" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O439" s="2" t="inlineStr">
-        <is>
-          <t>https://www.jiyuken.co.jp/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for it in Namba.</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr"/>
       <c r="P439" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -28979,7 +29375,7 @@
       </c>
       <c r="N441" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its area and category; no account found for this name in Namba.</t>
         </is>
       </c>
       <c r="O441" t="inlineStr"/>
@@ -29037,14 +29433,10 @@
       </c>
       <c r="N442" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O442" s="2" t="inlineStr">
-        <is>
-          <t>http://masamuneya.com/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the shop and its Aioibashi branch; no account found for it - the name match at that bridge is a different restaurant, Ginza Zushi.</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr"/>
       <c r="P442" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29092,17 +29484,21 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
-      <c r="M443" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M443" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N443" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O443" t="inlineStr"/>
+          <t>An account carrying this name as Sousaku Teppan Miraku exists and gives its lunch and dinner hours, but it states no address, so it could not be placed in Kita-ku; the other name match is in Yuzawa, Akita.</t>
+        </is>
+      </c>
+      <c r="O443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sousakuteppanmiraku/</t>
+        </is>
+      </c>
       <c r="P443" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29146,21 +29542,41 @@
           <t>https://www.google.com/maps/place/%E5%B1%85%E9%85%92%E5%B1%8B+%E3%81%AA%E3%81%8C%E3%81%BB%E3%82%8A/data=!4m2!3m1!1s0x6000e0b547f41c7d:0x2cacd460417953ef</t>
         </is>
       </c>
-      <c r="I444" t="inlineStr"/>
-      <c r="J444" t="inlineStr"/>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
-      <c r="M444" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/izakaya_nagahori/</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>izakaya_nagahori</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M444" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N444" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O444" t="inlineStr"/>
+          <t>The account's own profile gives the restaurant's address as Uemachi 1-3-9, Chuo-ku, Osaka with its telephone number, opening hours and Sunday, Monday and holiday closing, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/izakaya_nagahori/</t>
+        </is>
+      </c>
       <c r="P444" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29200,21 +29616,41 @@
           <t>https://www.google.com/maps/place/WONDERMENT/data=!4m2!3m1!1s0x6000e6e17c310001:0x6a36912949aa1424</t>
         </is>
       </c>
-      <c r="I445" t="inlineStr"/>
-      <c r="J445" t="inlineStr"/>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
-      <c r="M445" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wonderment321/</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>wonderment321</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M445" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N445" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O445" t="inlineStr"/>
+          <t>The account's own profile gives the venue's address as Awajicho 3-4-12, Chuo-ku, Osaka, floors 2 to 3 of the Sunplaza Awajicho building, with an Osaka telephone number, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wonderment321/</t>
+        </is>
+      </c>
       <c r="P445" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29269,7 +29705,7 @@
       </c>
       <c r="N446" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Osaka.</t>
         </is>
       </c>
       <c r="O446" t="inlineStr"/>
@@ -29323,7 +29759,7 @@
       </c>
       <c r="N447" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its ward and category; no account found for this name in Kita-ku - the name matches are in Saitama, Kurume and Tokyo.</t>
         </is>
       </c>
       <c r="O447" t="inlineStr"/>
@@ -29377,7 +29813,7 @@
       </c>
       <c r="N448" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city and category; no account found for this name in Osaka.</t>
         </is>
       </c>
       <c r="O448" t="inlineStr"/>
@@ -29431,7 +29867,7 @@
       </c>
       <c r="N449" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name in Namba.</t>
         </is>
       </c>
       <c r="O449" t="inlineStr"/>
@@ -29474,21 +29910,41 @@
           <t>https://www.google.com/maps/place/%E7%A9%BA%20%E9%B6%B4%E6%A9%8B%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x6000e0abfa6cff2f:0xf02ffcecd9932480</t>
         </is>
       </c>
-      <c r="I450" t="inlineStr"/>
-      <c r="J450" t="inlineStr"/>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
-      <c r="M450" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yakinikuhorumon_sora/</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>yakinikuhorumon_sora</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M450" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N450" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O450" t="inlineStr"/>
+          <t>The restaurant's own account; its profile gives the Tsuruhashi head shop's address as Shimoajihara-cho 1-10, Tennoji-ku, Osaka with its Tuesday closing, and also covers the Dotonbori branch, so it is recorded as the operator's account. The guide calls the shop the Tsuruhashi main shop and the profile calls it the Tsuruhashi head shop.</t>
+        </is>
+      </c>
+      <c r="O450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yakinikuhorumon_sora/</t>
+        </is>
+      </c>
       <c r="P450" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29536,17 +29992,21 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
-      <c r="M451" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M451" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O451" t="inlineStr"/>
+          <t>The restaurant's own account exists and gives its telephone number, whose 06-6458 exchange covers the Fukushima area, but the profile prints no address, so the area could not be confirmed from the profile itself.</t>
+        </is>
+      </c>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sweetbasil2001/</t>
+        </is>
+      </c>
       <c r="P451" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29590,21 +30050,41 @@
           <t>https://www.google.com/maps/place/%E6%97%85%E4%BA%BA%E3%82%B7%E3%82%A7%E3%83%95%E3%81%AE%E3%82%BF%E3%82%A4%E9%A3%9F%E5%A0%82%20KHAO/data=!4m2!3m1!1s0x6000e74145514049:0x564e20b868fa0275</t>
         </is>
       </c>
-      <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr"/>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr"/>
-      <c r="M452" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tabichef/</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>tabichef</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M452" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N452" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O452" t="inlineStr"/>
+          <t>The account's own profile gives the restaurant's address as Tenjinbashi 6-2-5, Kita-ku, Osaka, in the Tenma area where this listing places it, with its hours and Sunday-Monday closing.</t>
+        </is>
+      </c>
+      <c r="O452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tabichef/</t>
+        </is>
+      </c>
       <c r="P452" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -29652,14 +30132,14 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr"/>
-      <c r="M453" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M453" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>The restaurant keeps an account for its Hanshin Umeda shop in Kita-ku, but no account was found for the Kitahorie main shop and no brand-level account exists, so none could be tied to this listing.</t>
         </is>
       </c>
       <c r="O453" t="inlineStr"/>
@@ -29779,14 +30259,10 @@
       </c>
       <c r="N455" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O455" s="2" t="inlineStr">
-        <is>
-          <t>https://futamiokitamajinja.or.jp/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the shrine with its city and its landmark rocks; it keeps no account of its own - the only name match is a restaurant beside a different pair of rocks in Itoshima, Fukuoka.</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr"/>
       <c r="P455" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30122,21 +30598,41 @@
           <t>https://www.google.com/maps/place/%E3%81%8D%E3%82%93%E3%82%81%E3%81%A0%E3%81%84/data=!4m2!3m1!1s0x601881e2495b5993:0x5c1d4d191b3e0290</t>
         </is>
       </c>
-      <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
-      <c r="M460" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kinmaidai/</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>kinmaidai</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M460" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N460" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O460" t="inlineStr"/>
+          <t>The account's own name places the shop in Nishifuna, the Nishi-Funabashi area where this listing places it, and its profile gives its lunch and dinner hours, Tuesday closing and no-reservation policy.</t>
+        </is>
+      </c>
+      <c r="O460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kinmaidai/</t>
+        </is>
+      </c>
       <c r="P460" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30180,21 +30676,41 @@
           <t>https://www.google.com/maps/place/%E3%82%A2%E3%83%A6%E3%82%BF%E3%83%A4/data=!4m2!3m1!1s0x60187fd71b85a9d7:0xa461bfb6a86ba8b5</t>
         </is>
       </c>
-      <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr"/>
-      <c r="K461" t="inlineStr"/>
-      <c r="L461" t="inlineStr"/>
-      <c r="M461" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ayuthaya.gcp/</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>ayuthaya.gcp</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M461" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N461" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O461" t="inlineStr"/>
+          <t>The account's own profile states that the restaurant trades in Funabashi, Chiba, where this listing places it.</t>
+        </is>
+      </c>
+      <c r="O461" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ayuthaya.gcp/</t>
+        </is>
+      </c>
       <c r="P461" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30242,17 +30758,21 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
-      <c r="M462" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M462" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O462" t="inlineStr"/>
+          <t>The only account carrying this shop's name is the proprietor Osamu Tomita's own account; it is a personal account rather than the shop's and gives no address, so it is not recorded.</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomita.8860/</t>
+        </is>
+      </c>
       <c r="P462" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30435,14 +30955,10 @@
       </c>
       <c r="N465" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
-        </is>
-      </c>
-      <c r="O465" s="2" t="inlineStr">
-        <is>
-          <t>https://misono.org/</t>
-        </is>
-      </c>
+          <t>Searched Instagram for the restaurant and its Kobe main shop; no account found for it - the name match is a teppanyaki restaurant serving Iga beef with no Kobe branch.</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr"/>
       <c r="P465" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30497,7 +31013,7 @@
       </c>
       <c r="N466" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name in Ashiya - the name match is a Thai restaurant in Joetsu, Niigata.</t>
         </is>
       </c>
       <c r="O466" t="inlineStr"/>
@@ -30551,7 +31067,7 @@
       </c>
       <c r="N467" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and city; no account found for this name in Haruyoshi.</t>
         </is>
       </c>
       <c r="O467" t="inlineStr"/>
@@ -30598,17 +31114,21 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr"/>
-      <c r="M468" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M468" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O468" t="inlineStr"/>
+          <t>The restaurant's own account exists but its profile lists only its Kashii branches, with no Chiyo branch, so no account could be tied to this listing.</t>
+        </is>
+      </c>
+      <c r="O468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/genpukan1996/</t>
+        </is>
+      </c>
       <c r="P468" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -30663,7 +31183,7 @@
       </c>
       <c r="N469" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name in Itoshima.</t>
         </is>
       </c>
       <c r="O469" t="inlineStr"/>
@@ -30717,7 +31237,7 @@
       </c>
       <c r="N470" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O470" t="inlineStr"/>
@@ -30771,7 +31291,7 @@
       </c>
       <c r="N471" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant and its Asuka branch; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O471" t="inlineStr"/>
@@ -30818,14 +31338,14 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr"/>
-      <c r="M472" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M472" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N472" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>The chain keeps branch accounts for Mizonokuchi and Obihiro, and the Mizonokuchi profile names itself an offshoot of the Otaru main shop, but no account for the Otaru main shop itself was found.</t>
         </is>
       </c>
       <c r="O472" t="inlineStr"/>
@@ -30879,7 +31399,7 @@
       </c>
       <c r="N473" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O473" t="inlineStr"/>
@@ -30922,23 +31442,39 @@
           <t>https://www.google.com/maps/place/%E3%81%8A%E3%81%9F%E3%82%8B%E6%94%BF%E5%AF%BF%E5%8F%B8+%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x5f0ae051659543b9:0x2be81415c4b44909</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
-      <c r="J474" t="inlineStr"/>
-      <c r="K474" t="inlineStr"/>
-      <c r="L474" t="inlineStr"/>
-      <c r="M474" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/otarumasazushi/</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>otarumasazushi</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M474" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N474" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The restaurant's own account, named for the shop in Otaru; its Ginza branch keeps a separate account that describes itself as the Ginza branch, leaving this one as the Otaru shop's.</t>
         </is>
       </c>
       <c r="O474" s="2" t="inlineStr">
         <is>
-          <t>https://www.masazushi.co.jp/</t>
+          <t>https://www.instagram.com/otarumasazushi/</t>
         </is>
       </c>
       <c r="P474" t="inlineStr">
@@ -30991,7 +31527,7 @@
       </c>
       <c r="N475" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city and category; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O475" t="inlineStr"/>
@@ -31103,7 +31639,7 @@
       </c>
       <c r="N477" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O477" t="inlineStr"/>
@@ -31220,21 +31756,41 @@
           <t>https://www.google.com/maps/place/%E3%82%89%E3%81%8F%E5%A4%A9/data=!4m2!3m1!1s0x5f0ae0531d8e87d3:0x239b85174a784a3f</t>
         </is>
       </c>
-      <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr"/>
-      <c r="K479" t="inlineStr"/>
-      <c r="L479" t="inlineStr"/>
-      <c r="M479" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raku10_official/</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>raku10_official</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M479" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N479" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O479" t="inlineStr"/>
+          <t>The account's own name places the izakaya in Otaru, Hokkaido and lists its oden, horumon and chuka soba, and its profile puts it on Miyako-dori ten minutes' walk from Otaru station with its hours and Monday closing.</t>
+        </is>
+      </c>
+      <c r="O479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raku10_official/</t>
+        </is>
+      </c>
       <c r="P479" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -31343,7 +31899,7 @@
       </c>
       <c r="N481" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Otaru.</t>
         </is>
       </c>
       <c r="O481" t="inlineStr"/>
@@ -31455,7 +32011,7 @@
       </c>
       <c r="N483" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the izakaya with its city and category; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O483" t="inlineStr"/>
@@ -31567,7 +32123,7 @@
       </c>
       <c r="N485" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the izakaya with its city and category; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O485" t="inlineStr"/>
@@ -31621,7 +32177,7 @@
       </c>
       <c r="N486" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O486" t="inlineStr"/>
@@ -31675,7 +32231,7 @@
       </c>
       <c r="N487" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bathhouse with its city; no account found for this name in Asahikawa - the name matches are bathhouses in Tokyo, Nagoya and Kyoto.</t>
         </is>
       </c>
       <c r="O487" t="inlineStr"/>
@@ -31729,7 +32285,7 @@
       </c>
       <c r="N488" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bathhouse with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O488" t="inlineStr"/>
@@ -31783,7 +32339,7 @@
       </c>
       <c r="N489" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bathhouse with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O489" t="inlineStr"/>
@@ -31837,7 +32393,7 @@
       </c>
       <c r="N490" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the izakaya with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O490" t="inlineStr"/>
@@ -31965,7 +32521,7 @@
       </c>
       <c r="N492" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O492" t="inlineStr"/>
@@ -32019,7 +32575,7 @@
       </c>
       <c r="N493" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O493" t="inlineStr"/>
@@ -32073,7 +32629,7 @@
       </c>
       <c r="N494" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O494" t="inlineStr"/>
@@ -32127,7 +32683,7 @@
       </c>
       <c r="N495" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O495" t="inlineStr"/>
@@ -32174,17 +32730,21 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr"/>
-      <c r="M496" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M496" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N496" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O496" t="inlineStr"/>
+          <t>The only account found for this shop belongs to its manager; it places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is a personal account rather than the shop's own, so it is not recorded.</t>
+        </is>
+      </c>
+      <c r="O496" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ginneko.manager_matchan/</t>
+        </is>
+      </c>
       <c r="P496" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -32224,23 +32784,39 @@
           <t>https://www.google.com/maps/place/%E3%82%89%E3%83%BC%E3%82%81%E3%82%93%E5%B1%B1%E9%A0%AD%E7%81%AB+%E6%97%AD%E5%B7%9D%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x5f0ce6110ddef21d:0x61dd14fd7bdaf12d</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr"/>
-      <c r="J497" t="inlineStr"/>
-      <c r="K497" t="inlineStr"/>
-      <c r="L497" t="inlineStr"/>
-      <c r="M497" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I497" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/santouka_honten/</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>santouka_honten</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M497" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N497" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The account's own name identifies the Asahikawa main shop and its profile gives the founding year of 1988, the daily hours and items sold only at the main shop, matching this listing.</t>
         </is>
       </c>
       <c r="O497" s="2" t="inlineStr">
         <is>
-          <t>https://www.santouka.co.jp/shop-jp/hokkaido/area01-001/</t>
+          <t>https://www.instagram.com/santouka_honten/</t>
         </is>
       </c>
       <c r="P497" t="inlineStr">
@@ -32293,7 +32869,7 @@
       </c>
       <c r="N498" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Asahikawa.</t>
         </is>
       </c>
       <c r="O498" t="inlineStr"/>
@@ -32347,7 +32923,7 @@
       </c>
       <c r="N499" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city and category; no account found for this name in Sapporo.</t>
         </is>
       </c>
       <c r="O499" t="inlineStr"/>
@@ -32401,7 +32977,7 @@
       </c>
       <c r="N500" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the shop with its city; no account found for this name in Sapporo.</t>
         </is>
       </c>
       <c r="O500" t="inlineStr"/>
@@ -32576,23 +33152,39 @@
           <t>https://www.google.com/maps/place/%E7%8B%B8%E5%B0%8F%E8%B7%AF/data=!4m2!3m1!1s0x5f0b298530a7cfd5:0x2ad2065307072ffd</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr"/>
-      <c r="J503" t="inlineStr"/>
-      <c r="K503" t="inlineStr"/>
-      <c r="L503" t="inlineStr"/>
-      <c r="M503" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I503" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tanukikoji_syotengai/</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>tanukikoji_syotengai</t>
+        </is>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M503" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N503" s="4" t="inlineStr">
         <is>
-          <t>The venue's own site was read and carries no link to an Instagram account.</t>
+          <t>The shopping street's own account, marked official in its name; its profile describes it as the historic arcade in central Sapporo dating from 1873 and gives its extent as Minami 2 and 3-jo Nishi 1 to 7-chome, Chuo-ku, matching this listing.</t>
         </is>
       </c>
       <c r="O503" s="2" t="inlineStr">
         <is>
-          <t>https://www.tanukikoji.or.jp/</t>
+          <t>https://www.instagram.com/tanukikoji_syotengai/</t>
         </is>
       </c>
       <c r="P503" t="inlineStr">
@@ -32707,7 +33299,7 @@
       </c>
       <c r="N505" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the izakaya with its region and category; no account found for this name in Hokkaido.</t>
         </is>
       </c>
       <c r="O505" t="inlineStr"/>
@@ -32750,21 +33342,41 @@
           <t>https://www.google.com/maps/place/%E7%84%BC%E8%82%89%20%E3%82%B0%E3%83%AB%E3%83%9E%E3%83%B3%E3%82%BA%E3%81%84%E3%81%A8%E3%81%86/data=!4m2!3m1!1s0x5f0b2988b48e5197:0xaf340660bb2a485d</t>
         </is>
       </c>
-      <c r="I506" t="inlineStr"/>
-      <c r="J506" t="inlineStr"/>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
-      <c r="M506" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gurumanzu_ito/</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>gurumanzu_ito</t>
+        </is>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M506" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N506" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O506" t="inlineStr"/>
+          <t>The account's own profile gives the restaurant's address as Minami 3-jo Nishi 3-chome 8-2, Katsumi building ground floor, Chuo-ku, Sapporo, with its telephone number and Wednesday closing, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O506" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gurumanzu_ito/</t>
+        </is>
+      </c>
       <c r="P506" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -32873,7 +33485,7 @@
       </c>
       <c r="N508" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city and category; no account found for this name in Naha.</t>
         </is>
       </c>
       <c r="O508" t="inlineStr"/>
@@ -32927,7 +33539,7 @@
       </c>
       <c r="N509" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its village and category; no account found for this name in Onna - the name match is in Chatan.</t>
         </is>
       </c>
       <c r="O509" t="inlineStr"/>
@@ -32985,7 +33597,7 @@
       </c>
       <c r="N510" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city; no account found for this name in Nagoya.</t>
         </is>
       </c>
       <c r="O510" t="inlineStr"/>
@@ -33028,21 +33640,41 @@
           <t>https://www.google.com/maps/place/tbz%20%E8%A6%9A%E7%8E%8B%E5%B1%B1%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x600371495f45fbb7:0xe6d97bb08a5e832c</t>
         </is>
       </c>
-      <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr"/>
-      <c r="K511" t="inlineStr"/>
-      <c r="L511" t="inlineStr"/>
-      <c r="M511" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tbz_kakuozan/</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>tbz_kakuozan</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M511" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N511" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O511" t="inlineStr"/>
+          <t>The account's own handle names the Kakuozan shop and its profile describes it as a teriyaki burger specialist with its lunch and dinner hours and Wednesday closing, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O511" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tbz_kakuozan/</t>
+        </is>
+      </c>
       <c r="P511" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33082,21 +33714,41 @@
           <t>https://www.google.com/maps/place/%E3%83%93%E3%83%83%E3%82%B0%E3%82%B9%E3%83%9E%E3%82%A4%E3%83%AB/data=!4m2!3m1!1s0x60189dce1df7acab:0xeec6e3bca6c0703c</t>
         </is>
       </c>
-      <c r="I512" t="inlineStr"/>
-      <c r="J512" t="inlineStr"/>
-      <c r="K512" t="inlineStr"/>
-      <c r="L512" t="inlineStr"/>
-      <c r="M512" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamburger_big_smile/</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>hamburger_big_smile</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M512" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N512" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O512" t="inlineStr"/>
+          <t>The account's own profile gives the shop's address as Togashira 2-3-11, Toride, Ibaraki, describes it as a small American roadside-style burger shop and gives its weekday and weekend hours, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O512" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hamburger_big_smile/</t>
+        </is>
+      </c>
       <c r="P512" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33136,21 +33788,41 @@
           <t>https://www.google.com/maps/place/THE%20BURGER%20HEARTS/data=!4m2!3m1!1s0x5f88a72bd14eb051:0x48969b05840fb20d</t>
         </is>
       </c>
-      <c r="I513" t="inlineStr"/>
-      <c r="J513" t="inlineStr"/>
-      <c r="K513" t="inlineStr"/>
-      <c r="L513" t="inlineStr"/>
-      <c r="M513" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_burger_hearts/</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>the_burger_hearts</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M513" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N513" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O513" t="inlineStr"/>
+          <t>The account's own profile describes the shop as a hamburger shop in Ofunato, Iwate, where this listing places it, and gives its hours of 11:30 to 19:00 and Monday closing.</t>
+        </is>
+      </c>
+      <c r="O513" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_burger_hearts/</t>
+        </is>
+      </c>
       <c r="P513" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33201,7 +33873,7 @@
       </c>
       <c r="N514" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its city and category; no account found for this name in Yokosuka.</t>
         </is>
       </c>
       <c r="O514" t="inlineStr"/>
@@ -33259,7 +33931,7 @@
       </c>
       <c r="N515" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its area and category; no account found for this name in Minami-Rinkan.</t>
         </is>
       </c>
       <c r="O515" t="inlineStr"/>
@@ -33310,17 +33982,21 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
-      <c r="M516" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M516" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N516" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O516" t="inlineStr"/>
+          <t>An account for the restaurant's main shop exists and its profile describes a 75-year-old Kumamoto restaurant serving horse meat and local dishes, but it names no branch or address, so it could not be tied to the Suizenji shop.</t>
+        </is>
+      </c>
+      <c r="O516" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gorohachi_kumamoto0568/</t>
+        </is>
+      </c>
       <c r="P516" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33364,21 +34040,41 @@
           <t>https://www.google.com/maps/place/%E3%81%BE%E3%82%93%E3%81%94%E3%82%84/data=!4m2!3m1!1s0x3538b70f046af81b:0xb0df4ec1b2f7f624</t>
         </is>
       </c>
-      <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
-      <c r="K517" t="inlineStr"/>
-      <c r="L517" t="inlineStr"/>
-      <c r="M517" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raanmamuan/</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>raanmamuan</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M517" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N517" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O517" t="inlineStr"/>
+          <t>The account's own profile places the restaurant on Haikara-dori two minutes' walk from Yamakataya in Miyazaki, gives its opening year of 2002 and describes the owner's training in Bangkok, matching this listing.</t>
+        </is>
+      </c>
+      <c r="O517" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/raanmamuan/</t>
+        </is>
+      </c>
       <c r="P517" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33422,14 +34118,14 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
-      <c r="M518" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="M518" s="6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N518" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Two accounts exist for facilities on this bathhouse's grounds in Hakuba - its car-stay park and its campsite - and both describe the spring's iron-rich water, but neither is the bathhouse's own account, so none is recorded.</t>
         </is>
       </c>
       <c r="O518" t="inlineStr"/>
@@ -33631,7 +34327,7 @@
       </c>
       <c r="N521" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the izakaya with its village and category; no account found for this name in Hakuba.</t>
         </is>
       </c>
       <c r="O521" t="inlineStr"/>
@@ -33685,7 +34381,7 @@
       </c>
       <c r="N522" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the restaurant with its village; no account found for this name in Hakuba - the name match is a yakiniku restaurant in Kanazawa.</t>
         </is>
       </c>
       <c r="O522" t="inlineStr"/>
@@ -33848,21 +34544,41 @@
           <t>https://www.google.com/maps/place/YOKOKURA%20STOREHOUSE/data=!4m2!3m1!1s0x601f4dab2c006dc7:0xff0a0559239a91da</t>
         </is>
       </c>
-      <c r="I525" t="inlineStr"/>
-      <c r="J525" t="inlineStr"/>
-      <c r="K525" t="inlineStr"/>
-      <c r="L525" t="inlineStr"/>
-      <c r="M525" s="3" t="inlineStr">
-        <is>
-          <t>NOT_FOUND</t>
+      <c r="I525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yokokura_storehouse.un/</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>yokokura_storehouse.un</t>
+        </is>
+      </c>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M525" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N525" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
-        </is>
-      </c>
-      <c r="O525" t="inlineStr"/>
+          <t>The account's own profile gives the restaurant's address as Yokokura 596-76, Oyama, Tochigi with its telephone number, Thursday closing and lunch and dinner hours; the guide records the area as Oyama written with a different first character.</t>
+        </is>
+      </c>
+      <c r="O525" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yokokura_storehouse.un/</t>
+        </is>
+      </c>
       <c r="P525" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -33917,7 +34633,7 @@
       </c>
       <c r="N526" s="4" t="inlineStr">
         <is>
-          <t>No official website is on record for this venue, so no page under its own domain could be read. Instagram blocks unauthenticated profile reads, so a profile-only match could not be cross-checked either.</t>
+          <t>Searched Instagram for the bar with its city and category; no account found for this name in Toyama.</t>
         </is>
       </c>
       <c r="O526" t="inlineStr"/>
@@ -34041,949 +34757,1017 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O28" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId667"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId668"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId669"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O383" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O392" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O439" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O442" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O455" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O465" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1060"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35019,7 +35803,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>180</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -35039,7 +35823,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>70</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5">
@@ -35049,7 +35833,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6">
@@ -35059,7 +35843,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -35069,7 +35853,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8">
@@ -35079,7 +35863,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>254</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
@@ -35101,12 +35885,12 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Venues still to search</t>
+          <t>Per-venue search coverage</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>139 of the NOT_FOUND rows have not yet had the per-venue Instagram search run on them; their evidence line is from the website pass</t>
+          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them; every row carries either a result or the reason none could be established</t>
         </is>
       </c>
     </row>

--- a/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
+++ b/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>An account named イト I.To describes a French-based a la carte restaurant, but its profile text does not state Higashi-Nakano, so it could not be tied to this listing.</t>
+          <t>An account named イト I.To describes a French-based a la carte restaurant, but its profile text does not state Higashi-Nakano, so it could not be tied to this listing. Second pass: the restaurant's own account was found and its profile describes its French-based a la carte cooking and private-hire minimum, but it states no address or area, so it could not be placed in Higashi-Nakano.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1218,23 +1218,39 @@
           <t>https://www.google.com/maps/place/%E9%AF%96%E9%BB%92%E7%85%AE%E5%B0%82%E9%96%80%E5%BA%97+%E9%A3%9F%E5%A0%82%E6%96%B0+%E7%A5%9E%E4%BF%9D%E7%94%BA/data=!4m2!3m1!1s0x60188ddcc9fc2b7b:0x47e8e57c6ca38c8a</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jimbocho_shokudou.arata/</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>jimbocho_shokudou.arata</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: jimbocho_shokudou.arata</t>
+          <t>Second pass: the account's own profile gives the shop's address as Kanda-Sarugakucho 1-2-4, Chiyoda-ku - the block beside Jimbocho where this listing places it - names its mackerel speciality and gives its lunch-only hours and weekend closing.</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/en/shop/xE95RKbN1ajXXqTyT2r8</t>
+          <t>https://www.instagram.com/jimbocho_shokudou.arata/</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1799,7 +1815,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>The only account of this brand is the Ueno/Okachimachi branch's, whose profile gives the Ueno address; no account for the Harajuku branch was found, and the Ueno branch's account is not this branch's.</t>
+          <t>The only account of this brand is the Ueno/Okachimachi branch's, whose profile gives the Ueno address; no account for the Harajuku branch was found, and the Ueno branch's account is not this branch's. Second pass: the brand keeps one account, whose profile gives only the Ueno shop's address and hours; no account for the Harajuku branch exists, so none could be tied to this listing.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1842,23 +1858,39 @@
           <t>https://www.google.com/maps/place/%E3%81%A8%E3%82%93%E3%81%8B%E3%81%A4+%E3%81%82%E3%81%92%E7%A6%8F%EF%BC%88Tonkatsu+Agefuku%EF%BC%89/data=!4m2!3m1!1s0x60188ae4a2157c1f:0x53108000e616ac89</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/agefuku29/</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>agefuku29</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: artsupply1971</t>
+          <t>Second pass: the account's own name identifies the Gotanda shop where this listing places it, and its profile describes its sous-vide tonkatsu and the Yazawa Meat group that runs it.</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>https://san-tatsu.jp/articles/244674/</t>
+          <t>https://www.instagram.com/agefuku29/</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2093,7 +2125,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: azabuen0818</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: azabuen0818 Second pass: no account was found under this restaurant's name; the nearest match is a differently named Azabu-Juban restaurant whose only account belongs to its manager.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3178,23 +3210,39 @@
           <t>https://www.google.com/maps/place/%E3%81%84%E3%81%96%E3%81%8B%E3%82%84+%E3%81%BB%E3%81%97%E3%81%90%E3%81%BF/data=!4m2!3m1!1s0x6018f49f4fcad591:0x469d70df557dfec7</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/izakaya_hoshigumi/</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>izakaya_hoshigumi</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>The account found is the group's annex shop (shinkan, its third shop) in Sangenjaya, not identifiably this listing's shop; no account for this shop itself was found.</t>
+          <t>Second pass: the account's own profile places the izakaya one minute from Sangenjaya station with 45 seats and a 20-person tatami room upstairs, and gives its weekday and weekend hours; the third branch keeps a separate account.</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/izakaya_hoshigumi_shinkan/</t>
+          <t>https://www.instagram.com/izakaya_hoshigumi/</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4392,23 +4440,39 @@
           <t>https://www.google.com/maps/place/BAKER+Aoyagi+%E3%83%99%E3%83%BC%E3%82%AB%E3%83%BC%E3%82%A2%E3%82%AA%E3%83%A4%E3%82%AE/data=!4m2!3m1!1s0x6018f347559e5173:0x9783714320a7d338</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/baker_aoyagi/</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>baker_aoyagi</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: baker_aoyagi, katayamachikako</t>
+          <t>Second pass: the bakery's own account; its profile lists Higashi-Kitazawa and Yoyogi-Uehara as its locations, describes its high-hydration sourdough baking and gives its Wednesday-to-Saturday hours.</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>https://www.enjoytokyo.jp/article/201854/</t>
+          <t>https://www.instagram.com/baker_aoyagi/</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -4450,23 +4514,39 @@
           <t>https://www.google.com/maps/place/%C3%A9t%C3%A9co+bread/data=!4m2!3m1!1s0x6018f3afaaab9c1f:0xebc09730bba5ac06</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/eteco_bread/</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>eteco_bread</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: eteco_bread</t>
+          <t>Second pass: the account's own profile gives the bakery's address as Daizawa 2-42-7, Setagaya-ku, in the Shimokitazawa area where this listing places it, with its closing days and sell-out closing.</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>https://gendai.media/articles/-/85279</t>
+          <t>https://www.instagram.com/eteco_bread/</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -4519,7 +4599,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: senrigaaan</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: senrigaaan Second pass: no account was found for this shop in Yoyogi-Uehara; the handle printed for it on a directory page belongs to a shop of the same name in Shiki, Saitama, so it was not recorded.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -4896,23 +4976,39 @@
           <t>https://www.google.com/maps/place/%E3%83%AB%E3%83%BB%E3%83%AB%E3%82%BD%E3%83%BC%E3%83%AB/data=!4m2!3m1!1s0x6018f350700ffdfb:0xe018dd0b5eface13</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/le_ressort/</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>le_ressort</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bondicoffeesandwiches, le_ressort</t>
+          <t>Second pass: the account's own profile places the bakery one minute from Komaba-Todaimae station on the Inokashira line and gives its hours of 9:00 to 17:00, matching this listing.</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>https://www.timeout.jp/tokyo/ja/%E3%82%B7%E3%83%A7%E3%83%83%E3%83%94%E3%83%B3%E3%82%B0/%E3%83%AB%E3%83%BB%E3%83%AB%E3%82%BD%E3%83%BC%E3%83%AB</t>
+          <t>https://www.instagram.com/le_ressort/</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5019,12 +5115,12 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bakumatsucurry, ippukuandmatcha_uehara, sakaba_debayashi</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bakumatsucurry, ippukuandmatcha_uehara, sakaba_debayashi Second pass: the bakery's own account was found and its profile gives the opening hours and closing days, but it states no address or area, so it could not be placed in Nishihara.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/area/tokyo/shibuya/yoyogiuehara/shops</t>
+          <t>https://www.instagram.com/katanebakery/</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5288,23 +5384,39 @@
           <t>https://www.google.com/maps/place/%E3%83%86%E3%82%B3%E3%83%8A+%E3%83%99%E3%83%BC%E3%82%B0%E3%83%AB+%E3%83%AF%E3%83%BC%E3%82%AF%E3%82%B9/data=!4m2!3m1!1s0x6018f34c9cca8119:0x6ae961c52c1ada22</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tecona_bagel_works/</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>tecona_bagel_works</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: embed.js, tokyo_bagel</t>
+          <t>Second pass: the account's own name identifies the Yoyogi-Hachiman main shop and its profile gives its hours, its takeout-only service and its trading since 2009; this guide records the same shop under the adjoining neighbourhood name Tomigaya, which is where Yoyogi-Hachiman station stands. The Jiyugaoka and Kyodo shops keep separate accounts.</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>https://macaro-ni.jp/26492?page=2</t>
+          <t>https://www.instagram.com/tecona_bagel_works/</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5357,10 +5469,14 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. The only Instagram link on the page reached was rurubuplus, the publisher's own account. Seen: none</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. The only Instagram link on the page reached was rurubuplus, the publisher's own account. Seen: none Second pass: an account under this shop's name was found and its profile gives the cafe and crepe hours and the whole-cake ordering, but it states no address or area, so it could not be placed in Yoyogi-Uehara.</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/horn.tokyo/</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -5411,7 +5527,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yomuno_official</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yomuno_official Second pass: no account was found under this restaurant's name in Nakameguro; the results were other steak and teppanyaki restaurants in the area.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -5631,7 +5747,7 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kinarino_official</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kinarino_official Second pass: no account was found under this shop's name in Otowa; the handle printed for it on a directory page is the publisher's own.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -5763,7 +5879,7 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Two accounts both present themselves as this brand's Omotesando shop (amam_dacotan_omotesando and amam_dacotan_omotedando) and they give different addresses; neither could be established as the shop's own, so none is recorded.</t>
+          <t>Two accounts both present themselves as this brand's Omotesando shop (amam_dacotan_omotesando and amam_dacotan_omotedando) and they give different addresses; neither could be established as the shop's own, so none is recorded. Second pass: two accounts present themselves as this brand's Omotesando shop under near-identical names, and both now give the same address at Kita-Aoyama 3-7-6; because nothing distinguishes which of the two is the shop's current account, neither is recorded. A third account belongs to the separate cafe and bake shop at Kita-Aoyama 3-6-23.</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
@@ -6403,7 +6519,7 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>The account found belongs to this operator's Keikeikaku branches near Kamata station, not to the main shop this listing records; no account for the main shop was found.</t>
+          <t>The account found belongs to this operator's Keikeikaku branches near Kamata station, not to the main shop this listing records; no account for the main shop was found. Second pass: the brand keeps an account for its Keishinkaku branch, whose profile lists the Kamata branches, but no account was found for the main shop, so none could be tied to this listing.</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
@@ -7323,12 +7439,12 @@
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: pizzeriaciro.hgn</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: pizzeriaciro.hgn Second pass: the shop's own account was found and its profile gives the lunch and dinner hours, closing days and a Tokyo telephone number, but no address or area, so it could not be placed in Nakano.</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>https://macaro-ni.jp/91224?page=2</t>
+          <t>https://www.instagram.com/soba_yamasho/</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -7518,23 +7634,39 @@
           <t>https://www.google.com/maps/place/%E5%AF%BF%E6%B9%AF/data=!4m2!3m1!1s0x60188e9822404bfb:0x6f65f3c536670490</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kotobukiyu.ueno/</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>kotobukiyu.ueno</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: niftyonsen</t>
+          <t>Second pass: the account's own handle names the Ueno bathhouse and its profile describes its open-air bath, bathing and sauna charges and hours of 11:00 to 25:30; the same-named bathhouse in Higashi-Yotsugi keeps a separate account.</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>https://onsen.nifty.com/ueno-tokyo-onsen/onsen007554/</t>
+          <t>https://www.instagram.com/kotobukiyu.ueno/</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -7957,7 +8089,7 @@
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The monument has no account of its own. The site links two Yasukuni Shrine accounts and neither is the statue's - left ambiguous rather than attributing the shrine's account to a monument. Candidates: yasukuni.official, yasukunijinja</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The monument has no account of its own. The site links two Yasukuni Shrine accounts and neither is the statue's - left ambiguous rather than attributing the shrine's account to a monument. Candidates: yasukuni.official, yasukunijinja Second pass: the statue has no account of its own. The shrine whose grounds it stands in keeps one, but attributing the shrine's account to a monument would misrepresent it, so none is recorded.</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
@@ -9005,7 +9137,7 @@
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Accounts reached are Meiji Kinenkan and the shrine's support association, neither of them the shrine's own account. Seen: meiji_kinenkan_official, meijijingu_sukeikai</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Accounts reached are Meiji Kinenkan and the shrine's support association, neither of them the shrine's own account. Seen: meiji_kinenkan_official, meijijingu_sukeikai Second pass: the shrine keeps no account of its own; the only official account in its name belongs to its wedding venue, Forest Terrace, so none is recorded for the shrine.</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -9052,23 +9184,39 @@
           <t>https://www.google.com/maps/place/%EF%A8%9C%E5%9C%8B%E7%A5%9E%E7%A4%BE/data=!4m2!3m1!1s0x60188c680dae43d5:0xb5e754e6bf88ce90</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yasukuni.official/</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>yasukuni.official</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N135" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The shrine's own site links two accounts (yasukuni.official / yasukunijinja) and does not say which is current. Candidates: yasukuni.official, yasukunijinja</t>
+          <t>Second pass: of the shrine's two accounts this one is the current official account - its profile names the shrine at Kudan in central Tokyo, gives Kudanshita, Ichigaya and Iidabashi as its nearest stations and states the number of souls enshrined since 1853, while the older account announced that its series had ended and that a new recognised account would follow.</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>https://www.yasukuni.or.jp/</t>
+          <t>https://www.instagram.com/yasukuni.official/</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -9195,7 +9343,7 @@
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Museum inside Yasukuni; its page links the shrine's two accounts, neither specific to the museum. Candidates: yasukuni.official, yasukunijinja</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Museum inside Yasukuni; its page links the shrine's two accounts, neither specific to the museum. Candidates: yasukuni.official, yasukunijinja Second pass: the museum keeps no account of its own. The shrine it stands in has one, but it is the shrine's and not this museum's, so none is recorded.</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
@@ -9381,7 +9529,7 @@
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the street were reached, not the shopping street's own. Seen: kanaya_brush_1914, takaso_demoandkitchen</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the street were reached, not the shopping street's own. Seen: kanaya_brush_1914, takaso_demoandkitchen Second pass: the shopping street keeps no account of its own; the association that runs it maintains an account for its annual tool fair, and the rest are individual member shops, so none is recorded for the street.</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
@@ -9493,7 +9641,7 @@
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: agora_jp, sensyuyatai</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: agora_jp, sensyuyatai Second pass: no account was found that carries this shop's name and places it anywhere; the handle printed for it on a directory page could not be confirmed on a profile.</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -9901,7 +10049,7 @@
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only the hotel's and its sibling restaurants' accounts were reached, none of them this bar's. Seen: aoyamagrand, theriveroriental, thetokyorestaurant</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only the hotel's and its sibling restaurants' accounts were reached, none of them this bar's. Seen: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this bar's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this bar's.</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -9959,7 +10107,7 @@
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>Two accounts carry this name: one places itself in Minami-Aoyama and Nishi-Azabu, not Ginza, and the other gives no location. Neither could be tied to this listing.</t>
+          <t>Two accounts carry this name: one places itself in Minami-Aoyama and Nishi-Azabu, not Ginza, and the other gives no location. Neither could be tied to this listing. Second pass: the account carrying this bar's name places itself in Minami-Aoyama and Nishi-Azabu, not Ginza where this listing places it, so it was not recorded.</t>
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
@@ -10087,7 +10235,7 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>An account of this exact name exists and describes a soba restaurant in a century-old townhouse, but its profile states no location, so it could not be tied to this listing's area.</t>
+          <t>An account of this exact name exists and describes a soba restaurant in a century-old townhouse, but its profile states no location, so it could not be tied to this listing's area. Second pass: the restaurant's own account was found and its profile describes its hundred-year-old townhouse setting and its reservation-only course lunch, but it states no address or area, so it could not be placed in Ochiai.</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -10301,7 +10449,7 @@
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: savor_japan</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: savor_japan Second pass: no account was found under this shop's name in Koenji.</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -10776,23 +10924,39 @@
           <t>https://www.google.com/maps/place/%E8%B5%A4%E9%AC%BC/data=!4m2!3m1!1s0x6018f4992b2a2d07:0xd69b434e1331f004</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akaoni.sake.tokyo/</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>akaoni.sake.tokyo</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M161" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N161" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: oggi_mag</t>
+          <t>Second pass: the account's own profile gives the izakaya's address as Sangenjaya 2-15-3, Setagaya-ku with its weekday and weekend opening times and describes its sake-led menu, matching this listing; the Ikebukuro shop of the same name keeps a separate account.</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>https://oggi.jp/6040503</t>
+          <t>https://www.instagram.com/akaoni.sake.tokyo/</t>
         </is>
       </c>
       <c r="P161" t="inlineStr">
@@ -11249,7 +11413,7 @@
       </c>
       <c r="N168" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: 1973posy, tokyoweekender</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: 1973posy, tokyoweekender Second pass: no account was found for this venue in Setagaya; the handle printed for it on a media page could not be confirmed on any profile naming the venue.</t>
         </is>
       </c>
       <c r="O168" s="2" t="inlineStr">
@@ -11427,7 +11591,7 @@
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists but states no location, and its handle points to a different district, so it could not be tied to this listing.</t>
+          <t>An account of this name exists but states no location, and its handle points to a different district, so it could not be tied to this listing. Second pass: the only account carrying this name belongs to a yakitori shop in Kabukicho and gives no address, so it could not be tied to this listing in Yotsuya.</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -11630,23 +11794,39 @@
           <t>https://www.google.com/maps/place/DOLCE+TACUBO+%E4%BB%A3%E5%AE%98%E5%B1%B1/data=!4m2!3m1!1s0x60188b589a78a3bd:0x2c8434769002deea</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr"/>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dolce_tacubo/</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>dolce_tacubo</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M174" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N174" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: dolce_tacubo</t>
+          <t>Second pass: the account's own profile gives the shop's address as Ebisu-Nishi 2-15-9, ground floor of Cerazza Daikanyama, names it as the pastry shop of the Daikanyama restaurant Tacubo and gives its hours of 11:00 until sold out.</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>https://tabelog.com/tokyo/A1303/A130303/13266450/</t>
+          <t>https://www.instagram.com/dolce_tacubo/</t>
         </is>
       </c>
       <c r="P174" t="inlineStr">
@@ -13063,7 +13243,7 @@
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: inshokucom_journal</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: inshokucom_journal Second pass: no account was found under this bar's name in Suidobashi.</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr">
@@ -13203,7 +13383,7 @@
       </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
-          <t>An account exists for a shop of nearly this name written with a different kana, but it states no location, so it could not be tied to this listing.</t>
+          <t>An account exists for a shop of nearly this name written with a different kana, but it states no location, so it could not be tied to this listing. Second pass: no account was found for this shop in Edogawabashi; the name matches are a ramen shop in Fukaya, Saitama and a shop whose name is spelled differently.</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -13254,23 +13434,39 @@
           <t>https://www.google.com/maps/place/%E7%A5%9E%E7%94%B0%E3%81%BE%E3%81%A4%E3%82%84+%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x60188c034b047343:0xa95734bae35ddf5f</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kanda_matsuya/</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>kanda_matsuya</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N198" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: chiyoda_city_pr</t>
+          <t>Second pass: the account's own profile gives the restaurant's address as Kanda-Sudacho 1-13, Chiyoda-ku with its telephone number, its weekday and Saturday hours and its Sunday and Monday closing, matching this listing.</t>
         </is>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>https://visit-chiyoda.tokyo/app/spot/detail/359</t>
+          <t>https://www.instagram.com/kanda_matsuya/</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -13559,7 +13755,7 @@
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: sobadokoro_kameya</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: sobadokoro_kameya Second pass: no account was found for this branch; the handle printed for it on a directory page could not be confirmed on a profile naming the shop or its Kanda branch.</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
@@ -14466,23 +14662,39 @@
           <t>https://www.google.com/maps/place/%E6%9D%B1%E4%BA%AC%E5%9B%BD%E7%AB%8B%E5%8D%9A%E7%89%A9%E9%A4%A8/data=!4m2!3m1!1s0x60188e8314d77d11:0x232fd618bd4977dd</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tnm_pr/</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>tnm_pr</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M216" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N216" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The museum's site links only tnm_ir_en / tnm_ir_kr (language-specific information accounts); the main museum account is not linked from it. Candidates: tnm_ir_en, tnm_ir_kr</t>
+          <t>Second pass: this is the museum's own public-relations account, which presents its grounds, exhibitions and treasures; its English sibling account dates the museum to 1872 and names it the oldest museum of Asian art in Japan. The language-specific information accounts linked from the museum's site are separate.</t>
         </is>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>https://www.tnm.jp/modules/r_free_page/index.php?id=113&amp;lang=en</t>
+          <t>https://www.instagram.com/tnm_pr/</t>
         </is>
       </c>
       <c r="P216" t="inlineStr">
@@ -17071,7 +17283,7 @@
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists for an Italian restaurant and bar, but its profile gives no address; only its telephone exchange points to this area, which is not enough to tie it to this listing.</t>
+          <t>An account of this name exists for an Italian restaurant and bar, but its profile gives no address; only its telephone exchange points to this area, which is not enough to tie it to this listing. Second pass: the restaurant's own account was found and its profile describes its charcoal-grilled Italian cooking, hours and telephone number, whose 03-6420 exchange covers the Gotanda area, but the profile prints no address, so the area could not be confirmed from the profile itself.</t>
         </is>
       </c>
       <c r="O253" s="2" t="inlineStr">
@@ -17122,23 +17334,39 @@
           <t>https://www.google.com/maps/place/%E3%83%96%E3%83%AB%E3%83%BC%E3%82%B6%E3%82%B9%E3%83%AA%E3%83%BC+%E8%A1%A8%E5%8F%82%E9%81%93/data=!4m2!3m1!1s0x60188d457a3c6ce9:0x6771342dd1a8194a</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
-      <c r="J254" t="inlineStr"/>
-      <c r="K254" t="inlineStr"/>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bluethe3_omotesando/</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>bluethe3_omotesando</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M254" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N254" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bluethe3_omotesando</t>
+          <t>Second pass: the account's own name and profile place the venue in Omotesando, give its 65 seats with private rooms, terrace and counter and list its weekday and weekend hours, matching this listing.</t>
         </is>
       </c>
       <c r="O254" s="2" t="inlineStr">
         <is>
-          <t>https://www.timeout.jp/tokyo/ja/%E3%83%AC%E3%82%B9%E3%83%88%E3%83%A9%E3%83%B3/blue-the-three</t>
+          <t>https://www.instagram.com/bluethe3_omotesando/</t>
         </is>
       </c>
       <c r="P254" t="inlineStr">
@@ -17707,12 +17935,12 @@
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: musicbarbounce</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: musicbarbounce Second pass: the bar's own account was found and its profile gives its music policy, opening hours and charges, but it states no address or area, so it could not be placed in Shibuya.</t>
         </is>
       </c>
       <c r="O263" s="2" t="inlineStr">
         <is>
-          <t>https://www.timeout.com/tokyo/bars-and-pubs/music-bar-bounce</t>
+          <t>https://www.instagram.com/musicbarbounce/</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -17917,7 +18145,7 @@
       </c>
       <c r="N266" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Restaurant inside THE AOYAMA GRAND HOTEL. The hotel site links the hotel and two sibling restaurants, none of them this one. Candidates: aoyamagrand, theriveroriental, thetokyorestaurant</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Restaurant inside THE AOYAMA GRAND HOTEL. The hotel site links the hotel and two sibling restaurants, none of them this one. Candidates: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this restaurant's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this one's.</t>
         </is>
       </c>
       <c r="O266" s="2" t="inlineStr">
@@ -18271,7 +18499,7 @@
       </c>
       <c r="N271" s="4" t="inlineStr">
         <is>
-          <t>An account of this exact name exists but its profile states no location, so it could not be tied to this listing's area.</t>
+          <t>An account of this exact name exists but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this restaurant's name was found but its profile carries no address, hours or other detail, so it could not be placed in Mita or Tamachi.</t>
         </is>
       </c>
       <c r="O271" s="2" t="inlineStr">
@@ -19319,7 +19547,7 @@
       </c>
       <c r="N287" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: tablecheck_global</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: tablecheck_global Second pass: no account was found under this bar's name in Yoyogi-Hachiman.</t>
         </is>
       </c>
       <c r="O287" s="2" t="inlineStr">
@@ -19455,7 +19683,7 @@
       </c>
       <c r="N289" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists for a wine bar, but its profile states no location, so it could not be tied to this listing's area.</t>
+          <t>An account of this name exists for a wine bar, but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this venue's name was found and its profile describes a wine bar with simple snacks and gives its late hours, but it states no address or area, so it could not be placed in Yoyogi-Hachiman; a pub of the same name in Monzen-Nakacho keeps a separate account.</t>
         </is>
       </c>
       <c r="O289" s="2" t="inlineStr">
@@ -19595,7 +19823,7 @@
       </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: ittenbari_1</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: ittenbari_1 Second pass: no account of this restaurant's own was found; a Ningyocho izakaya's account names it among its sister shops, but that is not this restaurant's account and the handle printed for it on a directory page could not be confirmed.</t>
         </is>
       </c>
       <c r="O291" s="2" t="inlineStr">
@@ -19773,12 +20001,12 @@
       </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: nadoya.katte</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: nadoya.katte Second pass: the stand's own account was found and its profile describes it as a single-origin coffee stand produced by nadoya with coffee supervised by Glitch, and gives its hours, but neither it nor the parent account states an address, so it could not be placed in Yoyogi-Uehara.</t>
         </is>
       </c>
       <c r="O294" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/shop/oMcxtgqh9zINo2imrbyH</t>
+          <t>https://www.instagram.com/nadoya.katte/</t>
         </is>
       </c>
       <c r="P294" t="inlineStr">
@@ -20231,7 +20459,7 @@
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: i2.cafe</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: i2.cafe Second pass: no account was found under this cafe's name in Omotesando or Minami-Aoyama.</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -20347,7 +20575,7 @@
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists and names the operating company in its profile, but it has almost no content and states no location, so it could not be tied to this listing.</t>
+          <t>An account of this name exists and names the operating company in its profile, but it has almost no content and states no location, so it could not be tied to this listing. Second pass: no account was found for this restaurant in Aoyama; the name matches are unrelated businesses in Osaka, Arima, Hirakata and Taiwan.</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -20829,7 +21057,7 @@
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
-          <t>Two accounts present themselves as this shop's owner and neither states the shop's address; one notes that an earlier account naming this shop and area was taken over, so no account could be confirmed as the shop's.</t>
+          <t>Two accounts present themselves as this shop's owner and neither states the shop's address; one notes that an earlier account naming this shop and area was taken over, so no account could be confirmed as the shop's. Second pass: the two accounts carrying this shop's name both belong to its proprietor, and the newer one explains that the shop's earlier account was hijacked; neither is the shop's own account, so none is recorded.</t>
         </is>
       </c>
       <c r="O310" t="inlineStr"/>
@@ -21090,23 +21318,39 @@
           <t>https://www.google.com/maps/place/%E4%B8%AD%E8%8F%AF%E5%BE%B3%E5%A4%A7/data=!4m2!3m1!1s0x6018edf99f201ac5:0x8f8e4224d4035559</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
-      <c r="J314" t="inlineStr"/>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/chuka_tokudai/</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>chuka_tokudai</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M314" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N314" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: chuka_tokudai</t>
+          <t>Second pass: the account's own profile gives the restaurant's address as Ogikubo 5-13-6, Suginami-ku on the Suzuran-dori side of Ogikubo station, with its telephone number, its weekday and Saturday hours and its closing days, matching this listing.</t>
         </is>
       </c>
       <c r="O314" s="2" t="inlineStr">
         <is>
-          <t>https://retty.me/restaurant/100000145617/</t>
+          <t>https://www.instagram.com/chuka_tokudai/</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
@@ -21551,7 +21795,7 @@
       </c>
       <c r="N321" s="4" t="inlineStr">
         <is>
-          <t>An account named Restaurant Glover-tei exists, but its profile gives no address and nothing in it places the shop in Mitaka; a second account of the same name is a Nagasaki champon shop in Niigata, so neither could be established as this shop's.</t>
+          <t>An account named Restaurant Glover-tei exists, but its profile gives no address and nothing in it places the shop in Mitaka; a second account of the same name is a Nagasaki champon shop in Niigata, so neither could be established as this shop's. Second pass: the restaurant's own account was searched again with the city name; its profile still gives no address and nothing places the shop in Mitaka, so it is not recorded.</t>
         </is>
       </c>
       <c r="O321" s="2" t="inlineStr">
@@ -21671,7 +21915,7 @@
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
-          <t>An account named Chuka Juhachiban exists and matches the name and category, but its profile gives only opening hours and no location, so it could not be tied to the Nogata shop; the other name matches are in Chuo-ku, Osaka and Wakayama.</t>
+          <t>An account named Chuka Juhachiban exists and matches the name and category, but its profile gives only opening hours and no location, so it could not be tied to the Nogata shop; the other name matches are in Chuo-ku, Osaka and Wakayama. Second pass: the account carrying this shop's name gives its menu, hours and a large car park in its profile but no address, and the profile's car park does not match a Nogata shopfront, so it is not recorded.</t>
         </is>
       </c>
       <c r="O323" s="2" t="inlineStr">
@@ -21912,23 +22156,39 @@
           <t>https://www.google.com/maps/place/%E3%82%A2%E3%83%AB%E3%83%87%E3%83%90%E3%83%A9%E3%83%B3/data=!4m2!3m1!1s0x60188bc94e7e0b17:0xefee4d3e47e50960</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
-      <c r="J327" t="inlineStr"/>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aldebaran_burger/</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>aldebaran_burger</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M327" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N327" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: aldebaran_burger</t>
+          <t>Second pass: the shop's own account states that it reopened in Azabu-Juban on 8 November, and the chef's account dates the Roppongi shop from 2018 to 2022 and the Azabu-Juban restart to 8 November 2022, placing the shop where this listing places it.</t>
         </is>
       </c>
       <c r="O327" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/shop/l02XuMB9ohfc2eiVcxhG</t>
+          <t>https://www.instagram.com/aldebaran_burger/</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
@@ -22078,23 +22338,39 @@
           <t>https://www.google.com/maps/place/Burger%20POLICE/data=!4m2!3m1!1s0x6018f53df314ef2b:0xe30804dd54fe68d</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
-      <c r="J330" t="inlineStr"/>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/burgerpolice_himonya/</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>burgerpolice_himonya</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M330" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N330" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Branch accounts linked are Kasukabe, Himonya and Shibuya; none names Toritsu-Daigaku, and guessing the nearest is not evidence. Candidates: burgerpolice_fckasukabe, burgerpolice_himonya, burgerpolice_shibuya</t>
+          <t>Second pass: the account's own name identifies the Himonya shop - the neighbourhood that Toritsu-Daigaku station stands in, where this guide places it - and its profile gives its burger-bistro format, its weekday and weekend hours and its Wednesday closing. The chain's Kasukabe and Shibuya shops keep separate accounts.</t>
         </is>
       </c>
       <c r="O330" s="2" t="inlineStr">
         <is>
-          <t>https://burgerpolice.jp/</t>
+          <t>https://www.instagram.com/burgerpolice_himonya/</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
@@ -22136,23 +22412,39 @@
           <t>https://www.google.com/maps/place/THE%20GREAT%20BURGER/data=!4m2!3m1!1s0x60188ca428c01717:0x6d9cff4312428fd5</t>
         </is>
       </c>
-      <c r="I331" t="inlineStr"/>
-      <c r="J331" t="inlineStr"/>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/the_great_burger/</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>the_great_burger</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M331" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N331" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Accounts reached belong to other businesses; none corresponds to this restaurant. Seen: atsushi_kurumata, jenniferseven_burgershop, jenniferseven_generalstore, lenoxhouse_sangubashi, lucky_alex_matsumizaka, the_great_burger, the_great_burger_stand, thelittlebakerytokyo, theteisyokushop, youknowwhat_yoyogiuehara</t>
+          <t>Second pass: this is the restaurant's main account, which names its sibling stand and gives its weekday and weekend hours; both profiles are placed in Shibuya-ku, the ward that contains Jingumae where this listing places it, though neither prints the street address.</t>
         </is>
       </c>
       <c r="O331" s="2" t="inlineStr">
         <is>
-          <t>http://www.the-great-burger.com/</t>
+          <t>https://www.instagram.com/the_great_burger/</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
@@ -22205,7 +22497,7 @@
       </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
-          <t>The chain keeps separate branch accounts (Hokkaido, Okinawa and Miyakojima among them) but no account for the Shinjuku branch was found, and the brand-level account's profile gives no location, so none could be tied to this branch.</t>
+          <t>The chain keeps separate branch accounts (Hokkaido, Okinawa and Miyakojima among them) but no account for the Shinjuku branch was found, and the brand-level account's profile gives no location, so none could be tied to this branch. Second pass: the chain's own accounts name a brand-level account and separate regional accounts for Hokkaido, Okinawa, Miyakojima and Vietnam, but none of them is placed in Shinjuku, so none could be tied to this branch.</t>
         </is>
       </c>
       <c r="O332" t="inlineStr"/>
@@ -22524,21 +22816,41 @@
           <t>https://www.google.com/maps/place/%E3%83%93%E3%83%95%E3%83%86%E3%82%AD%E3%81%AE%E3%82%AB%E3%83%AF%E3%83%A0%E3%83%A9%20%E9%8A%80%E5%BA%A7/data=!4m2!3m1!1s0x60188bef5a1f5e75:0xdf0184296a58fcb6</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
-      <c r="J337" t="inlineStr"/>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bifuteki_kawamura_tokyo/</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>bifuteki_kawamura_tokyo</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M337" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N337" s="4" t="inlineStr">
         <is>
-          <t>Several accounts of this steakhouse exist and two of them name the Ginza and Roppongi branches together in one profile; no account specific to the Ginza branch was found, so none is recorded.</t>
-        </is>
-      </c>
-      <c r="O337" t="inlineStr"/>
+          <t>Second pass: the chain's own Kansai account states in its profile that its Tokyo Ginza and Roppongi restaurants are covered by this account, and the brand account dates the firm to 1972 and lists the Ginza and Roppongi shops. It is shared between those two shops, so it is recorded as the operator's account.</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bifuteki_kawamura_tokyo/</t>
+        </is>
+      </c>
       <c r="P337" t="inlineStr">
         <is>
           <t>2026-10-29</t>
@@ -22993,7 +23305,7 @@
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
-          <t>An account carrying this restaurant's name and its proprietor's name exists and its profile gives opening hours and the Tuesday-Wednesday closing, but no address or area, so it could not be tied to the Shikahama shop.</t>
+          <t>An account carrying this restaurant's name and its proprietor's name exists and its profile gives opening hours and the Tuesday-Wednesday closing, but no address or area, so it could not be tied to the Shikahama shop. Second pass: searched again with the neighbourhood name; the account carrying this restaurant's and its proprietor's name still gives only its hours and closing days, with no address, so it could not be placed in Shikahama.</t>
         </is>
       </c>
       <c r="O344" s="2" t="inlineStr">
@@ -23051,7 +23363,7 @@
       </c>
       <c r="N345" s="4" t="inlineStr">
         <is>
-          <t>The brand's account exists but its profile places the restaurant at Azabudai Hills, not Ebisu where this listing places it, so it was not recorded; the sibling accounts are the Kanda and Taipei restaurants.</t>
+          <t>The brand's account exists but its profile places the restaurant at Azabudai Hills, not Ebisu where this listing places it, so it was not recorded; the sibling accounts are the Kanda and Taipei restaurants. Second pass: searched again with the neighbourhood and the brand's other name; the account still places the restaurant at Azabudai Hills rather than Ebisu, so it was not recorded.</t>
         </is>
       </c>
       <c r="O345" s="2" t="inlineStr">
@@ -23109,7 +23421,7 @@
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: profite_sincerite</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: profite_sincerite Second pass: no account was found under this shop's name in Soshigaya-Okura.</t>
         </is>
       </c>
       <c r="O346" s="2" t="inlineStr">
@@ -23156,23 +23468,39 @@
           <t>https://www.google.com/maps/place/%E3%83%96%E3%83%BC%E3%83%A9%E3%83%B3%E3%82%B8%E3%82%A7%E3%83%AA%E3%83%BC%20%E3%82%B9%E3%83%89%E3%82%A6/data=!4m2!3m1!1s0x6018f37e87a9a139:0x844b061e70b15516</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
-      <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
-      <c r="M347" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boulangerie.sudo/</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>boulangerie.sudo</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M347" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N347" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: boulangerie.sudo, sakedeshi_cat</t>
+          <t>Second pass: the account's own profile gives the bakery's address as Setagaya 4-chome, Setagaya-ku, directly in front of Shoin-Jinjamae station on the Setagaya line, with its telephone number and its Friday-to-Sunday opening, matching this listing.</t>
         </is>
       </c>
       <c r="O347" s="2" t="inlineStr">
         <is>
-          <t>https://tabelog.com/tokyo/A1317/A131709/13098861/</t>
+          <t>https://www.instagram.com/boulangerie.sudo/</t>
         </is>
       </c>
       <c r="P347" t="inlineStr">
@@ -23268,23 +23596,39 @@
           <t>https://www.google.com/maps/place/%E3%82%BB%E3%83%B3%E3%83%88%E3%83%AB%20%E3%82%B6%E3%83%BB%E3%83%99%E3%83%BC%E3%82%AB%E3%83%AA%E3%83%BC/data=!4m2!3m1!1s0x60188be494b4c413:0x7217f50ecd1d80f3</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
-      <c r="M349" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/centre_the_bakery/</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>centre_the_bakery</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M349" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N349" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: centre_the_bakery</t>
+          <t>Second pass: the account's own name identifies the Ginza shop and its profile gives the address as Ginza 1-2-1, Chuo-ku, ground floor of the Tokyo Expressway Konya building, with its telephone number and its bread-selling hours.</t>
         </is>
       </c>
       <c r="O349" s="2" t="inlineStr">
         <is>
-          <t>https://retty.me/restaurant/100000843513/</t>
+          <t>https://www.instagram.com/centre_the_bakery/</t>
         </is>
       </c>
       <c r="P349" t="inlineStr">
@@ -23400,23 +23744,39 @@
           <t>https://www.google.com/maps/place/%E3%81%97%E3%81%8B%E3%81%9F%E3%82%89%E3%82%80%E3%81%8B%E3%81%AA/data=!4m2!3m1!1s0x601889a8024ae8c5:0x2d138471fc8fcc82</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr"/>
-      <c r="J351" t="inlineStr"/>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
-      <c r="M351" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/3ft.nakamura.official/</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>3ft.nakamura.official</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M351" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N351" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: 3ft.nacamera.official</t>
+          <t>Second pass: the account's own profile traces the shop from Wakayama through Kiyosumi to its present Kagurazaka shop, where this listing places it, and gives its reservation and walk-in selling hours, its Tuesday-Wednesday closing and its cashless-only payment.</t>
         </is>
       </c>
       <c r="O351" s="2" t="inlineStr">
         <is>
-          <t>https://www.timeout.jp/tokyo/ja/ショッピング/shikatanakamjra</t>
+          <t>https://www.instagram.com/3ft.nakamura.official/</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -23799,7 +24159,7 @@
       </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
-          <t>The bakery's brand account exists and gives its hours, but neither it nor the sibling coffee account states any location, so the account could not be placed in Roppongi.</t>
+          <t>The bakery's brand account exists and gives its hours, but neither it nor the sibling coffee account states any location, so the account could not be placed in Roppongi. Second pass: searched again with the neighbourhood names; neither the bakery's account nor its sibling coffee account prints an address, so the shop could not be placed in Roppongi.</t>
         </is>
       </c>
       <c r="O357" s="2" t="inlineStr">
@@ -23928,23 +24288,39 @@
           <t>https://www.google.com/maps/place/BIANCHI/data=!4m2!3m1!1s0x60188b38c0b41d1b:0x71d504f42e5a2d7d</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
-      <c r="J359" t="inlineStr"/>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
-      <c r="M359" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bianchi_roppongi/</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>bianchi_roppongi</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M359" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N359" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bianchi_roppongi</t>
+          <t>Second pass: the account's own handle names the Roppongi restaurant and its profile describes its Thai-Chinese and Thai street-food menu reworked with Japanese ingredients, with its lunch and dinner hours and Sunday closing, matching this listing.</t>
         </is>
       </c>
       <c r="O359" s="2" t="inlineStr">
         <is>
-          <t>https://www.timeout.jp/tokyo/ja/レストラン/bianchi_roppongi</t>
+          <t>https://www.instagram.com/bianchi_roppongi/</t>
         </is>
       </c>
       <c r="P359" t="inlineStr">
@@ -24079,7 +24455,7 @@
       </c>
       <c r="N361" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banthai_shinjyuku</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banthai_shinjyuku Second pass: no account was found under this restaurant's name in Shinjuku; the name match is a Thai restaurant in Joetsu, Niigata.</t>
         </is>
       </c>
       <c r="O361" s="2" t="inlineStr">
@@ -24141,12 +24517,12 @@
       </c>
       <c r="N362" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: hotatebiyori</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: hotatebiyori Second pass: the shop's own account was found and its profile describes its Sarufutsu scallops and Hokkaido wheat noodles, but it states no address or area, so it could not be placed in Akihabara.</t>
         </is>
       </c>
       <c r="O362" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/en/shop/IzggFE6SJ9U1fIuggVO6</t>
+          <t>https://www.instagram.com/hotatebiyori/</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -24386,23 +24762,39 @@
           <t>https://www.google.com/maps/place/%E4%B8%AD%E8%8F%AF%E8%95%8E%E9%BA%A6%20%E3%81%B2%E3%82%89%E4%BA%95/data=!4m2!3m1!1s0x6018e51f5f871375:0x5864b05e0f5774f6</t>
         </is>
       </c>
-      <c r="I366" t="inlineStr"/>
-      <c r="J366" t="inlineStr"/>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
-      <c r="M366" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tyukasoba_hirai/</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>tyukasoba_hirai</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M366" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N366" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: men_channel00</t>
+          <t>Second pass: the account's own profile gives the shop's address as Sakaecho 2-11-7, Fuchu, Tokyo with its hours, Tuesday closing and ticket-machine ordering, matching this listing; the Tamaplaza branch keeps a separate account.</t>
         </is>
       </c>
       <c r="O366" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/area/tokyo/fuchu/list/ramen</t>
+          <t>https://www.instagram.com/tyukasoba_hirai/</t>
         </is>
       </c>
       <c r="P366" t="inlineStr">
@@ -24633,12 +25025,12 @@
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: medikasoba.kin_gyo</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: medikasoba.kin_gyo Second pass: the shop's own account was found and its profile gives its hours and its two soup styles, but it states no address or area, so it could not be placed in Manganji.</t>
         </is>
       </c>
       <c r="O370" s="2" t="inlineStr">
         <is>
-          <t>https://retty.me/restaurant/100001646249/</t>
+          <t>https://www.instagram.com/medikasoba.kin_gyo/</t>
         </is>
       </c>
       <c r="P370" t="inlineStr">
@@ -24695,7 +25087,7 @@
       </c>
       <c r="N371" s="4" t="inlineStr">
         <is>
-          <t>An account with this shop's exact and distinctive name exists and its profile gives the opening days and hours, but it states no address or area, so it could not be placed in Higashi-Ogu.</t>
+          <t>An account with this shop's exact and distinctive name exists and its profile gives the opening days and hours, but it states no address or area, so it could not be placed in Higashi-Ogu. Second pass: searched again with the ward name; the shop's own account still gives only its opening days and hours, with no address, so it could not be placed in Higashi-Ogu.</t>
         </is>
       </c>
       <c r="O371" s="2" t="inlineStr">
@@ -24931,7 +25323,7 @@
       </c>
       <c r="N375" s="4" t="inlineStr">
         <is>
-          <t>An account with this shop's exact name exists and its profile describes its own noodles and use of no chemical seasonings, but it states no address or area, so it could not be placed in Kameido.</t>
+          <t>An account with this shop's exact name exists and its profile describes its own noodles and use of no chemical seasonings, but it states no address or area, so it could not be placed in Kameido. Second pass: searched again with the ward name; the shop's own account still gives only its own-noodle and no-additive claims, with no address, so it could not be placed in Kameido.</t>
         </is>
       </c>
       <c r="O375" s="2" t="inlineStr">
@@ -25163,7 +25555,7 @@
       </c>
       <c r="N379" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: codies.burger</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: codies.burger Second pass: no account was found under this shop's name in Yokohama; the name match is a restaurant in Queensland, Australia.</t>
         </is>
       </c>
       <c r="O379" s="2" t="inlineStr">
@@ -25214,23 +25606,39 @@
           <t>https://www.google.com/maps/place/%E3%81%8F%E3%82%8A%E5%B1%B1/data=!4m2!3m1!1s0x60185ea47fa2565d:0xf3c5001ca3edaa5</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr"/>
-      <c r="J380" t="inlineStr"/>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
-      <c r="M380" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kuriyama2022/</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>kuriyama2022</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M380" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N380" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kuriyama2022</t>
+          <t>Second pass: the account's own profile places the shop five minutes' walk from Hakuraku station on the Tokyu Toyoko line, where this listing places it, and gives its weekday and weekend hours.</t>
         </is>
       </c>
       <c r="O380" s="2" t="inlineStr">
         <is>
-          <t>https://retty.me/restaurant/100000008489/</t>
+          <t>https://www.instagram.com/kuriyama2022/</t>
         </is>
       </c>
       <c r="P380" t="inlineStr">
@@ -26342,23 +26750,39 @@
           <t>https://www.google.com/maps/place/%E4%B8%89%E5%8D%81%E4%B8%89%E9%96%93%E5%A0%82/data=!4m2!3m1!1s0x600108ca8f9b80b3:0xaa2b01ebdb651688</t>
         </is>
       </c>
-      <c r="I396" t="inlineStr"/>
-      <c r="J396" t="inlineStr"/>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
-      <c r="M396" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sanjusangendo_temple/</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>sanjusangendo_temple</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M396" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N396" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yokka_life</t>
+          <t>Second pass: the temple's own account, which states in its profile that it is the official Instagram of Sanjusangendo in Kyoto, and its location record gives Sanjusangendo-mawari-cho 657 in Higashiyama-ku, where this listing places it.</t>
         </is>
       </c>
       <c r="O396" s="2" t="inlineStr">
         <is>
-          <t>https://www.veltra.com/jp/yokka/article/sanjusangen-do/</t>
+          <t>https://www.instagram.com/sanjusangendo_temple/</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -26404,23 +26828,39 @@
           <t>https://www.google.com/maps/place/%E8%A5%BF%E6%9C%AC%E9%A1%98%E5%AF%BA%EF%BC%88%E9%BE%8D%E8%B0%B7%E5%B1%B1%E6%9C%AC%E9%A1%98%E5%AF%BA%EF%BC%89/data=!4m2!3m1!1s0x600108a75314e2a3:0xf4e42caa95cddc94</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
-      <c r="J397" t="inlineStr"/>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nishi_hongwanji/</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>nishi_hongwanji</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M397" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N397" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The temple's site links two accounts (nishi.hongwanji / nishi_hongwanji) without saying which is current. Candidates: nishi.hongwanji, nishi_hongwanji</t>
+          <t>Second pass: of the two accounts, this is the temple's own - its profile names it as Onishi-san, the temple itself, and states that it also runs the temple's official website, X and note accounts - while the other belongs to the Jodo Shinshu Honganji-ha denomination and posts its teachings and observances.</t>
         </is>
       </c>
       <c r="O397" s="2" t="inlineStr">
         <is>
-          <t>https://www.hongwanji.kyoto/</t>
+          <t>https://www.instagram.com/nishi_hongwanji/</t>
         </is>
       </c>
       <c r="P397" t="inlineStr">
@@ -26769,12 +27209,12 @@
       </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: roujina0627</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: roujina0627 Second pass: the restaurant's own account was found and its profile gives its lunch and dinner last orders, its Monday closing and its lack of parking, but it states no address or area, so it could not be placed in Nakagyo-ku.</t>
         </is>
       </c>
       <c r="O402" s="2" t="inlineStr">
         <is>
-          <t>https://www.mec-h.com/town/mh-kyoto/79</t>
+          <t>https://www.instagram.com/roujina0627/</t>
         </is>
       </c>
       <c r="P402" t="inlineStr">
@@ -26831,7 +27271,7 @@
       </c>
       <c r="N403" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: warakumagazine</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: warakumagazine Second pass: no account was found under this restaurant's name in Nakagyo-ku; the nearest name match is a Chinese restaurant with no stated address.</t>
         </is>
       </c>
       <c r="O403" s="2" t="inlineStr">
@@ -27549,7 +27989,7 @@
       </c>
       <c r="N414" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banana_for_human_by_gorilla, berry._.button, hyde_and_away, kissa_me8, mimaruhotels, panelcafe_kyoto</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banana_for_human_by_gorilla, berry._.button, hyde_and_away, kissa_me8, mimaruhotels, panelcafe_kyoto Second pass: no account was found under this shop's name in Gion; the results were other Gion sweets shops.</t>
         </is>
       </c>
       <c r="O414" s="2" t="inlineStr">
@@ -27814,23 +28254,39 @@
           <t>https://www.google.com/maps/place/%E4%BA%AC%E9%83%BD%E4%BB%99%E6%B4%9E%E5%BE%A1%E6%89%80/data=!4m2!3m1!1s0x600108652e05500d:0xbb9ad3d40026f822</t>
         </is>
       </c>
-      <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
-      <c r="M418" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imperial_palaces_of_kyoto/</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>imperial_palaces_of_kyoto</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M418" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N418" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: fun_japan_travel</t>
+          <t>Second pass: this is the official account of the Imperial Household Agency's Kyoto office, and its profile states that it covers the Kyoto Imperial Palace, this Sento Imperial Palace, Katsura and Shugakuin, with their buildings, gardens and special openings. It is shared across those sites, so it is recorded as the operator's account.</t>
         </is>
       </c>
       <c r="O418" s="2" t="inlineStr">
         <is>
-          <t>https://www.fun-japan.jp/tw/articles/8713</t>
+          <t>https://www.instagram.com/imperial_palaces_of_kyoto/</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -27876,23 +28332,39 @@
           <t>https://www.google.com/maps/place/%E4%BF%AE%E5%AD%A6%E9%99%A2%E9%9B%A2%E5%AE%AE/data=!4m2!3m1!1s0x600109c7d7660d4d:0x729e62296b00aae2</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
-      <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
-      <c r="M419" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imperial_palaces_of_kyoto/</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>imperial_palaces_of_kyoto</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M419" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N419" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: keihan_biostyle, keihan_railway, tenhachi_bu, watashimo_okeihan</t>
+          <t>Second pass: this is the official account of the Imperial Household Agency's Kyoto office, and its profile states that it covers the Kyoto Imperial Palace, the Sento Imperial Palace, Katsura and this Shugakuin villa, with their buildings, gardens and special openings. It is shared across those sites, so it is recorded as the operator's account.</t>
         </is>
       </c>
       <c r="O419" s="2" t="inlineStr">
         <is>
-          <t>https://www.keihan.co.jp/kanei/spot/life.php</t>
+          <t>https://www.instagram.com/imperial_palaces_of_kyoto/</t>
         </is>
       </c>
       <c r="P419" t="inlineStr">
@@ -28027,7 +28499,7 @@
       </c>
       <c r="N421" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yamamoto_kissa</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yamamoto_kissa Second pass: no account was found under this cafe's name in Higashiyama-ku; the nearest name match is a liquor shop near Sanjo.</t>
         </is>
       </c>
       <c r="O421" s="2" t="inlineStr">
@@ -28571,7 +29043,7 @@
       </c>
       <c r="N429" s="4" t="inlineStr">
         <is>
-          <t>The only account tying this name to Kyoto is the proprietor's personal account, whose profile describes him as the owner of Yakiniku Yamachan in Kyoto and a wine sommelier; it is a personal account, not the restaurant's own, and gives no address, so it is not recorded.</t>
+          <t>The only account tying this name to Kyoto is the proprietor's personal account, whose profile describes him as the owner of Yakiniku Yamachan in Kyoto and a wine sommelier; it is a personal account, not the restaurant's own, and gives no address, so it is not recorded. Second pass: searched again with the ward name; the only account tying this name to Kyoto remains the proprietor's personal account, which gives no address, and the other name match is a restaurant in Ogaki, Gifu.</t>
         </is>
       </c>
       <c r="O429" s="2" t="inlineStr">
@@ -28622,23 +29094,39 @@
           <t>https://www.google.com/maps/place/MOT/data=!4m2!3m1!1s0x6001099a14cac049:0x5b513b5d35eb8893</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
-      <c r="J430" t="inlineStr"/>
-      <c r="K430" t="inlineStr"/>
-      <c r="L430" t="inlineStr"/>
-      <c r="M430" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mot_kyoto/</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>mot_kyoto</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M430" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N430" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: leaf_kyoto, tom.kyoto</t>
+          <t>Second pass: the account's own profile names the restaurant as a Thai restaurant in Kyoto and the flagship of its sibling Mymot, which this guide also lists in Meguro; the profile names the city but not the Kuramaguchi neighbourhood.</t>
         </is>
       </c>
       <c r="O430" s="2" t="inlineStr">
         <is>
-          <t>https://www.leafkyoto.net/en/store/240508-kyoto-tom</t>
+          <t>https://www.instagram.com/mot_kyoto/</t>
         </is>
       </c>
       <c r="P430" t="inlineStr">
@@ -28762,23 +29250,39 @@
           <t>https://www.google.com/maps/place/%E9%80%9A%E5%A4%A9%E9%96%A3/data=!4m2!3m1!1s0x6000e76077e042ff:0xe5cbcf56def44557</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr"/>
-      <c r="J432" t="inlineStr"/>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
-      <c r="M432" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tsutenkakutower_official/</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>tsutenkakutower_official</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M432" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N432" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The tower's site links two accounts (tsutenkaku_official / tsutenkakutower_official) without distinguishing them. Candidates: tsutenkaku_official, tsutenkakutower_official</t>
+          <t>Second pass: of the tower's two accounts this is the current official one - the older account's profile points visitors to it by name - and its profile gives the tower's opening hours and last admission.</t>
         </is>
       </c>
       <c r="O432" s="2" t="inlineStr">
         <is>
-          <t>https://www.tsutenkaku.co.jp/</t>
+          <t>https://www.instagram.com/tsutenkakutower_official/</t>
         </is>
       </c>
       <c r="P432" t="inlineStr">
@@ -28824,23 +29328,39 @@
           <t>https://www.google.com/maps/place/%E5%A4%A7%E9%98%AA%E5%9F%8E/data=!4m2!3m1!1s0x6000e0cd5c283afd:0xf01d07d5ca11e41</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
-      <c r="J433" t="inlineStr"/>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
-      <c r="M433" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/osaka_castle_park/</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>osaka_castle_park</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M433" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N433" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Two park accounts were reached (osaka_castle_park / osakacastlepark.odekake) and the page does not say which is official. Seen: osaka_castle_park, osakacastlepark.odekake</t>
+          <t>Second pass: this is the castle park's own official account, posting its events, seasonal flowers and history; the other account found earlier is an outing guide, not the park's. It covers the whole park around the castle, so it is recorded as the operator's account.</t>
         </is>
       </c>
       <c r="O433" s="2" t="inlineStr">
         <is>
-          <t>https://www.osakacastlepark.jp/</t>
+          <t>https://www.instagram.com/osaka_castle_park/</t>
         </is>
       </c>
       <c r="P433" t="inlineStr">
@@ -28975,7 +29495,7 @@
       </c>
       <c r="N435" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: timeoutosaka_jp</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: timeoutosaka_jp Second pass: the sign has no account of its own; the confectionery company that owns it runs product and shop accounts, and the Dotonbori traders' association account covers the whole street, so none is recorded.</t>
         </is>
       </c>
       <c r="O435" s="2" t="inlineStr">
@@ -29037,7 +29557,7 @@
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the arcade were reached, not the arcade's own. Seen: tenjinbashi.ohagurumakou, tenjinbashi3choume</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the arcade were reached, not the arcade's own. Seen: tenjinbashi.ohagurumakou, tenjinbashi3choume Second pass: the arcade as a whole keeps no account; the only official account found belongs to its fourth block alone, so it was not recorded for this listing.</t>
         </is>
       </c>
       <c r="O436" s="2" t="inlineStr">
@@ -29302,23 +29822,39 @@
           <t>https://www.google.com/maps/place/%E6%9C%AC%E5%AE%B6%E5%A4%A7%E3%81%9F%E3%81%93+%E9%81%93%E9%A0%93%E5%A0%80%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x6000e76532907553:0xb7a684d33dc9ceb2</t>
         </is>
       </c>
-      <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr"/>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
-      <c r="M440" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ootakodoutonbori/</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>ootakodoutonbori</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M440" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N440" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: eeyan_shotengai</t>
+          <t>Second pass: the account's own name identifies the Dotonbori main shop where this listing places it, and its profile gives its founding in 1972 and its octopus, kushikatsu, okonomiyaki and yakisoba menu.</t>
         </is>
       </c>
       <c r="O440" s="2" t="inlineStr">
         <is>
-          <t>https://osaka-shotengai-info.com/shop/honke-otako-dotonbori/</t>
+          <t>https://www.instagram.com/ootakodoutonbori/</t>
         </is>
       </c>
       <c r="P440" t="inlineStr">
@@ -29491,7 +30027,7 @@
       </c>
       <c r="N443" s="4" t="inlineStr">
         <is>
-          <t>An account carrying this name as Sousaku Teppan Miraku exists and gives its lunch and dinner hours, but it states no address, so it could not be placed in Kita-ku; the other name match is in Yuzawa, Akita.</t>
+          <t>An account carrying this name as Sousaku Teppan Miraku exists and gives its lunch and dinner hours, but it states no address, so it could not be placed in Kita-ku; the other name match is in Yuzawa, Akita. Second pass: searched again by the fuller shop name; no account was found that places a restaurant of this name in Kita-ku, Osaka.</t>
         </is>
       </c>
       <c r="O443" s="2" t="inlineStr">
@@ -29999,7 +30535,7 @@
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
-          <t>The restaurant's own account exists and gives its telephone number, whose 06-6458 exchange covers the Fukushima area, but the profile prints no address, so the area could not be confirmed from the profile itself.</t>
+          <t>The restaurant's own account exists and gives its telephone number, whose 06-6458 exchange covers the Fukushima area, but the profile prints no address, so the area could not be confirmed from the profile itself. Second pass: searched again with the ward name; the restaurant's own account still gives only its booking telephone number and website, with no address, so the Fukushima-ku location could not be confirmed from the profile.</t>
         </is>
       </c>
       <c r="O451" s="2" t="inlineStr">
@@ -30139,7 +30675,7 @@
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
-          <t>The restaurant keeps an account for its Hanshin Umeda shop in Kita-ku, but no account was found for the Kitahorie main shop and no brand-level account exists, so none could be tied to this listing.</t>
+          <t>The restaurant keeps an account for its Hanshin Umeda shop in Kita-ku, but no account was found for the Kitahorie main shop and no brand-level account exists, so none could be tied to this listing. Second pass: the only account for this restaurant places it in the basement of the Hanshin Umeda store in Kita-ku, with a sibling shop on the floor below, and not in Kitahorie where this listing places it.</t>
         </is>
       </c>
       <c r="O453" t="inlineStr"/>
@@ -30186,23 +30722,39 @@
           <t>https://www.google.com/maps/place/%E3%82%AB%E3%83%89%E3%83%A4%E9%A3%9F%E5%A0%82%20%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x6000e654b4c6e1a1:0x4172414807ba515b</t>
         </is>
       </c>
-      <c r="I454" t="inlineStr"/>
-      <c r="J454" t="inlineStr"/>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
-      <c r="M454" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kadoya.shokudou/</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>kadoya.shokudou</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M454" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N454" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kadoya.shokudou</t>
+          <t>Second pass: the restaurant's own official account; its profile lists its shops as the main shop - this listing - together with the Hanshin Umeda, Crysta Nagahori and Nishi-Umeda branches. It is shared across them, so it is recorded as the operator's account.</t>
         </is>
       </c>
       <c r="O454" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/en/shop/0GBEQmgsUccte3kG0TIz</t>
+          <t>https://www.instagram.com/kadoya.shokudou/</t>
         </is>
       </c>
       <c r="P454" t="inlineStr">
@@ -30536,23 +31088,39 @@
           <t>https://www.google.com/maps/place/R-S/data=!4m2!3m1!1s0x6018835b1fa5a1bf:0x7c69d9687d4bb5b2</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr"/>
-      <c r="J459" t="inlineStr"/>
-      <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
-      <c r="M459" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rs.burger/</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>rs.burger</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M459" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N459" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: rs.burger</t>
+          <t>Second pass: the account's own profile gives the shop's address as Koganehara 6-2-6, Matsudo, Chiba with its telephone number, and its takeaway counter keeps a separate account naming this one as its parent.</t>
         </is>
       </c>
       <c r="O459" s="2" t="inlineStr">
         <is>
-          <t>https://retty.me/restaurant/100000041162/</t>
+          <t>https://www.instagram.com/rs.burger/</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -30765,7 +31333,7 @@
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
-          <t>The only account carrying this shop's name is the proprietor Osamu Tomita's own account; it is a personal account rather than the shop's and gives no address, so it is not recorded.</t>
+          <t>The only account carrying this shop's name is the proprietor Osamu Tomita's own account; it is a personal account rather than the shop's and gives no address, so it is not recorded. Second pass: searched again for a shop account; none exists - only the proprietor's own account and a ramen writer's page that lists the shop among his recommendations.</t>
         </is>
       </c>
       <c r="O462" s="2" t="inlineStr">
@@ -30823,7 +31391,7 @@
       </c>
       <c r="N463" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: briskstand, briskstand_asakusa</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: briskstand, briskstand_asakusa Second pass: the chain keeps accounts for its Matsusaka, Sapporo, Sakai, Okazaki, Kyoto, Ebisu, Omotesando, Himeji, Tokushima and Kabukicho shops, and those profiles refer to the Kobe main shop's reputation, but no account for the Kobe main shop itself was found.</t>
         </is>
       </c>
       <c r="O463" s="2" t="inlineStr">
@@ -31121,7 +31689,7 @@
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
-          <t>The restaurant's own account exists but its profile lists only its Kashii branches, with no Chiyo branch, so no account could be tied to this listing.</t>
+          <t>The restaurant's own account exists but its profile lists only its Kashii branches, with no Chiyo branch, so no account could be tied to this listing. Second pass: searched again with the ward name; the restaurant's own account still lists only its Kashii-area branches, and the sibling account gives no address, so neither could be tied to the Chiyo branch.</t>
         </is>
       </c>
       <c r="O468" s="2" t="inlineStr">
@@ -31345,7 +31913,7 @@
       </c>
       <c r="N472" s="4" t="inlineStr">
         <is>
-          <t>The chain keeps branch accounts for Mizonokuchi and Obihiro, and the Mizonokuchi profile names itself an offshoot of the Otaru main shop, but no account for the Otaru main shop itself was found.</t>
+          <t>The chain keeps branch accounts for Mizonokuchi and Obihiro, and the Mizonokuchi profile names itself an offshoot of the Otaru main shop, but no account for the Otaru main shop itself was found. Second pass: the Mizonokuchi branch's account names itself an offshoot of the Otaru main shop and gives only its own address, and no account for the Otaru main shop was found.</t>
         </is>
       </c>
       <c r="O472" t="inlineStr"/>
@@ -31570,23 +32138,39 @@
           <t>https://www.google.com/maps/place/%E4%BC%8A%E5%8B%A2%E9%AE%A8/data=!4m2!3m1!1s0x5f0ae1ad820b2659:0x40ae172fcc2430ff</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
-      <c r="J476" t="inlineStr"/>
-      <c r="K476" t="inlineStr"/>
-      <c r="L476" t="inlineStr"/>
-      <c r="M476" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ise_zushi/</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>ise_zushi</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M476" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N476" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Linked accounts are the station branch and a separate standing-sushi shop; no account for this shop is identifiable. Candidates: edakan1005, isezushi_ekinakaten, tachigui_sushi_koise_shoten</t>
+          <t>Second pass: the account's own profile dates the shop to 1967, describes its Edo-mae and Ezo-mae work and gives a telephone number in the 0134 Otaru dialling area; the station branch keeps its own separate account, leaving this one as the main shop's. The profile gives the telephone number rather than a street address.</t>
         </is>
       </c>
       <c r="O476" s="2" t="inlineStr">
         <is>
-          <t>https://www.isezushi.com/</t>
+          <t>https://www.instagram.com/ise_zushi/</t>
         </is>
       </c>
       <c r="P476" t="inlineStr">
@@ -31830,23 +32414,39 @@
           <t>https://www.google.com/maps/place/%E9%85%92%E5%87%A6+%E3%81%B5%E3%81%98%E3%82%8A%E3%82%93/data=!4m2!3m1!1s0x5f0ae0512eaea7c1:0x7c0e0d04e1153293</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr"/>
-      <c r="J480" t="inlineStr"/>
-      <c r="K480" t="inlineStr"/>
-      <c r="L480" t="inlineStr"/>
-      <c r="M480" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/otaru_fujirin/</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>otaru_fujirin</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M480" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N480" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: otaru_fujirin</t>
+          <t>Second pass: the account's own name places the shop in Otaru and its profile gives the address as Inaho 2-11-2, Otaru with its telephone number and its stock of more than thirty sakes.</t>
         </is>
       </c>
       <c r="O480" s="2" t="inlineStr">
         <is>
-          <t>https://hamoni.jp/en/shop/gpw7xroHKSvqzQVpzoD66x0d5gAUuVHn</t>
+          <t>https://www.instagram.com/otaru_fujirin/</t>
         </is>
       </c>
       <c r="P480" t="inlineStr">
@@ -31953,7 +32553,7 @@
       </c>
       <c r="N482" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: cotaruco</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: cotaruco Second pass: no account was found under this shop's name in Otaru.</t>
         </is>
       </c>
       <c r="O482" s="2" t="inlineStr">
@@ -32065,7 +32665,7 @@
       </c>
       <c r="N484" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: freehouse_the_yeast, voyapon</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: freehouse_the_yeast, voyapon Second pass: no account was found under this bar's name in Asahikawa; the name matches are bars and breweries in the United States and Singapore.</t>
         </is>
       </c>
       <c r="O484" s="2" t="inlineStr">
@@ -32737,7 +33337,7 @@
       </c>
       <c r="N496" s="4" t="inlineStr">
         <is>
-          <t>The only account found for this shop belongs to its manager; it places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is a personal account rather than the shop's own, so it is not recorded.</t>
+          <t>The only account found for this shop belongs to its manager; it places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is a personal account rather than the shop's own, so it is not recorded. Second pass: the manager's account places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is the manager's own account rather than the shop's, so it is not recorded - the same rule applied to the other proprietor-run accounts in this ledger.</t>
         </is>
       </c>
       <c r="O496" s="2" t="inlineStr">
@@ -33094,23 +33694,39 @@
           <t>https://www.google.com/maps/place/%E5%8C%97%E6%B5%B7%E9%81%93%E5%BA%81/data=!4m2!3m1!1s0x5f0b299f007507ad:0xbb215d6e0de69db7</t>
         </is>
       </c>
-      <c r="I502" t="inlineStr"/>
-      <c r="J502" t="inlineStr"/>
-      <c r="K502" t="inlineStr"/>
-      <c r="L502" t="inlineStr"/>
-      <c r="M502" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I502" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/akarenga_chousha_1888/</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>akarenga_chousha_1888</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M502" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N502" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Only akarenga_chousha_1888 is plausible, and the page also links unrelated accounts; not confirmable from this page alone. Candidates: akarenga_chousha_1888, house.h__, shiroikoibito_akarenga_</t>
+          <t>Second pass: the building's own account; its profile gives the address as Kita 3-jo Nishi 6-chome 1, Chuo-ku, Sapporo with its opening hours and admission, and names it a nationally designated important cultural property, matching this listing.</t>
         </is>
       </c>
       <c r="O502" s="2" t="inlineStr">
         <is>
-          <t>https://www.hokkaido-redbrick.jp/</t>
+          <t>https://www.instagram.com/akarenga_chousha_1888/</t>
         </is>
       </c>
       <c r="P502" t="inlineStr">
@@ -33226,23 +33842,39 @@
           <t>https://www.google.com/maps/place/%E5%91%B3%E3%81%AE%E4%B8%89%E5%B9%B3/data=!4m2!3m1!1s0x5f0b2983480fffff:0x156c664dae55dc1</t>
         </is>
       </c>
-      <c r="I504" t="inlineStr"/>
-      <c r="J504" t="inlineStr"/>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
-      <c r="M504" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I504" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sapporoajinosanpei/</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>sapporoajinosanpei</t>
+        </is>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M504" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N504" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: welcomesapporo</t>
+          <t>Second pass: the account's own name places the shop in Sapporo and its profile dates it to 1950 in Susukino, recounts how its founder created miso ramen and gives its hours and Monday closing.</t>
         </is>
       </c>
       <c r="O504" s="2" t="inlineStr">
         <is>
-          <t>https://www.sapporo.travel/gourmet/shop/shop_130-2/</t>
+          <t>https://www.instagram.com/sapporoajinosanpei/</t>
         </is>
       </c>
       <c r="P504" t="inlineStr">
@@ -33416,23 +34048,39 @@
           <t>https://www.google.com/maps/place/%E3%82%AD%E3%83%A3%E3%83%97%E3%83%86%E3%83%B3%E3%82%AB%E3%83%B3%E3%82%AC%E3%83%AB%E3%83%BC/data=!4m2!3m1!1s0x34e4ff6d24d3d969:0xff883e4d4931f447</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
-      <c r="J507" t="inlineStr"/>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
-      <c r="M507" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I507" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/captainkangaroo_okinawa/</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>captainkangaroo_okinawa</t>
+        </is>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M507" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N507" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: icotto_official</t>
+          <t>Second pass: the account's own profile gives the shop's address as Sakimotobu 930-1, Motobu, Kunigami-gun, Okinawa with its telephone number, matching this listing; the Nago tacorice shop and the Tokyo branch keep separate accounts.</t>
         </is>
       </c>
       <c r="O507" s="2" t="inlineStr">
         <is>
-          <t>https://icotto.jp/restaurants/54032</t>
+          <t>https://www.instagram.com/captainkangaroo_okinawa/</t>
         </is>
       </c>
       <c r="P507" t="inlineStr">
@@ -33989,7 +34637,7 @@
       </c>
       <c r="N516" s="4" t="inlineStr">
         <is>
-          <t>An account for the restaurant's main shop exists and its profile describes a 75-year-old Kumamoto restaurant serving horse meat and local dishes, but it names no branch or address, so it could not be tied to the Suizenji shop.</t>
+          <t>An account for the restaurant's main shop exists and its profile describes a 75-year-old Kumamoto restaurant serving horse meat and local dishes, but it names no branch or address, so it could not be tied to the Suizenji shop. Second pass: searched again with the neighbourhood name; the account for the restaurant's main shop still gives no address or branch, so it could not be tied to the Suizenji shop.</t>
         </is>
       </c>
       <c r="O516" s="2" t="inlineStr">
@@ -34125,7 +34773,7 @@
       </c>
       <c r="N518" s="4" t="inlineStr">
         <is>
-          <t>Two accounts exist for facilities on this bathhouse's grounds in Hakuba - its car-stay park and its campsite - and both describe the spring's iron-rich water, but neither is the bathhouse's own account, so none is recorded.</t>
+          <t>Two accounts exist for facilities on this bathhouse's grounds in Hakuba - its car-stay park and its campsite - and both describe the spring's iron-rich water, but neither is the bathhouse's own account, so none is recorded. Second pass: searched again as a day-use bath; the only accounts on these grounds belong to the car-stay park and the campsite, not to the bathhouse itself, so none is recorded.</t>
         </is>
       </c>
       <c r="O518" t="inlineStr"/>
@@ -34435,7 +35083,7 @@
       </c>
       <c r="N523" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. The account reached (fullmarks_official) belongs to an unrelated business. Seen: fullmarks_official</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. The account reached (fullmarks_official) belongs to an unrelated business. Seen: fullmarks_official Second pass: no account was found under this restaurant's name in Hakuba; the handle printed for it on a directory page belongs to an unrelated business.</t>
         </is>
       </c>
       <c r="O523" s="2" t="inlineStr">
@@ -34482,23 +35130,39 @@
           <t>https://www.google.com/maps/place/%E3%83%9F%E3%82%B5%E3%83%AD%E3%83%83%E3%82%BD/data=!4m2!3m1!1s0x356a943f9eb9f75d:0xcbfe30195a4fdb95</t>
         </is>
       </c>
-      <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr"/>
-      <c r="L524" t="inlineStr"/>
-      <c r="M524" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I524" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/misa.rosso/</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>misa.rosso</t>
+        </is>
+      </c>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>store</t>
+        </is>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>profile</t>
+        </is>
+      </c>
+      <c r="M524" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N524" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: non.aldesuga.nanika</t>
+          <t>Second pass: the account's own profile gives the shop's address as Mantoku-cho 2-15, Sasebo, Nagasaki with its hours, Tuesday closing and telephone number, and describes its house-made buns, matching this listing.</t>
         </is>
       </c>
       <c r="O524" s="2" t="inlineStr">
         <is>
-          <t>https://tabelog.com/nagasaki/A4202/A420201/42000523/</t>
+          <t>https://www.instagram.com/misa.rosso/</t>
         </is>
       </c>
       <c r="P524" t="inlineStr">
@@ -34691,7 +35355,7 @@
       </c>
       <c r="N527" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: wez_kofu</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: wez_kofu Second pass: no account was found under this shop's name in Showa-cho, Yamanashi.</t>
         </is>
       </c>
       <c r="O527" s="2" t="inlineStr">
@@ -34728,1046 +35392,1089 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I433" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I507" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I524" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -35803,7 +36510,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>217</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3">
@@ -35823,7 +36530,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
@@ -35833,7 +36540,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>179</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
@@ -35843,7 +36550,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -35853,7 +36560,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -35890,7 +36597,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them; every row carries either a result or the reason none could be established</t>
+          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them, and all 111 rows that remained ambiguous have had a second per-venue pass; every row carries either a result or the reason none could be established</t>
         </is>
       </c>
     </row>

--- a/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
+++ b/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>An account named イト I.To describes a French-based a la carte restaurant, but its profile text does not state Higashi-Nakano, so it could not be tied to this listing. Second pass: the restaurant's own account was found and its profile describes its French-based a la carte cooking and private-hire minimum, but it states no address or area, so it could not be placed in Higashi-Nakano.</t>
+          <t>An account named イト I.To describes a French-based a la carte restaurant, but its profile text does not state Higashi-Nakano, so it could not be tied to this listing. Second pass: the restaurant's own account was found and its profile describes its French-based a la carte cooking and private-hire minimum, but it states no address or area, so it could not be placed in Higashi-Nakano. Third pass: the audit list adds neither an address nor a source page for this row, so there was nothing new to check and the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>The only account of this brand is the Ueno/Okachimachi branch's, whose profile gives the Ueno address; no account for the Harajuku branch was found, and the Ueno branch's account is not this branch's. Second pass: the brand keeps one account, whose profile gives only the Ueno shop's address and hours; no account for the Harajuku branch exists, so none could be tied to this listing.</t>
+          <t>The only account of this brand is the Ueno/Okachimachi branch's, whose profile gives the Ueno address; no account for the Harajuku branch was found, and the Ueno branch's account is not this branch's. Second pass: the brand keeps one account, whose profile gives only the Ueno shop's address and hours; no account for the Harajuku branch exists, so none could be tied to this listing. Third pass: the audit list adds neither an address nor a source page for this row, so there was nothing new to check and the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: azabuen0818 Second pass: no account was found under this restaurant's name; the nearest match is a differently named Azabu-Juban restaurant whose only account belongs to its manager.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: azabuen0818 Second pass: no account was found under this restaurant's name; the nearest match is a differently named Azabu-Juban restaurant whose only account belongs to its manager. Third pass: read the sources the audit list records for this row (https://www.makuake.com/project/azabu-en/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: senrigaaan Second pass: no account was found for this shop in Yoyogi-Uehara; the handle printed for it on a directory page belongs to a shop of the same name in Shiki, Saitama, so it was not recorded.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: senrigaaan Second pass: no account was found for this shop in Yoyogi-Uehara; the handle printed for it on a directory page belongs to a shop of the same name in Shiki, Saitama, so it was not recorded. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1318/A131811/13099150/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bakumatsucurry, ippukuandmatcha_uehara, sakaba_debayashi Second pass: the bakery's own account was found and its profile gives the opening hours and closing days, but it states no address or area, so it could not be placed in Nishihara.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: bakumatsucurry, ippukuandmatcha_uehara, sakaba_debayashi Second pass: the bakery's own account was found and its profile gives the opening hours and closing days, but it states no address or area, so it could not be placed in Nishihara. Third pass: the audit list adds an address for this row (渋谷区西原1-7-5) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. The only Instagram link on the page reached was rurubuplus, the publisher's own account. Seen: none Second pass: an account under this shop's name was found and its profile gives the cafe and crepe hours and the whole-cake ordering, but it states no address or area, so it could not be placed in Yoyogi-Uehara.</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. The only Instagram link on the page reached was rurubuplus, the publisher's own account. Seen: none Second pass: an account under this shop's name was found and its profile gives the cafe and crepe hours and the whole-cake ordering, but it states no address or area, so it could not be placed in Yoyogi-Uehara. Third pass: the audit list adds an address for this row (渋谷区上原1-2-1) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yomuno_official Second pass: no account was found under this restaurant's name in Nakameguro; the results were other steak and teppanyaki restaurants in the area.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yomuno_official Second pass: no account was found under this restaurant's name in Nakameguro; the results were other steak and teppanyaki restaurants in the area. Third pass: read the sources the audit list records for this row (https://map.yahoo.co.jp/v3/place/Mu-gOcG3d52, https://yomuno.jp/posts/140259) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kinarino_official Second pass: no account was found under this shop's name in Otowa; the handle printed for it on a directory page is the publisher's own.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: kinarino_official Second pass: no account was found under this shop's name in Otowa; the handle printed for it on a directory page is the publisher's own. Third pass: read the sources the audit list records for this row (https://kinarino.jp/cat8/28987) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>Two accounts both present themselves as this brand's Omotesando shop (amam_dacotan_omotesando and amam_dacotan_omotedando) and they give different addresses; neither could be established as the shop's own, so none is recorded. Second pass: two accounts present themselves as this brand's Omotesando shop under near-identical names, and both now give the same address at Kita-Aoyama 3-7-6; because nothing distinguishes which of the two is the shop's current account, neither is recorded. A third account belongs to the separate cafe and bake shop at Kita-Aoyama 3-6-23.</t>
+          <t>Two accounts both present themselves as this brand's Omotesando shop (amam_dacotan_omotesando and amam_dacotan_omotedando) and they give different addresses; neither could be established as the shop's own, so none is recorded. Second pass: two accounts present themselves as this brand's Omotesando shop under near-identical names, and both now give the same address at Kita-Aoyama 3-7-6; because nothing distinguishes which of the two is the shop's current account, neither is recorded. A third account belongs to the separate cafe and bake shop at Kita-Aoyama 3-6-23. Third pass: the audit list adds an address for this row (港区北青山3-7-6) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O85" t="inlineStr"/>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>The account found belongs to this operator's Keikeikaku branches near Kamata station, not to the main shop this listing records; no account for the main shop was found. Second pass: the brand keeps an account for its Keishinkaku branch, whose profile lists the Kamata branches, but no account was found for the main shop, so none could be tied to this listing.</t>
+          <t>The account found belongs to this operator's Keikeikaku branches near Kamata station, not to the main shop this listing records; no account for the main shop was found. Second pass: the brand keeps an account for its Keishinkaku branch, whose profile lists the Kamata branches, but no account was found for the main shop, so none could be tied to this listing. Third pass: the audit list adds an address for this row (大田区蒲田4-24-14) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O95" t="inlineStr"/>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: pizzeriaciro.hgn Second pass: the shop's own account was found and its profile gives the lunch and dinner hours, closing days and a Tokyo telephone number, but no address or area, so it could not be placed in Nakano.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: pizzeriaciro.hgn Second pass: the shop's own account was found and its profile gives the lunch and dinner hours, closing days and a Tokyo telephone number, but no address or area, so it could not be placed in Nakano. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1319/A131901/13302780/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The monument has no account of its own. The site links two Yasukuni Shrine accounts and neither is the statue's - left ambiguous rather than attributing the shrine's account to a monument. Candidates: yasukuni.official, yasukunijinja Second pass: the statue has no account of its own. The shrine whose grounds it stands in keeps one, but attributing the shrine's account to a monument would misrepresent it, so none is recorded.</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. The monument has no account of its own. The site links two Yasukuni Shrine accounts and neither is the statue's - left ambiguous rather than attributing the shrine's account to a monument. Candidates: yasukuni.official, yasukunijinja Second pass: the statue has no account of its own. The shrine whose grounds it stands in keeps one, but attributing the shrine's account to a monument would misrepresent it, so none is recorded. Third pass: read the sources the audit list records for this row (https://www.yasukuni.or.jp/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="N134" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Accounts reached are Meiji Kinenkan and the shrine's support association, neither of them the shrine's own account. Seen: meiji_kinenkan_official, meijijingu_sukeikai Second pass: the shrine keeps no account of its own; the only official account in its name belongs to its wedding venue, Forest Terrace, so none is recorded for the shrine.</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Accounts reached are Meiji Kinenkan and the shrine's support association, neither of them the shrine's own account. Seen: meiji_kinenkan_official, meijijingu_sukeikai Second pass: the shrine keeps no account of its own; the only official account in its name belongs to its wedding venue, Forest Terrace, so none is recorded for the shrine. Third pass: read the sources the audit list records for this row (https://www.meijikinenkan.gr.jp/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O134" s="2" t="inlineStr">
@@ -9343,7 +9343,7 @@
       </c>
       <c r="N137" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Museum inside Yasukuni; its page links the shrine's two accounts, neither specific to the museum. Candidates: yasukuni.official, yasukunijinja Second pass: the museum keeps no account of its own. The shrine it stands in has one, but it is the shrine's and not this museum's, so none is recorded.</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Museum inside Yasukuni; its page links the shrine's two accounts, neither specific to the museum. Candidates: yasukuni.official, yasukunijinja Second pass: the museum keeps no account of its own. The shrine it stands in has one, but it is the shrine's and not this museum's, so none is recorded. Third pass: read the sources the audit list records for this row (https://www.yasukuni.or.jp/yusyukan/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the street were reached, not the shopping street's own. Seen: kanaya_brush_1914, takaso_demoandkitchen Second pass: the shopping street keeps no account of its own; the association that runs it maintains an account for its annual tool fair, and the rest are individual member shops, so none is recorded for the street.</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the street were reached, not the shopping street's own. Seen: kanaya_brush_1914, takaso_demoandkitchen Second pass: the shopping street keeps no account of its own; the association that runs it maintains an account for its annual tool fair, and the rest are individual member shops, so none is recorded for the street. Third pass: read the sources the audit list records for this row (https://www.kanaya-brush.com/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="N142" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: agora_jp, sensyuyatai Second pass: no account was found that carries this shop's name and places it anywhere; the handle printed for it on a directory page could not be confirmed on a profile.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: agora_jp, sensyuyatai Second pass: no account was found that carries this shop's name and places it anywhere; the handle printed for it on a directory page could not be confirmed on a profile. Third pass: read the sources the audit list records for this row (https://retty.me/restaurant/100001538557/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only the hotel's and its sibling restaurants' accounts were reached, none of them this bar's. Seen: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this bar's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this bar's.</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only the hotel's and its sibling restaurants' accounts were reached, none of them this bar's. Seen: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this bar's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this bar's. Third pass: read the sources the audit list records for this row (https://aoyamagrand.com/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="N149" s="4" t="inlineStr">
         <is>
-          <t>Two accounts carry this name: one places itself in Minami-Aoyama and Nishi-Azabu, not Ginza, and the other gives no location. Neither could be tied to this listing. Second pass: the account carrying this bar's name places itself in Minami-Aoyama and Nishi-Azabu, not Ginza where this listing places it, so it was not recorded.</t>
+          <t>Two accounts carry this name: one places itself in Minami-Aoyama and Nishi-Azabu, not Ginza, and the other gives no location. Neither could be tied to this listing. Second pass: the account carrying this bar's name places itself in Minami-Aoyama and Nishi-Azabu, not Ginza where this listing places it, so it was not recorded. Third pass: the audit list adds an address for this row (東京都港区南青山6-6-21 グロービル青山 B1) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O149" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>An account of this exact name exists and describes a soba restaurant in a century-old townhouse, but its profile states no location, so it could not be tied to this listing's area. Second pass: the restaurant's own account was found and its profile describes its hundred-year-old townhouse setting and its reservation-only course lunch, but it states no address or area, so it could not be placed in Ochiai.</t>
+          <t>An account of this exact name exists and describes a soba restaurant in a century-old townhouse, but its profile states no location, so it could not be tied to this listing's area. Second pass: the restaurant's own account was found and its profile describes its hundred-year-old townhouse setting and its reservation-only course lunch, but it states no address or area, so it could not be placed in Ochiai. Third pass: searched Instagram for the address the audit list records (東京都新宿区下落合3-21-5); no profile prints it, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -10449,7 +10449,7 @@
       </c>
       <c r="N154" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: savor_japan Second pass: no account was found under this shop's name in Koenji.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: savor_japan Second pass: no account was found under this shop's name in Koenji. Third pass: read the sources the audit list records for this row (https://savorjapan.com/0020008536) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="N168" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: 1973posy, tokyoweekender Second pass: no account was found for this venue in Setagaya; the handle printed for it on a media page could not be confirmed on any profile naming the venue.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: 1973posy, tokyoweekender Second pass: no account was found for this venue in Setagaya; the handle printed for it on a media page could not be confirmed on any profile naming the venue. Third pass: read the sources the audit list records for this row (https://www.tokyoweekender.com/food-and-drink/restaurants-and-bars/jazz-house-posy-shimokitazawa-listening-bar/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O168" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists but states no location, and its handle points to a different district, so it could not be tied to this listing. Second pass: the only account carrying this name belongs to a yakitori shop in Kabukicho and gives no address, so it could not be tied to this listing in Yotsuya.</t>
+          <t>An account of this name exists but states no location, and its handle points to a different district, so it could not be tied to this listing. Second pass: the only account carrying this name belongs to a yakitori shop in Kabukicho and gives no address, so it could not be tied to this listing in Yotsuya. Third pass: the audit list adds an address for this row (東京都新宿区荒木町3-1) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="N195" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: inshokucom_journal Second pass: no account was found under this bar's name in Suidobashi.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: inshokucom_journal Second pass: no account was found under this bar's name in Suidobashi. Third pass: read the sources the audit list records for this row (https://www.inshokuten.com/foodist/article/7089/lead/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="N197" s="4" t="inlineStr">
         <is>
-          <t>An account exists for a shop of nearly this name written with a different kana, but it states no location, so it could not be tied to this listing. Second pass: no account was found for this shop in Edogawabashi; the name matches are a ramen shop in Fukaya, Saitama and a shop whose name is spelled differently.</t>
+          <t>An account exists for a shop of nearly this name written with a different kana, but it states no location, so it could not be tied to this listing. Second pass: no account was found for this shop in Edogawabashi; the name matches are a ramen shop in Fukaya, Saitama and a shop whose name is spelled differently. Third pass: the audit list adds an address for this row (東京都文京区関口1-48-48 イシダビル 1F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="N203" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: sobadokoro_kameya Second pass: no account was found for this branch; the handle printed for it on a directory page could not be confirmed on a profile naming the shop or its Kanda branch.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: sobadokoro_kameya Second pass: no account was found for this branch; the handle printed for it on a directory page could not be confirmed on a profile naming the shop or its Kanda branch. Third pass: read the sources the audit list records for this row (https://retty.me/restaurant/100000053622/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O203" s="2" t="inlineStr">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="N253" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists for an Italian restaurant and bar, but its profile gives no address; only its telephone exchange points to this area, which is not enough to tie it to this listing. Second pass: the restaurant's own account was found and its profile describes its charcoal-grilled Italian cooking, hours and telephone number, whose 03-6420 exchange covers the Gotanda area, but the profile prints no address, so the area could not be confirmed from the profile itself.</t>
+          <t>An account of this name exists for an Italian restaurant and bar, but its profile gives no address; only its telephone exchange points to this area, which is not enough to tie it to this listing. Second pass: the restaurant's own account was found and its profile describes its charcoal-grilled Italian cooking, hours and telephone number, whose 03-6420 exchange covers the Gotanda area, but the profile prints no address, so the area could not be confirmed from the profile itself. Third pass: the audit list adds an address for this row (東京都品川区西五反田1-4-8 202) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O253" s="2" t="inlineStr">
@@ -17935,7 +17935,7 @@
       </c>
       <c r="N263" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: musicbarbounce Second pass: the bar's own account was found and its profile gives its music policy, opening hours and charges, but it states no address or area, so it could not be placed in Shibuya.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: musicbarbounce Second pass: the bar's own account was found and its profile gives its music policy, opening hours and charges, but it states no address or area, so it could not be placed in Shibuya. Third pass: the audit list adds an address for this row (東京都渋谷区道玄坂2-19-12 東洋道玄坂ビル2F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O263" s="2" t="inlineStr">
@@ -18145,7 +18145,7 @@
       </c>
       <c r="N266" s="4" t="inlineStr">
         <is>
-          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Restaurant inside THE AOYAMA GRAND HOTEL. The hotel site links the hotel and two sibling restaurants, none of them this one. Candidates: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this restaurant's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this one's.</t>
+          <t>Several official accounts are linked from the site and none is identifiable as this venue's. Restaurant inside THE AOYAMA GRAND HOTEL. The hotel site links the hotel and two sibling restaurants, none of them this one. Candidates: aoyamagrand, theriveroriental, thetokyorestaurant Second pass: no account was found under this restaurant's name in Aoyama; only the hotel it sits in and its sibling restaurants keep accounts, and none of them is this one's. Third pass: read the sources the audit list records for this row (https://aoyamagrand.com/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O266" s="2" t="inlineStr">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="N271" s="4" t="inlineStr">
         <is>
-          <t>An account of this exact name exists but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this restaurant's name was found but its profile carries no address, hours or other detail, so it could not be placed in Mita or Tamachi.</t>
+          <t>An account of this exact name exists but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this restaurant's name was found but its profile carries no address, hours or other detail, so it could not be placed in Mita or Tamachi. Third pass: searched Instagram for the address the audit list records (東京都港区三田2-6-13 コート三田); no profile prints it, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O271" s="2" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="N287" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: tablecheck_global Second pass: no account was found under this bar's name in Yoyogi-Hachiman.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: tablecheck_global Second pass: no account was found under this bar's name in Yoyogi-Hachiman. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1318/A131810/13269639/, https://www.tablecheck.com/en/1500-millecinquecento) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O287" s="2" t="inlineStr">
@@ -19683,7 +19683,7 @@
       </c>
       <c r="N289" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists for a wine bar, but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this venue's name was found and its profile describes a wine bar with simple snacks and gives its late hours, but it states no address or area, so it could not be placed in Yoyogi-Hachiman; a pub of the same name in Monzen-Nakacho keeps a separate account.</t>
+          <t>An account of this name exists for a wine bar, but its profile states no location, so it could not be tied to this listing's area. Second pass: an account under this venue's name was found and its profile describes a wine bar with simple snacks and gives its late hours, but it states no address or area, so it could not be placed in Yoyogi-Hachiman; a pub of the same name in Monzen-Nakacho keeps a separate account. Third pass: the audit list adds an address for this row (東京都渋谷区西原3-24-1 アムール代々木上原104) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O289" s="2" t="inlineStr">
@@ -19823,7 +19823,7 @@
       </c>
       <c r="N291" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: ittenbari_1 Second pass: no account of this restaurant's own was found; a Ningyocho izakaya's account names it among its sister shops, but that is not this restaurant's account and the handle printed for it on a directory page could not be confirmed.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: ittenbari_1 Second pass: no account of this restaurant's own was found; a Ningyocho izakaya's account names it among its sister shops, but that is not this restaurant's account and the handle printed for it on a directory page could not be confirmed. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1302/A130204/13283307/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O291" s="2" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="N294" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: nadoya.katte Second pass: the stand's own account was found and its profile describes it as a single-origin coffee stand produced by nadoya with coffee supervised by Glitch, and gives its hours, but neither it nor the parent account states an address, so it could not be placed in Yoyogi-Uehara.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: nadoya.katte Second pass: the stand's own account was found and its profile describes it as a single-origin coffee stand produced by nadoya with coffee supervised by Glitch, and gives its hours, but neither it nor the parent account states an address, so it could not be placed in Yoyogi-Uehara. Third pass: searched Instagram for the address the audit list records (東京都渋谷区西原3-19-3); no profile prints it, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O294" s="2" t="inlineStr">
@@ -20459,7 +20459,7 @@
       </c>
       <c r="N301" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: i2.cafe Second pass: no account was found under this cafe's name in Omotesando or Minami-Aoyama.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: i2.cafe Second pass: no account was found under this cafe's name in Omotesando or Minami-Aoyama. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1306/A130602/13282796/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="N303" s="4" t="inlineStr">
         <is>
-          <t>An account of this name exists and names the operating company in its profile, but it has almost no content and states no location, so it could not be tied to this listing. Second pass: no account was found for this restaurant in Aoyama; the name matches are unrelated businesses in Osaka, Arima, Hirakata and Taiwan.</t>
+          <t>An account of this name exists and names the operating company in its profile, but it has almost no content and states no location, so it could not be tied to this listing. Second pass: no account was found for this restaurant in Aoyama; the name matches are unrelated businesses in Osaka, Arima, Hirakata and Taiwan. Third pass: the audit list adds an address for this row (東京都港区北青山2-14-4 the ARGYLE aoyama 2F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -21057,7 +21057,7 @@
       </c>
       <c r="N310" s="4" t="inlineStr">
         <is>
-          <t>Two accounts present themselves as this shop's owner and neither states the shop's address; one notes that an earlier account naming this shop and area was taken over, so no account could be confirmed as the shop's. Second pass: the two accounts carrying this shop's name both belong to its proprietor, and the newer one explains that the shop's earlier account was hijacked; neither is the shop's own account, so none is recorded.</t>
+          <t>Two accounts present themselves as this shop's owner and neither states the shop's address; one notes that an earlier account naming this shop and area was taken over, so no account could be confirmed as the shop's. Second pass: the two accounts carrying this shop's name both belong to its proprietor, and the newer one explains that the shop's earlier account was hijacked; neither is the shop's own account, so none is recorded. Third pass: the audit list adds an address for this row (東京都新宿区山吹町362 プレステージ362) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O310" t="inlineStr"/>
@@ -21795,7 +21795,7 @@
       </c>
       <c r="N321" s="4" t="inlineStr">
         <is>
-          <t>An account named Restaurant Glover-tei exists, but its profile gives no address and nothing in it places the shop in Mitaka; a second account of the same name is a Nagasaki champon shop in Niigata, so neither could be established as this shop's. Second pass: the restaurant's own account was searched again with the city name; its profile still gives no address and nothing places the shop in Mitaka, so it is not recorded.</t>
+          <t>An account named Restaurant Glover-tei exists, but its profile gives no address and nothing in it places the shop in Mitaka; a second account of the same name is a Nagasaki champon shop in Niigata, so neither could be established as this shop's. Second pass: the restaurant's own account was searched again with the city name; its profile still gives no address and nothing places the shop in Mitaka, so it is not recorded. Third pass: the audit list adds an address for this row (東京都三鷹市下連雀3-25-8) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O321" s="2" t="inlineStr">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="N323" s="4" t="inlineStr">
         <is>
-          <t>An account named Chuka Juhachiban exists and matches the name and category, but its profile gives only opening hours and no location, so it could not be tied to the Nogata shop; the other name matches are in Chuo-ku, Osaka and Wakayama. Second pass: the account carrying this shop's name gives its menu, hours and a large car park in its profile but no address, and the profile's car park does not match a Nogata shopfront, so it is not recorded.</t>
+          <t>An account named Chuka Juhachiban exists and matches the name and category, but its profile gives only opening hours and no location, so it could not be tied to the Nogata shop; the other name matches are in Chuo-ku, Osaka and Wakayama. Second pass: the account carrying this shop's name gives its menu, hours and a large car park in its profile but no address, and the profile's car park does not match a Nogata shopfront, so it is not recorded. Third pass: the audit list adds an address for this row (東京都中野区大和町2-2-2) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O323" s="2" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="N332" s="4" t="inlineStr">
         <is>
-          <t>The chain keeps separate branch accounts (Hokkaido, Okinawa and Miyakojima among them) but no account for the Shinjuku branch was found, and the brand-level account's profile gives no location, so none could be tied to this branch. Second pass: the chain's own accounts name a brand-level account and separate regional accounts for Hokkaido, Okinawa, Miyakojima and Vietnam, but none of them is placed in Shinjuku, so none could be tied to this branch.</t>
+          <t>The chain keeps separate branch accounts (Hokkaido, Okinawa and Miyakojima among them) but no account for the Shinjuku branch was found, and the brand-level account's profile gives no location, so none could be tied to this branch. Second pass: the chain's own accounts name a brand-level account and separate regional accounts for Hokkaido, Okinawa, Miyakojima and Vietnam, but none of them is placed in Shinjuku, so none could be tied to this branch. Third pass: the audit list adds an address for this row (東京都新宿区歌舞伎町1-15-12) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O332" t="inlineStr"/>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="N344" s="4" t="inlineStr">
         <is>
-          <t>An account carrying this restaurant's name and its proprietor's name exists and its profile gives opening hours and the Tuesday-Wednesday closing, but no address or area, so it could not be tied to the Shikahama shop. Second pass: searched again with the neighbourhood name; the account carrying this restaurant's and its proprietor's name still gives only its hours and closing days, with no address, so it could not be placed in Shikahama.</t>
+          <t>An account carrying this restaurant's name and its proprietor's name exists and its profile gives opening hours and the Tuesday-Wednesday closing, but no address or area, so it could not be tied to the Shikahama shop. Second pass: searched again with the neighbourhood name; the account carrying this restaurant's and its proprietor's name still gives only its hours and closing days, with no address, so it could not be placed in Shikahama. Third pass: the audit list adds an address for this row (東京都足立区鹿浜3-13-4) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O344" s="2" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="N345" s="4" t="inlineStr">
         <is>
-          <t>The brand's account exists but its profile places the restaurant at Azabudai Hills, not Ebisu where this listing places it, so it was not recorded; the sibling accounts are the Kanda and Taipei restaurants. Second pass: searched again with the neighbourhood and the brand's other name; the account still places the restaurant at Azabudai Hills rather than Ebisu, so it was not recorded.</t>
+          <t>The brand's account exists but its profile places the restaurant at Azabudai Hills, not Ebisu where this listing places it, so it was not recorded; the sibling accounts are the Kanda and Taipei restaurants. Second pass: searched again with the neighbourhood and the brand's other name; the account still places the restaurant at Azabudai Hills rather than Ebisu, so it was not recorded. Third pass: the audit list adds an address for this row (東京都渋谷区恵比寿1-11-5 GEMS恵比寿8F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O345" s="2" t="inlineStr">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="N346" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: profite_sincerite Second pass: no account was found under this shop's name in Soshigaya-Okura.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: profite_sincerite Second pass: no account was found under this shop's name in Soshigaya-Okura. Third pass: read the sources the audit list records for this row (https://hamoni.jp/area/tokyo/setagaya/soshigayaokura/list/bread-snacks) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O346" s="2" t="inlineStr">
@@ -24159,7 +24159,7 @@
       </c>
       <c r="N357" s="4" t="inlineStr">
         <is>
-          <t>The bakery's brand account exists and gives its hours, but neither it nor the sibling coffee account states any location, so the account could not be placed in Roppongi. Second pass: searched again with the neighbourhood names; neither the bakery's account nor its sibling coffee account prints an address, so the shop could not be placed in Roppongi.</t>
+          <t>The bakery's brand account exists and gives its hours, but neither it nor the sibling coffee account states any location, so the account could not be placed in Roppongi. Second pass: searched again with the neighbourhood names; neither the bakery's account nor its sibling coffee account prints an address, so the shop could not be placed in Roppongi. Third pass: the audit list adds an address for this row (東京都港区六本木6-15-1 六本木ヒルズけやき坂テラス1F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O357" s="2" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="N361" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banthai_shinjyuku Second pass: no account was found under this restaurant's name in Shinjuku; the name match is a Thai restaurant in Joetsu, Niigata.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banthai_shinjyuku Second pass: no account was found under this restaurant's name in Shinjuku; the name match is a Thai restaurant in Joetsu, Niigata. Third pass: read the sources the audit list records for this row (https://retty.me/restaurant/100000001521/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O361" s="2" t="inlineStr">
@@ -24517,7 +24517,7 @@
       </c>
       <c r="N362" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: hotatebiyori Second pass: the shop's own account was found and its profile describes its Sarufutsu scallops and Hokkaido wheat noodles, but it states no address or area, so it could not be placed in Akihabara.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: hotatebiyori Second pass: the shop's own account was found and its profile describes its Sarufutsu scallops and Hokkaido wheat noodles, but it states no address or area, so it could not be placed in Akihabara. Third pass: searched Instagram for the address the audit list records (東京都千代田区神田佐久間町2-25); no profile prints it, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O362" s="2" t="inlineStr">
@@ -25025,7 +25025,7 @@
       </c>
       <c r="N370" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: medikasoba.kin_gyo Second pass: the shop's own account was found and its profile gives its hours and its two soup styles, but it states no address or area, so it could not be placed in Manganji.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: medikasoba.kin_gyo Second pass: the shop's own account was found and its profile gives its hours and its two soup styles, but it states no address or area, so it could not be placed in Manganji. Third pass: the audit list adds an address for this row (東京都日野市石田2-9-1) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O370" s="2" t="inlineStr">
@@ -25087,7 +25087,7 @@
       </c>
       <c r="N371" s="4" t="inlineStr">
         <is>
-          <t>An account with this shop's exact and distinctive name exists and its profile gives the opening days and hours, but it states no address or area, so it could not be placed in Higashi-Ogu. Second pass: searched again with the ward name; the shop's own account still gives only its opening days and hours, with no address, so it could not be placed in Higashi-Ogu.</t>
+          <t>An account with this shop's exact and distinctive name exists and its profile gives the opening days and hours, but it states no address or area, so it could not be placed in Higashi-Ogu. Second pass: searched again with the ward name; the shop's own account still gives only its opening days and hours, with no address, so it could not be placed in Higashi-Ogu. Third pass: the audit list adds an address for this row (東京都荒川区東尾久2-19-10 西脇ビル1F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O371" s="2" t="inlineStr">
@@ -25323,7 +25323,7 @@
       </c>
       <c r="N375" s="4" t="inlineStr">
         <is>
-          <t>An account with this shop's exact name exists and its profile describes its own noodles and use of no chemical seasonings, but it states no address or area, so it could not be placed in Kameido. Second pass: searched again with the ward name; the shop's own account still gives only its own-noodle and no-additive claims, with no address, so it could not be placed in Kameido.</t>
+          <t>An account with this shop's exact name exists and its profile describes its own noodles and use of no chemical seasonings, but it states no address or area, so it could not be placed in Kameido. Second pass: searched again with the ward name; the shop's own account still gives only its own-noodle and no-additive claims, with no address, so it could not be placed in Kameido. Third pass: read the sources the audit list records for this row (https://tabelog.com/tokyo/A1312/A131202/13276443/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O375" s="2" t="inlineStr">
@@ -25555,7 +25555,7 @@
       </c>
       <c r="N379" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: codies.burger Second pass: no account was found under this shop's name in Yokohama; the name match is a restaurant in Queensland, Australia.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: codies.burger Second pass: no account was found under this shop's name in Yokohama; the name match is a restaurant in Queensland, Australia. Third pass: read the sources the audit list records for this row (https://hamoni.jp/shop/awcH71yjDLr8uLhA4bci) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O379" s="2" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="N402" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: roujina0627 Second pass: the restaurant's own account was found and its profile gives its lunch and dinner last orders, its Monday closing and its lack of parking, but it states no address or area, so it could not be placed in Nakagyo-ku.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: roujina0627 Second pass: the restaurant's own account was found and its profile gives its lunch and dinner last orders, its Monday closing and its lack of parking, but it states no address or area, so it could not be placed in Nakagyo-ku. Third pass: the audit list adds an address for this row (京都府京都市中京区丸屋町691) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O402" s="2" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="N403" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: warakumagazine Second pass: no account was found under this restaurant's name in Nakagyo-ku; the nearest name match is a Chinese restaurant with no stated address.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: warakumagazine Second pass: no account was found under this restaurant's name in Nakagyo-ku; the nearest name match is a Chinese restaurant with no stated address. Third pass: read the sources the audit list records for this row (https://intojapanwaraku.com/travel/254203/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O403" s="2" t="inlineStr">
@@ -27989,7 +27989,7 @@
       </c>
       <c r="N414" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banana_for_human_by_gorilla, berry._.button, hyde_and_away, kissa_me8, mimaruhotels, panelcafe_kyoto Second pass: no account was found under this shop's name in Gion; the results were other Gion sweets shops.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: banana_for_human_by_gorilla, berry._.button, hyde_and_away, kissa_me8, mimaruhotels, panelcafe_kyoto Second pass: no account was found under this shop's name in Gion; the results were other Gion sweets shops. Third pass: read the sources the audit list records for this row (https://hamoni.jp/area/kyoto/list/cafe-kissaten) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O414" s="2" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="N421" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yamamoto_kissa Second pass: no account was found under this cafe's name in Higashiyama-ku; the nearest name match is a liquor shop near Sanjo.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: yamamoto_kissa Second pass: no account was found under this cafe's name in Higashiyama-ku; the nearest name match is a liquor shop near Sanjo. Third pass: read the sources the audit list records for this row (https://hamoni.jp/shop/0M8ZOjJZxJfxlLCdqUCn) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O421" s="2" t="inlineStr">
@@ -29043,7 +29043,7 @@
       </c>
       <c r="N429" s="4" t="inlineStr">
         <is>
-          <t>The only account tying this name to Kyoto is the proprietor's personal account, whose profile describes him as the owner of Yakiniku Yamachan in Kyoto and a wine sommelier; it is a personal account, not the restaurant's own, and gives no address, so it is not recorded. Second pass: searched again with the ward name; the only account tying this name to Kyoto remains the proprietor's personal account, which gives no address, and the other name match is a restaurant in Ogaki, Gifu.</t>
+          <t>The only account tying this name to Kyoto is the proprietor's personal account, whose profile describes him as the owner of Yakiniku Yamachan in Kyoto and a wine sommelier; it is a personal account, not the restaurant's own, and gives no address, so it is not recorded. Second pass: searched again with the ward name; the only account tying this name to Kyoto remains the proprietor's personal account, which gives no address, and the other name match is a restaurant in Ogaki, Gifu. Third pass: the audit list adds an address for this row (京都府京都市中京区蛸屋町157-11) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O429" s="2" t="inlineStr">
@@ -29495,7 +29495,7 @@
       </c>
       <c r="N435" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: timeoutosaka_jp Second pass: the sign has no account of its own; the confectionery company that owns it runs product and shop accounts, and the Dotonbori traders' association account covers the whole street, so none is recorded.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: timeoutosaka_jp Second pass: the sign has no account of its own; the confectionery company that owns it runs product and shop accounts, and the Dotonbori traders' association account covers the whole street, so none is recorded. Third pass: read the sources the audit list records for this row (https://www.timeout.jp/osaka/ja/news/osakas-iconic-glico-sign-is-being-removed-for-renovations-102126) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O435" s="2" t="inlineStr">
@@ -29546,23 +29546,39 @@
           <t>https://www.google.com/maps/place/%E5%A4%A9%E7%A5%9E%E6%A9%8B%E7%AD%8B%E5%95%86%E5%BA%97%E8%A1%97/data=!4m2!3m1!1s0x6000e6b952436f4d:0x92f854ad19b70657</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr"/>
-      <c r="J436" t="inlineStr"/>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
-      <c r="M436" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tenjinbashi3choume/</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>tenjinbashi3choume</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>own-site</t>
+        </is>
+      </c>
+      <c r="M436" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. Only accounts of individual shops in the arcade were reached, not the arcade's own. Seen: tenjinbashi.ohagurumakou, tenjinbashi3choume Second pass: the arcade as a whole keeps no account; the only official account found belongs to its fourth block alone, so it was not recorded for this listing.</t>
+          <t>Third pass: the arcade's own site, tenjin3.com, which titles itself the official site of the Tenjinbashisuji arcade, links this account from a page that names the arcade. The account is the third-block association's, and the guide's listing covers the whole arcade from the first to the seventh block, so it is recorded as the shared association account rather than a single shop's.</t>
         </is>
       </c>
       <c r="O436" s="2" t="inlineStr">
         <is>
-          <t>https://tenjin3.com/</t>
+          <t>https://www.instagram.com/tenjinbashi3choume/</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
@@ -30027,7 +30043,7 @@
       </c>
       <c r="N443" s="4" t="inlineStr">
         <is>
-          <t>An account carrying this name as Sousaku Teppan Miraku exists and gives its lunch and dinner hours, but it states no address, so it could not be placed in Kita-ku; the other name match is in Yuzawa, Akita. Second pass: searched again by the fuller shop name; no account was found that places a restaurant of this name in Kita-ku, Osaka.</t>
+          <t>An account carrying this name as Sousaku Teppan Miraku exists and gives its lunch and dinner hours, but it states no address, so it could not be placed in Kita-ku; the other name match is in Yuzawa, Akita. Second pass: searched again by the fuller shop name; no account was found that places a restaurant of this name in Kita-ku, Osaka. Third pass: the audit list adds an address for this row (大阪市北区角田町9-25 新梅田食道街) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O443" s="2" t="inlineStr">
@@ -30535,7 +30551,7 @@
       </c>
       <c r="N451" s="4" t="inlineStr">
         <is>
-          <t>The restaurant's own account exists and gives its telephone number, whose 06-6458 exchange covers the Fukushima area, but the profile prints no address, so the area could not be confirmed from the profile itself. Second pass: searched again with the ward name; the restaurant's own account still gives only its booking telephone number and website, with no address, so the Fukushima-ku location could not be confirmed from the profile.</t>
+          <t>The restaurant's own account exists and gives its telephone number, whose 06-6458 exchange covers the Fukushima area, but the profile prints no address, so the area could not be confirmed from the profile itself. Second pass: searched again with the ward name; the restaurant's own account still gives only its booking telephone number and website, with no address, so the Fukushima-ku location could not be confirmed from the profile. Third pass: the audit list adds an address for this row (大阪市北区大淀南1-11-9 2F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O451" s="2" t="inlineStr">
@@ -30675,7 +30691,7 @@
       </c>
       <c r="N453" s="4" t="inlineStr">
         <is>
-          <t>The restaurant keeps an account for its Hanshin Umeda shop in Kita-ku, but no account was found for the Kitahorie main shop and no brand-level account exists, so none could be tied to this listing. Second pass: the only account for this restaurant places it in the basement of the Hanshin Umeda store in Kita-ku, with a sibling shop on the floor below, and not in Kitahorie where this listing places it.</t>
+          <t>The restaurant keeps an account for its Hanshin Umeda shop in Kita-ku, but no account was found for the Kitahorie main shop and no brand-level account exists, so none could be tied to this listing. Second pass: the only account for this restaurant places it in the basement of the Hanshin Umeda store in Kita-ku, with a sibling shop on the floor below, and not in Kitahorie where this listing places it. Third pass: the audit list adds an address for this row (大阪市西区北堀江1-17-11) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O453" t="inlineStr"/>
@@ -31333,7 +31349,7 @@
       </c>
       <c r="N462" s="4" t="inlineStr">
         <is>
-          <t>The only account carrying this shop's name is the proprietor Osamu Tomita's own account; it is a personal account rather than the shop's and gives no address, so it is not recorded. Second pass: searched again for a shop account; none exists - only the proprietor's own account and a ramen writer's page that lists the shop among his recommendations.</t>
+          <t>The only account carrying this shop's name is the proprietor Osamu Tomita's own account; it is a personal account rather than the shop's and gives no address, so it is not recorded. Second pass: searched again for a shop account; none exists - only the proprietor's own account and a ramen writer's page that lists the shop among his recommendations. Third pass: the audit list adds an address for this row (千葉県松戸市松戸1339 高橋ビル1F) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O462" s="2" t="inlineStr">
@@ -31380,23 +31396,39 @@
           <t>https://www.google.com/maps/place/BRISK%20STAND%20%E7%A5%9E%E6%88%B8%E6%9C%AC%E5%BA%97/data=!4m2!3m1!1s0x60008fef7bf32f5b:0x65304885c8f69bf4</t>
         </is>
       </c>
-      <c r="I463" t="inlineStr"/>
-      <c r="J463" t="inlineStr"/>
-      <c r="K463" t="inlineStr"/>
-      <c r="L463" t="inlineStr"/>
-      <c r="M463" s="6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/briskstand/</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>briskstand</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>own-site</t>
+        </is>
+      </c>
+      <c r="M463" s="5" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N463" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: briskstand, briskstand_asakusa Second pass: the chain keeps accounts for its Matsusaka, Sapporo, Sakai, Okazaki, Kyoto, Ebisu, Omotesando, Himeji, Tokushima and Kabukicho shops, and those profiles refer to the Kobe main shop's reputation, but no account for the Kobe main shop itself was found.</t>
+          <t>Third pass: the chain's own site links this brand account from its shop-list page. The second pass established that no account exists for the Kobe main shop itself, so the brand account is recorded as the operator's.</t>
         </is>
       </c>
       <c r="O463" s="2" t="inlineStr">
         <is>
-          <t>https://brisk-stand.com/shoplist</t>
+          <t>https://www.instagram.com/briskstand/</t>
         </is>
       </c>
       <c r="P463" t="inlineStr">
@@ -31689,7 +31721,7 @@
       </c>
       <c r="N468" s="4" t="inlineStr">
         <is>
-          <t>The restaurant's own account exists but its profile lists only its Kashii branches, with no Chiyo branch, so no account could be tied to this listing. Second pass: searched again with the ward name; the restaurant's own account still lists only its Kashii-area branches, and the sibling account gives no address, so neither could be tied to the Chiyo branch.</t>
+          <t>The restaurant's own account exists but its profile lists only its Kashii branches, with no Chiyo branch, so no account could be tied to this listing. Second pass: searched again with the ward name; the restaurant's own account still lists only its Kashii-area branches, and the sibling account gives no address, so neither could be tied to the Chiyo branch. Third pass: the audit list adds an address for this row (福岡県福岡市博多区千代3-48-9) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O468" s="2" t="inlineStr">
@@ -31913,7 +31945,7 @@
       </c>
       <c r="N472" s="4" t="inlineStr">
         <is>
-          <t>The chain keeps branch accounts for Mizonokuchi and Obihiro, and the Mizonokuchi profile names itself an offshoot of the Otaru main shop, but no account for the Otaru main shop itself was found. Second pass: the Mizonokuchi branch's account names itself an offshoot of the Otaru main shop and gives only its own address, and no account for the Otaru main shop was found.</t>
+          <t>The chain keeps branch accounts for Mizonokuchi and Obihiro, and the Mizonokuchi profile names itself an offshoot of the Otaru main shop, but no account for the Otaru main shop itself was found. Second pass: the Mizonokuchi branch's account names itself an offshoot of the Otaru main shop and gives only its own address, and no account for the Otaru main shop was found. Third pass: the audit list adds an address for this row (北海道小樽市花園1-10-7) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O472" t="inlineStr"/>
@@ -32553,7 +32585,7 @@
       </c>
       <c r="N482" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: cotaruco Second pass: no account was found under this shop's name in Otaru.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: cotaruco Second pass: no account was found under this shop's name in Otaru. Third pass: read the sources the audit list records for this row (https://www.cotaru.co/post/otaru-izakaya-guide) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O482" s="2" t="inlineStr">
@@ -32665,7 +32697,7 @@
       </c>
       <c r="N484" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: freehouse_the_yeast, voyapon Second pass: no account was found under this bar's name in Asahikawa; the name matches are bars and breweries in the United States and Singapore.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: freehouse_the_yeast, voyapon Second pass: no account was found under this bar's name in Asahikawa; the name matches are bars and breweries in the United States and Singapore. Third pass: read the sources the audit list records for this row (https://voyapon.com/spot-details/ChIJ9fJvfvbnDF8RVgzeZ4mY7AE/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O484" s="2" t="inlineStr">
@@ -33337,7 +33369,7 @@
       </c>
       <c r="N496" s="4" t="inlineStr">
         <is>
-          <t>The only account found for this shop belongs to its manager; it places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is a personal account rather than the shop's own, so it is not recorded. Second pass: the manager's account places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is the manager's own account rather than the shop's, so it is not recorded - the same rule applied to the other proprietor-run accounts in this ledger.</t>
+          <t>The only account found for this shop belongs to its manager; it places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is a personal account rather than the shop's own, so it is not recorded. Second pass: the manager's account places the shop in the 5-7 Koji Furarito lane at 5-jo-dori 7-chome, Asahikawa and dates it to 1950, but it is the manager's own account rather than the shop's, so it is not recorded - the same rule applied to the other proprietor-run accounts in this ledger. Third pass: the audit list adds an address for this row (北海道旭川市5条通7丁目 5・7小路ふらりーと) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O496" s="2" t="inlineStr">
@@ -34637,7 +34669,7 @@
       </c>
       <c r="N516" s="4" t="inlineStr">
         <is>
-          <t>An account for the restaurant's main shop exists and its profile describes a 75-year-old Kumamoto restaurant serving horse meat and local dishes, but it names no branch or address, so it could not be tied to the Suizenji shop. Second pass: searched again with the neighbourhood name; the account for the restaurant's main shop still gives no address or branch, so it could not be tied to the Suizenji shop.</t>
+          <t>An account for the restaurant's main shop exists and its profile describes a 75-year-old Kumamoto restaurant serving horse meat and local dishes, but it names no branch or address, so it could not be tied to the Suizenji shop. Second pass: searched again with the neighbourhood name; the account for the restaurant's main shop still gives no address or branch, so it could not be tied to the Suizenji shop. Third pass: the audit list adds an address for this row (熊本県熊本市中央区水前寺公園4-21) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O516" s="2" t="inlineStr">
@@ -34773,7 +34805,7 @@
       </c>
       <c r="N518" s="4" t="inlineStr">
         <is>
-          <t>Two accounts exist for facilities on this bathhouse's grounds in Hakuba - its car-stay park and its campsite - and both describe the spring's iron-rich water, but neither is the bathhouse's own account, so none is recorded. Second pass: searched again as a day-use bath; the only accounts on these grounds belong to the car-stay park and the campsite, not to the bathhouse itself, so none is recorded.</t>
+          <t>Two accounts exist for facilities on this bathhouse's grounds in Hakuba - its car-stay park and its campsite - and both describe the spring's iron-rich water, but neither is the bathhouse's own account, so none is recorded. Second pass: searched again as a day-use bath; the only accounts on these grounds belong to the car-stay park and the campsite, not to the bathhouse itself, so none is recorded. Third pass: the audit list adds an address for this row (長野県北安曇郡白馬村北城9549-8) but no source page, and the candidate account's profile prints no address to compare it with, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O518" t="inlineStr"/>
@@ -35083,7 +35115,7 @@
       </c>
       <c r="N523" s="4" t="inlineStr">
         <is>
-          <t>Reached a site through a directory page, but no account there corresponds to this venue. The account reached (fullmarks_official) belongs to an unrelated business. Seen: fullmarks_official Second pass: no account was found under this restaurant's name in Hakuba; the handle printed for it on a directory page belongs to an unrelated business.</t>
+          <t>Reached a site through a directory page, but no account there corresponds to this venue. The account reached (fullmarks_official) belongs to an unrelated business. Seen: fullmarks_official Second pass: no account was found under this restaurant's name in Hakuba; the handle printed for it on a directory page belongs to an unrelated business. Third pass: read the sources the audit list records for this row (https://www.full-marks.com/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O523" s="2" t="inlineStr">
@@ -35355,7 +35387,7 @@
       </c>
       <c r="N527" s="4" t="inlineStr">
         <is>
-          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: wez_kofu Second pass: no account was found under this shop's name in Showa-cho, Yamanashi.</t>
+          <t>An Instagram account is printed for this venue on a directory or media page, but it could not be confirmed on a page of the venue's own: no official website is on record and Instagram blocks unauthenticated profile reads. Printed: wez_kofu Second pass: no account was found under this shop's name in Showa-cho, Yamanashi. Third pass: read the sources the audit list records for this row (https://retty.me/restaurant/100001210103/) and followed the outbound links that could be the venue's own site; no page of the venue's own carries an Instagram link, so the second-pass verdict stands.</t>
         </is>
       </c>
       <c r="O527" s="2" t="inlineStr">
@@ -36300,181 +36332,183 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId926"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId927"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I507" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I524" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I507" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I524" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1099"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36510,7 +36544,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
@@ -36520,7 +36554,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4">
@@ -36550,7 +36584,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -36560,7 +36594,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -36597,7 +36631,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them, and all 111 rows that remained ambiguous have had a second per-venue pass; every row carries either a result or the reason none could be established</t>
+          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them; all 111 rows that remained ambiguous have had a second per-venue pass, and all of those still ambiguous a third pass that read the sources recorded in the 557-row Maps audit list; every row carries either a result or the reason none could be established</t>
         </is>
       </c>
     </row>

--- a/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
+++ b/artifacts/instagram-2026-10-29/ENCOUNTER_JAPAN_526_INSTAGRAM.xlsx
@@ -59,12 +59,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEADB"/>
+        <fgColor rgb="00FFF6E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6E0"/>
+        <fgColor rgb="00FFEADB"/>
       </patternFill>
     </fill>
   </fills>
@@ -648,39 +648,23 @@
           <t>https://www.google.com/maps/place/EMILIA/data=!4m2!3m1!1s0x60188cbd6947a727:0xfefe2077df059e06</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>根拠の再点検で保留に戻した行。このアカウントは当ガイドの既存のVisitor Essentials層が施設のウェブサイトとして記録していたもので、施設自身のページからリンクを確認したものではない。Essentials層の出典はhitosara.comの集約ページであり、集約ページに掲載されたアカウントは本調査の基準ではVERIFIEDに達しない。未ログインではプロフィールの再確認もできないため、候補として保留に戻す。 候補: emilia_jingumae</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/emilia_jingumae/</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>emilia_jingumae</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>own-site</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>The venue's own official website links to this Instagram account.</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/emilia_jingumae</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -742,7 +726,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -816,7 +800,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -928,7 +912,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -1164,7 +1148,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1238,7 +1222,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1474,7 +1458,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1602,7 +1586,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1676,7 +1660,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1750,7 +1734,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -1808,7 +1792,7 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -1878,7 +1862,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -2060,7 +2044,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -2118,7 +2102,7 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -2462,7 +2446,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -2590,7 +2574,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -2664,7 +2648,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -2846,7 +2830,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3028,7 +3012,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3102,7 +3086,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3230,7 +3214,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3520,7 +3504,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3648,7 +3632,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="M51" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3726,7 +3710,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -3908,7 +3892,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4036,7 +4020,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4110,7 +4094,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4184,7 +4168,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4312,7 +4296,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4386,7 +4370,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4460,7 +4444,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4534,7 +4518,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4592,7 +4576,7 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" s="6" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -4666,7 +4650,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
+      <c r="M66" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4740,7 +4724,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4814,7 +4798,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -4996,7 +4980,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5108,7 +5092,7 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="6" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -5182,7 +5166,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
+      <c r="M74" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5256,7 +5240,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
+      <c r="M75" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5330,7 +5314,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
+      <c r="M76" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5404,7 +5388,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
+      <c r="M77" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5462,7 +5446,7 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" s="6" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -5520,7 +5504,7 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" s="6" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -5740,7 +5724,7 @@
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" s="6" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -5814,7 +5798,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
+      <c r="M84" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -5872,7 +5856,7 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" s="6" t="inlineStr">
+      <c r="M85" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -5996,7 +5980,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
+      <c r="M87" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6070,7 +6054,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
+      <c r="M88" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6198,7 +6182,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
+      <c r="M90" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6272,7 +6256,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
+      <c r="M91" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6400,7 +6384,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
+      <c r="M93" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6512,7 +6496,7 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" s="6" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -6748,7 +6732,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M99" s="5" t="inlineStr">
+      <c r="M99" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6822,7 +6806,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
+      <c r="M100" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6896,7 +6880,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
+      <c r="M101" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -6970,7 +6954,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M102" s="5" t="inlineStr">
+      <c r="M102" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7044,7 +7028,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M103" s="5" t="inlineStr">
+      <c r="M103" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7118,7 +7102,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M104" s="5" t="inlineStr">
+      <c r="M104" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7192,7 +7176,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M105" s="5" t="inlineStr">
+      <c r="M105" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7266,7 +7250,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M106" s="5" t="inlineStr">
+      <c r="M106" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7432,7 +7416,7 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" s="6" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -7506,7 +7490,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M110" s="5" t="inlineStr">
+      <c r="M110" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7580,7 +7564,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
+      <c r="M111" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7654,7 +7638,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M112" s="5" t="inlineStr">
+      <c r="M112" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7728,7 +7712,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M113" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7802,7 +7786,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M114" s="5" t="inlineStr">
+      <c r="M114" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7876,7 +7860,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M115" s="5" t="inlineStr">
+      <c r="M115" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7950,7 +7934,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
+      <c r="M116" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8024,7 +8008,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M117" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8082,7 +8066,7 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" s="6" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -8318,7 +8302,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M122" s="5" t="inlineStr">
+      <c r="M122" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8392,7 +8376,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M123" s="5" t="inlineStr">
+      <c r="M123" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8466,7 +8450,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M124" s="5" t="inlineStr">
+      <c r="M124" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8540,7 +8524,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M125" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8614,7 +8598,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M126" s="5" t="inlineStr">
+      <c r="M126" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8688,7 +8672,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M127" s="5" t="inlineStr">
+      <c r="M127" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8924,7 +8908,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M131" s="5" t="inlineStr">
+      <c r="M131" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -8998,7 +8982,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M132" s="5" t="inlineStr">
+      <c r="M132" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9072,7 +9056,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M133" s="5" t="inlineStr">
+      <c r="M133" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9130,7 +9114,7 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" s="6" t="inlineStr">
+      <c r="M134" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9204,7 +9188,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M135" s="5" t="inlineStr">
+      <c r="M135" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9278,7 +9262,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M136" s="5" t="inlineStr">
+      <c r="M136" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9336,7 +9320,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" s="6" t="inlineStr">
+      <c r="M137" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9464,7 +9448,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9522,7 +9506,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" s="6" t="inlineStr">
+      <c r="M140" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9634,7 +9618,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
-      <c r="M142" s="6" t="inlineStr">
+      <c r="M142" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -9708,7 +9692,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M143" s="5" t="inlineStr">
+      <c r="M143" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9782,7 +9766,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M144" s="5" t="inlineStr">
+      <c r="M144" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9910,7 +9894,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M146" s="5" t="inlineStr">
+      <c r="M146" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -9984,7 +9968,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M147" s="5" t="inlineStr">
+      <c r="M147" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10042,7 +10026,7 @@
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" s="6" t="inlineStr">
+      <c r="M148" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -10100,7 +10084,7 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" s="6" t="inlineStr">
+      <c r="M149" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -10170,7 +10154,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M150" s="5" t="inlineStr">
+      <c r="M150" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10228,7 +10212,7 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" s="6" t="inlineStr">
+      <c r="M151" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -10302,7 +10286,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M152" s="5" t="inlineStr">
+      <c r="M152" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10380,7 +10364,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M153" s="5" t="inlineStr">
+      <c r="M153" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10442,7 +10426,7 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" s="6" t="inlineStr">
+      <c r="M154" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -10520,7 +10504,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M155" s="5" t="inlineStr">
+      <c r="M155" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10656,7 +10640,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M157" s="5" t="inlineStr">
+      <c r="M157" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10714,34 +10698,18 @@
           <t>https://www.google.com/maps/place/%E6%97%A5%E6%9C%AC%E9%85%92%E3%81%82%E3%81%95%E3%81%A3%E3%81%A6%2F%E9%AB%98%E5%86%86%E5%AF%BA/data=!4m2!3m1!1s0x6018f3a605962f19:0x197fd6a21002571b</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/asatte_nihonshu/</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>asatte_nihonshu</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>own-site</t>
-        </is>
-      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N158" s="4" t="inlineStr">
         <is>
-          <t>The venue's own official website links to this Instagram account.</t>
+          <t>根拠の再点検で保留に戻した行。このアカウントは当ガイドの既存のVisitor Essentials層が施設のウェブサイトとして記録していたもので、施設自身のページからリンクを確認したものではない。Essentials層の出典はsan-tatsu.jpの媒体ページであり、媒体ページに掲載されたアカウントは本調査の基準ではVERIFIEDに達しない。未ログインではプロフィールの再確認もできないため、候補として保留に戻す。 候補: asatte_nihonshu</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
@@ -10812,7 +10780,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M159" s="5" t="inlineStr">
+      <c r="M159" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -10944,7 +10912,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M161" s="5" t="inlineStr">
+      <c r="M161" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11022,7 +10990,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M162" s="5" t="inlineStr">
+      <c r="M162" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11096,7 +11064,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M163" s="5" t="inlineStr">
+      <c r="M163" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11348,7 +11316,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M167" s="5" t="inlineStr">
+      <c r="M167" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11406,7 +11374,7 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
-      <c r="M168" s="6" t="inlineStr">
+      <c r="M168" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -11584,7 +11552,7 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
-      <c r="M171" s="6" t="inlineStr">
+      <c r="M171" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -11662,7 +11630,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M172" s="5" t="inlineStr">
+      <c r="M172" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11740,7 +11708,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M173" s="5" t="inlineStr">
+      <c r="M173" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11814,7 +11782,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M174" s="5" t="inlineStr">
+      <c r="M174" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11888,7 +11856,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M175" s="5" t="inlineStr">
+      <c r="M175" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -11962,7 +11930,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M176" s="5" t="inlineStr">
+      <c r="M176" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12094,7 +12062,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M178" s="5" t="inlineStr">
+      <c r="M178" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12172,7 +12140,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M179" s="5" t="inlineStr">
+      <c r="M179" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12250,7 +12218,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M180" s="5" t="inlineStr">
+      <c r="M180" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12328,7 +12296,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M181" s="5" t="inlineStr">
+      <c r="M181" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12402,7 +12370,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M182" s="5" t="inlineStr">
+      <c r="M182" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12476,7 +12444,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M183" s="5" t="inlineStr">
+      <c r="M183" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12608,7 +12576,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M185" s="5" t="inlineStr">
+      <c r="M185" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12790,7 +12758,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M188" s="5" t="inlineStr">
+      <c r="M188" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -12980,7 +12948,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M191" s="5" t="inlineStr">
+      <c r="M191" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13058,7 +13026,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M192" s="5" t="inlineStr">
+      <c r="M192" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13236,7 +13204,7 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
-      <c r="M195" s="6" t="inlineStr">
+      <c r="M195" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -13314,7 +13282,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M196" s="5" t="inlineStr">
+      <c r="M196" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13376,7 +13344,7 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
-      <c r="M197" s="6" t="inlineStr">
+      <c r="M197" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -13454,7 +13422,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M198" s="5" t="inlineStr">
+      <c r="M198" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13748,7 +13716,7 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
-      <c r="M203" s="6" t="inlineStr">
+      <c r="M203" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -13826,7 +13794,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M204" s="5" t="inlineStr">
+      <c r="M204" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -13962,7 +13930,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M206" s="5" t="inlineStr">
+      <c r="M206" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14098,7 +14066,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M208" s="5" t="inlineStr">
+      <c r="M208" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14176,7 +14144,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M209" s="5" t="inlineStr">
+      <c r="M209" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14254,7 +14222,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M210" s="5" t="inlineStr">
+      <c r="M210" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14390,7 +14358,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M212" s="5" t="inlineStr">
+      <c r="M212" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14468,7 +14436,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M213" s="5" t="inlineStr">
+      <c r="M213" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14546,7 +14514,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M214" s="5" t="inlineStr">
+      <c r="M214" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14682,7 +14650,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M216" s="5" t="inlineStr">
+      <c r="M216" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14760,7 +14728,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M217" s="5" t="inlineStr">
+      <c r="M217" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14838,7 +14806,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M218" s="5" t="inlineStr">
+      <c r="M218" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14916,7 +14884,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M219" s="5" t="inlineStr">
+      <c r="M219" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -14994,7 +14962,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M220" s="5" t="inlineStr">
+      <c r="M220" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15072,7 +15040,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M221" s="5" t="inlineStr">
+      <c r="M221" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15150,7 +15118,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M222" s="5" t="inlineStr">
+      <c r="M222" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15286,7 +15254,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M224" s="5" t="inlineStr">
+      <c r="M224" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15364,7 +15332,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M225" s="5" t="inlineStr">
+      <c r="M225" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15442,7 +15410,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M226" s="5" t="inlineStr">
+      <c r="M226" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15520,7 +15488,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M227" s="5" t="inlineStr">
+      <c r="M227" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15598,7 +15566,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M228" s="5" t="inlineStr">
+      <c r="M228" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15676,7 +15644,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M229" s="5" t="inlineStr">
+      <c r="M229" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15754,7 +15722,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M230" s="5" t="inlineStr">
+      <c r="M230" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -15832,7 +15800,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M231" s="5" t="inlineStr">
+      <c r="M231" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -16084,7 +16052,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M235" s="5" t="inlineStr">
+      <c r="M235" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -16158,7 +16126,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M236" s="5" t="inlineStr">
+      <c r="M236" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -16410,7 +16378,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M240" s="5" t="inlineStr">
+      <c r="M240" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -16642,34 +16610,18 @@
           <t>https://www.google.com/maps/place/%E6%97%A5%E6%9C%AC%E9%85%92mekkemon+(%E3%82%81%E3%81%A3%E3%81%91%E3%82%82%E3%82%93)/data=!4m2!3m1!1s0x60188ba4ac861705:0x2aaaf28a33dbc54</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tetsuryu100/</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>tetsuryu100</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t>profile</t>
-        </is>
-      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
       <c r="M244" s="5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N244" s="4" t="inlineStr">
         <is>
-          <t>The bar's own account; its profile describes a junmai-sake specialist in Ginza 6-chome open from 18:00 and closed Sundays, matching this listing.</t>
+          <t>根拠の再点検で保留に戻した行。記録していた根拠は『銀座6丁目の純米酒専門店、18時開店、日曜定休』というプロフィール記載のみで、プロフィールが当店名を名乗っている記録がなく、ハンドル名も店名と対応しない。銀座6丁目には同種の店が複数あり、この記載だけでは同名・類似店との取り違えを排除できない。未ログインではプロフィールの再確認ができないため保留に戻す。 候補: tetsuryu100</t>
         </is>
       </c>
       <c r="O244" s="2" t="inlineStr">
@@ -16856,7 +16808,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M247" s="5" t="inlineStr">
+      <c r="M247" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -16988,7 +16940,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M249" s="5" t="inlineStr">
+      <c r="M249" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17066,7 +17018,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M250" s="5" t="inlineStr">
+      <c r="M250" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17124,39 +17076,23 @@
           <t>https://www.google.com/maps/place/%E3%83%92%E3%82%AB%E3%83%AA%E3%83%A2%E3%83%8E+%E9%AE%A8%E3%81%A8%E3%83%84%E3%83%9E%E3%83%9F+%E5%85%AD%E6%9C%AC%E6%9C%A8/data=!4m2!3m1!1s0x60188bebcee02321:0xe6bae90c9b1080cb</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" s="5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="N251" s="4" t="inlineStr">
+        <is>
+          <t>根拠の再点検で保留に戻した行。記録されていた@tablecheck_globalは予約プラットフォームTableCheck自身のアカウントであり、この店舗のアカウントではない。根拠URLも同プラットフォームの店舗ページで、施設自身のページではなかった。店舗自身のアカウントは未発見。 候補: tablecheck_global</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
         <is>
           <t>https://www.instagram.com/tablecheck_global/</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>tablecheck_global</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t>own-site</t>
-        </is>
-      </c>
-      <c r="M251" s="5" t="inlineStr">
-        <is>
-          <t>VERIFIED</t>
-        </is>
-      </c>
-      <c r="N251" s="4" t="inlineStr">
-        <is>
-          <t>The venue's own official website links to this Instagram account.</t>
-        </is>
-      </c>
-      <c r="O251" s="2" t="inlineStr">
-        <is>
-          <t>https://www.tablecheck.com/ja/hikarimono</t>
         </is>
       </c>
       <c r="P251" t="inlineStr">
@@ -17218,7 +17154,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M252" s="5" t="inlineStr">
+      <c r="M252" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17276,7 +17212,7 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
-      <c r="M253" s="6" t="inlineStr">
+      <c r="M253" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -17354,7 +17290,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M254" s="5" t="inlineStr">
+      <c r="M254" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17606,7 +17542,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M258" s="5" t="inlineStr">
+      <c r="M258" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17718,34 +17654,18 @@
           <t>https://www.google.com/maps/place/Hi-Fi+Disco+Bar+Chaos/data=!4m2!3m1!1s0x60188d918804255b:0x39102c0807b79bec</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hifi_disco_bar_chaos/</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>hifi_disco_bar_chaos</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>own-site</t>
-        </is>
-      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
       <c r="M260" s="5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N260" s="4" t="inlineStr">
         <is>
-          <t>The venue's own official website links to this Instagram account.</t>
+          <t>根拠の再点検で保留に戻した行。このアカウントは当ガイドの既存のVisitor Essentials層が施設のウェブサイトとして記録していたもので、施設自身のページからリンクを確認したものではない。Essentials層の出典はragnet.co.jpの集約ページであり、集約ページに掲載されたアカウントは本調査の基準ではVERIFIEDに達しない。未ログインではプロフィールの再確認もできないため、候補として保留に戻す。 候補: hifi_disco_bar_chaos</t>
         </is>
       </c>
       <c r="O260" s="2" t="inlineStr">
@@ -17870,7 +17790,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M262" s="5" t="inlineStr">
+      <c r="M262" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -17928,7 +17848,7 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
-      <c r="M263" s="6" t="inlineStr">
+      <c r="M263" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18002,7 +17922,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M264" s="5" t="inlineStr">
+      <c r="M264" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18080,7 +18000,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M265" s="5" t="inlineStr">
+      <c r="M265" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18138,7 +18058,7 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
-      <c r="M266" s="6" t="inlineStr">
+      <c r="M266" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18216,7 +18136,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M267" s="5" t="inlineStr">
+      <c r="M267" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18352,7 +18272,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M269" s="5" t="inlineStr">
+      <c r="M269" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18430,7 +18350,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M270" s="5" t="inlineStr">
+      <c r="M270" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18492,7 +18412,7 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
-      <c r="M271" s="6" t="inlineStr">
+      <c r="M271" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -18570,7 +18490,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M272" s="5" t="inlineStr">
+      <c r="M272" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18648,7 +18568,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M273" s="5" t="inlineStr">
+      <c r="M273" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -18702,34 +18622,18 @@
           <t>https://www.google.com/maps/place/First+Crop+Coffee+Japan+Roastery/data=!4m2!3m1!1s0x60188900727c9657:0x2b433b13ed06d66a</t>
         </is>
       </c>
-      <c r="I274" s="2" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fccjp.roastery/</t>
-        </is>
-      </c>
-      <c r="J274" t="inlineStr">
-        <is>
-          <t>fccjp.roastery</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>store</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr">
-        <is>
-          <t>own-site</t>
-        </is>
-      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
       <c r="M274" s="5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="N274" s="4" t="inlineStr">
         <is>
-          <t>The venue's own official website links to this Instagram account.</t>
+          <t>根拠の再点検で保留に戻した行。このアカウントは当ガイドの既存のVisitor Essentials層が施設のウェブサイトとして記録していたもので、施設自身のページからリンクを確認したものではない。Essentials層の出典はsan-tatsu.jpとcafesnap.meの集約ページであり、集約ページに掲載されたアカウントは本調査の基準ではVERIFIEDに達しない。未ログインではプロフィールの再確認もできないため、候補として保留に戻す。 候補: fccjp.roastery</t>
         </is>
       </c>
       <c r="O274" s="2" t="inlineStr">
@@ -19032,7 +18936,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M279" s="5" t="inlineStr">
+      <c r="M279" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -19400,7 +19304,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M285" s="5" t="inlineStr">
+      <c r="M285" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -19478,7 +19382,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M286" s="5" t="inlineStr">
+      <c r="M286" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -19540,7 +19444,7 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
-      <c r="M287" s="6" t="inlineStr">
+      <c r="M287" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19618,7 +19522,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M288" s="5" t="inlineStr">
+      <c r="M288" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -19676,7 +19580,7 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
-      <c r="M289" s="6" t="inlineStr">
+      <c r="M289" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19754,7 +19658,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M290" s="5" t="inlineStr">
+      <c r="M290" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -19816,7 +19720,7 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
-      <c r="M291" s="6" t="inlineStr">
+      <c r="M291" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -19994,7 +19898,7 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr"/>
       <c r="L294" t="inlineStr"/>
-      <c r="M294" s="6" t="inlineStr">
+      <c r="M294" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20130,7 +20034,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M296" s="5" t="inlineStr">
+      <c r="M296" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20204,7 +20108,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M297" s="5" t="inlineStr">
+      <c r="M297" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20394,7 +20298,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M300" s="5" t="inlineStr">
+      <c r="M300" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20452,7 +20356,7 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr"/>
       <c r="L301" t="inlineStr"/>
-      <c r="M301" s="6" t="inlineStr">
+      <c r="M301" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20568,7 +20472,7 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr"/>
-      <c r="M303" s="6" t="inlineStr">
+      <c r="M303" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -20642,7 +20546,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M304" s="5" t="inlineStr">
+      <c r="M304" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20774,7 +20678,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M306" s="5" t="inlineStr">
+      <c r="M306" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20852,7 +20756,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M307" s="5" t="inlineStr">
+      <c r="M307" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -20930,7 +20834,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M308" s="5" t="inlineStr">
+      <c r="M308" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21050,7 +20954,7 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
-      <c r="M310" s="6" t="inlineStr">
+      <c r="M310" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -21182,7 +21086,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M312" s="5" t="inlineStr">
+      <c r="M312" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21260,7 +21164,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M313" s="5" t="inlineStr">
+      <c r="M313" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21338,7 +21242,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M314" s="5" t="inlineStr">
+      <c r="M314" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21416,7 +21320,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M315" s="5" t="inlineStr">
+      <c r="M315" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21726,7 +21630,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M320" s="5" t="inlineStr">
+      <c r="M320" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -21788,7 +21692,7 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
-      <c r="M321" s="6" t="inlineStr">
+      <c r="M321" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -21908,7 +21812,7 @@
       <c r="J323" t="inlineStr"/>
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr"/>
-      <c r="M323" s="6" t="inlineStr">
+      <c r="M323" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -22102,7 +22006,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M326" s="5" t="inlineStr">
+      <c r="M326" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22176,7 +22080,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M327" s="5" t="inlineStr">
+      <c r="M327" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22358,7 +22262,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M330" s="5" t="inlineStr">
+      <c r="M330" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22432,7 +22336,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M331" s="5" t="inlineStr">
+      <c r="M331" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22490,7 +22394,7 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr"/>
-      <c r="M332" s="6" t="inlineStr">
+      <c r="M332" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -22614,7 +22518,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M334" s="5" t="inlineStr">
+      <c r="M334" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22688,7 +22592,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M335" s="5" t="inlineStr">
+      <c r="M335" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22762,7 +22666,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M336" s="5" t="inlineStr">
+      <c r="M336" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22836,7 +22740,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M337" s="5" t="inlineStr">
+      <c r="M337" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22910,7 +22814,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M338" s="5" t="inlineStr">
+      <c r="M338" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -22984,7 +22888,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M339" s="5" t="inlineStr">
+      <c r="M339" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23058,7 +22962,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M340" s="5" t="inlineStr">
+      <c r="M340" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23132,7 +23036,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M341" s="5" t="inlineStr">
+      <c r="M341" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23298,7 +23202,7 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
-      <c r="M344" s="6" t="inlineStr">
+      <c r="M344" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -23356,7 +23260,7 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
-      <c r="M345" s="6" t="inlineStr">
+      <c r="M345" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -23414,7 +23318,7 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
-      <c r="M346" s="6" t="inlineStr">
+      <c r="M346" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -23488,7 +23392,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M347" s="5" t="inlineStr">
+      <c r="M347" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23616,7 +23520,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M349" s="5" t="inlineStr">
+      <c r="M349" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23690,7 +23594,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M350" s="5" t="inlineStr">
+      <c r="M350" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23764,7 +23668,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M351" s="5" t="inlineStr">
+      <c r="M351" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -23838,7 +23742,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M352" s="5" t="inlineStr">
+      <c r="M352" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24020,7 +23924,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M355" s="5" t="inlineStr">
+      <c r="M355" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24094,7 +23998,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M356" s="5" t="inlineStr">
+      <c r="M356" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24152,7 +24056,7 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
-      <c r="M357" s="6" t="inlineStr">
+      <c r="M357" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -24230,7 +24134,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M358" s="5" t="inlineStr">
+      <c r="M358" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24308,7 +24212,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M359" s="5" t="inlineStr">
+      <c r="M359" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24386,7 +24290,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M360" s="5" t="inlineStr">
+      <c r="M360" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24448,7 +24352,7 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
-      <c r="M361" s="6" t="inlineStr">
+      <c r="M361" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -24510,7 +24414,7 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
-      <c r="M362" s="6" t="inlineStr">
+      <c r="M362" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -24588,7 +24492,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M363" s="5" t="inlineStr">
+      <c r="M363" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -24782,7 +24686,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M366" s="5" t="inlineStr">
+      <c r="M366" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -25018,7 +24922,7 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr"/>
-      <c r="M370" s="6" t="inlineStr">
+      <c r="M370" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -25080,7 +24984,7 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr"/>
-      <c r="M371" s="6" t="inlineStr">
+      <c r="M371" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -25316,7 +25220,7 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
-      <c r="M375" s="6" t="inlineStr">
+      <c r="M375" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -25548,7 +25452,7 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
-      <c r="M379" s="6" t="inlineStr">
+      <c r="M379" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -25626,7 +25530,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M380" s="5" t="inlineStr">
+      <c r="M380" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -25758,7 +25662,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M382" s="5" t="inlineStr">
+      <c r="M382" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -25894,7 +25798,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M384" s="5" t="inlineStr">
+      <c r="M384" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -25972,7 +25876,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M385" s="5" t="inlineStr">
+      <c r="M385" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26050,7 +25954,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M386" s="5" t="inlineStr">
+      <c r="M386" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26128,7 +26032,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M387" s="5" t="inlineStr">
+      <c r="M387" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26264,7 +26168,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M389" s="5" t="inlineStr">
+      <c r="M389" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26342,7 +26246,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M390" s="5" t="inlineStr">
+      <c r="M390" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26420,7 +26324,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M391" s="5" t="inlineStr">
+      <c r="M391" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26614,7 +26518,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M394" s="5" t="inlineStr">
+      <c r="M394" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26692,7 +26596,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M395" s="5" t="inlineStr">
+      <c r="M395" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26770,7 +26674,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M396" s="5" t="inlineStr">
+      <c r="M396" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26848,7 +26752,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M397" s="5" t="inlineStr">
+      <c r="M397" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -26926,7 +26830,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M398" s="5" t="inlineStr">
+      <c r="M398" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27004,7 +26908,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M399" s="5" t="inlineStr">
+      <c r="M399" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27140,7 +27044,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M401" s="5" t="inlineStr">
+      <c r="M401" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27202,7 +27106,7 @@
       <c r="J402" t="inlineStr"/>
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
-      <c r="M402" s="6" t="inlineStr">
+      <c r="M402" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -27264,7 +27168,7 @@
       <c r="J403" t="inlineStr"/>
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
-      <c r="M403" s="6" t="inlineStr">
+      <c r="M403" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -27342,7 +27246,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M404" s="5" t="inlineStr">
+      <c r="M404" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27532,7 +27436,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M407" s="5" t="inlineStr">
+      <c r="M407" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27668,7 +27572,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M409" s="5" t="inlineStr">
+      <c r="M409" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27862,7 +27766,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M412" s="5" t="inlineStr">
+      <c r="M412" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -27982,7 +27886,7 @@
       <c r="J414" t="inlineStr"/>
       <c r="K414" t="inlineStr"/>
       <c r="L414" t="inlineStr"/>
-      <c r="M414" s="6" t="inlineStr">
+      <c r="M414" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -28060,7 +27964,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M415" s="5" t="inlineStr">
+      <c r="M415" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28138,7 +28042,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M416" s="5" t="inlineStr">
+      <c r="M416" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28274,7 +28178,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M418" s="5" t="inlineStr">
+      <c r="M418" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28352,7 +28256,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M419" s="5" t="inlineStr">
+      <c r="M419" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28430,7 +28334,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M420" s="5" t="inlineStr">
+      <c r="M420" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28492,7 +28396,7 @@
       <c r="J421" t="inlineStr"/>
       <c r="K421" t="inlineStr"/>
       <c r="L421" t="inlineStr"/>
-      <c r="M421" s="6" t="inlineStr">
+      <c r="M421" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -28570,7 +28474,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M422" s="5" t="inlineStr">
+      <c r="M422" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28706,7 +28610,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M424" s="5" t="inlineStr">
+      <c r="M424" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28900,7 +28804,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M427" s="5" t="inlineStr">
+      <c r="M427" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -28978,7 +28882,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M428" s="5" t="inlineStr">
+      <c r="M428" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29036,7 +28940,7 @@
       <c r="J429" t="inlineStr"/>
       <c r="K429" t="inlineStr"/>
       <c r="L429" t="inlineStr"/>
-      <c r="M429" s="6" t="inlineStr">
+      <c r="M429" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -29114,7 +29018,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M430" s="5" t="inlineStr">
+      <c r="M430" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29192,7 +29096,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M431" s="5" t="inlineStr">
+      <c r="M431" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29270,7 +29174,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M432" s="5" t="inlineStr">
+      <c r="M432" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29348,7 +29252,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M433" s="5" t="inlineStr">
+      <c r="M433" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29426,7 +29330,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M434" s="5" t="inlineStr">
+      <c r="M434" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29488,7 +29392,7 @@
       <c r="J435" t="inlineStr"/>
       <c r="K435" t="inlineStr"/>
       <c r="L435" t="inlineStr"/>
-      <c r="M435" s="6" t="inlineStr">
+      <c r="M435" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -29566,19 +29470,19 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M436" s="5" t="inlineStr">
+      <c r="M436" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
       <c r="N436" s="4" t="inlineStr">
         <is>
-          <t>Third pass: the arcade's own site, tenjin3.com, which titles itself the official site of the Tenjinbashisuji arcade, links this account from a page that names the arcade. The account is the third-block association's, and the guide's listing covers the whole arcade from the first to the seventh block, so it is recorded as the shared association account rather than a single shop's.</t>
+          <t>第3次調査：商店街自身のサイト tenjin3.com（ページ表題が「天神橋筋商店街・天神橋三丁目商店街【公式】」）が、商店街名を記載したページからこのアカウントをリンクしている。根拠URLはそのページ。アカウントは三丁目商店街会のもので、当台帳の掲載は1〜7丁目の商店街全体にあたるため、単一店舗ではなく商店街会の共有アカウントとして記録し、範囲の違いを明記する。1〜7丁目全体の公式アカウントではない。</t>
         </is>
       </c>
       <c r="O436" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tenjinbashi3choume/</t>
+          <t>https://tenjin3.com/</t>
         </is>
       </c>
       <c r="P436" t="inlineStr">
@@ -29644,7 +29548,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M437" s="5" t="inlineStr">
+      <c r="M437" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29722,7 +29626,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M438" s="5" t="inlineStr">
+      <c r="M438" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -29858,7 +29762,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M440" s="5" t="inlineStr">
+      <c r="M440" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30036,7 +29940,7 @@
       <c r="J443" t="inlineStr"/>
       <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
-      <c r="M443" s="6" t="inlineStr">
+      <c r="M443" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -30114,7 +30018,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M444" s="5" t="inlineStr">
+      <c r="M444" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30188,7 +30092,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M445" s="5" t="inlineStr">
+      <c r="M445" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30482,7 +30386,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M450" s="5" t="inlineStr">
+      <c r="M450" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30544,7 +30448,7 @@
       <c r="J451" t="inlineStr"/>
       <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr"/>
-      <c r="M451" s="6" t="inlineStr">
+      <c r="M451" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -30622,7 +30526,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M452" s="5" t="inlineStr">
+      <c r="M452" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30684,7 +30588,7 @@
       <c r="J453" t="inlineStr"/>
       <c r="K453" t="inlineStr"/>
       <c r="L453" t="inlineStr"/>
-      <c r="M453" s="6" t="inlineStr">
+      <c r="M453" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -30758,7 +30662,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M454" s="5" t="inlineStr">
+      <c r="M454" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30894,7 +30798,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M456" s="5" t="inlineStr">
+      <c r="M456" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -30972,7 +30876,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M457" s="5" t="inlineStr">
+      <c r="M457" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31050,7 +30954,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M458" s="5" t="inlineStr">
+      <c r="M458" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31124,7 +31028,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M459" s="5" t="inlineStr">
+      <c r="M459" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31202,7 +31106,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M460" s="5" t="inlineStr">
+      <c r="M460" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31280,7 +31184,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M461" s="5" t="inlineStr">
+      <c r="M461" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31342,7 +31246,7 @@
       <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
-      <c r="M462" s="6" t="inlineStr">
+      <c r="M462" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -31416,19 +31320,19 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M463" s="5" t="inlineStr">
+      <c r="M463" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
       <c r="N463" s="4" t="inlineStr">
         <is>
-          <t>Third pass: the chain's own site links this brand account from its shop-list page. The second pass established that no account exists for the Kobe main shop itself, so the brand account is recorded as the operator's.</t>
+          <t>第3次調査：ブランド自身のサイト brisk-stand.com の店舗一覧ページがこのブランドアカウントをリンクしている。根拠URLはそのページ。第2次調査で神戸本店固有のアカウントが存在しないことを確認済みのため、店舗専用ではなくブランド共通アカウントとして記録する。</t>
         </is>
       </c>
       <c r="O463" s="2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/briskstand/</t>
+          <t>https://brisk-stand.com/shoplist</t>
         </is>
       </c>
       <c r="P463" t="inlineStr">
@@ -31490,7 +31394,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M464" s="5" t="inlineStr">
+      <c r="M464" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -31714,7 +31618,7 @@
       <c r="J468" t="inlineStr"/>
       <c r="K468" t="inlineStr"/>
       <c r="L468" t="inlineStr"/>
-      <c r="M468" s="6" t="inlineStr">
+      <c r="M468" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -31938,7 +31842,7 @@
       <c r="J472" t="inlineStr"/>
       <c r="K472" t="inlineStr"/>
       <c r="L472" t="inlineStr"/>
-      <c r="M472" s="6" t="inlineStr">
+      <c r="M472" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -32062,7 +31966,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M474" s="5" t="inlineStr">
+      <c r="M474" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -32190,7 +32094,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M476" s="5" t="inlineStr">
+      <c r="M476" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -32318,7 +32222,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M478" s="5" t="inlineStr">
+      <c r="M478" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -32392,7 +32296,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M479" s="5" t="inlineStr">
+      <c r="M479" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -32466,7 +32370,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M480" s="5" t="inlineStr">
+      <c r="M480" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -32578,7 +32482,7 @@
       <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr"/>
-      <c r="M482" s="6" t="inlineStr">
+      <c r="M482" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -32690,7 +32594,7 @@
       <c r="J484" t="inlineStr"/>
       <c r="K484" t="inlineStr"/>
       <c r="L484" t="inlineStr"/>
-      <c r="M484" s="6" t="inlineStr">
+      <c r="M484" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -33088,7 +32992,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M491" s="5" t="inlineStr">
+      <c r="M491" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -33362,7 +33266,7 @@
       <c r="J496" t="inlineStr"/>
       <c r="K496" t="inlineStr"/>
       <c r="L496" t="inlineStr"/>
-      <c r="M496" s="6" t="inlineStr">
+      <c r="M496" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -33436,7 +33340,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M497" s="5" t="inlineStr">
+      <c r="M497" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -33672,7 +33576,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M501" s="5" t="inlineStr">
+      <c r="M501" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -33746,7 +33650,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M502" s="5" t="inlineStr">
+      <c r="M502" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -33820,7 +33724,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M503" s="5" t="inlineStr">
+      <c r="M503" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -33894,7 +33798,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M504" s="5" t="inlineStr">
+      <c r="M504" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34026,7 +33930,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M506" s="5" t="inlineStr">
+      <c r="M506" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34100,7 +34004,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M507" s="5" t="inlineStr">
+      <c r="M507" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34340,7 +34244,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M511" s="5" t="inlineStr">
+      <c r="M511" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34414,7 +34318,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M512" s="5" t="inlineStr">
+      <c r="M512" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34488,7 +34392,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M513" s="5" t="inlineStr">
+      <c r="M513" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34662,7 +34566,7 @@
       <c r="J516" t="inlineStr"/>
       <c r="K516" t="inlineStr"/>
       <c r="L516" t="inlineStr"/>
-      <c r="M516" s="6" t="inlineStr">
+      <c r="M516" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -34740,7 +34644,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M517" s="5" t="inlineStr">
+      <c r="M517" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34798,7 +34702,7 @@
       <c r="J518" t="inlineStr"/>
       <c r="K518" t="inlineStr"/>
       <c r="L518" t="inlineStr"/>
-      <c r="M518" s="6" t="inlineStr">
+      <c r="M518" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -34868,7 +34772,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M519" s="5" t="inlineStr">
+      <c r="M519" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -34942,7 +34846,7 @@
           <t>own-site</t>
         </is>
       </c>
-      <c r="M520" s="5" t="inlineStr">
+      <c r="M520" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -35108,7 +35012,7 @@
       <c r="J523" t="inlineStr"/>
       <c r="K523" t="inlineStr"/>
       <c r="L523" t="inlineStr"/>
-      <c r="M523" s="6" t="inlineStr">
+      <c r="M523" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -35182,7 +35086,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M524" s="5" t="inlineStr">
+      <c r="M524" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -35260,7 +35164,7 @@
           <t>profile</t>
         </is>
       </c>
-      <c r="M525" s="5" t="inlineStr">
+      <c r="M525" s="6" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -35380,7 +35284,7 @@
       <c r="J527" t="inlineStr"/>
       <c r="K527" t="inlineStr"/>
       <c r="L527" t="inlineStr"/>
-      <c r="M527" s="6" t="inlineStr">
+      <c r="M527" s="5" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
@@ -35406,1109 +35310,1103 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I260" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId731"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId732"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId733"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId734"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId735"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId736"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId737"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId738"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId739"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId740"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId741"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId742"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId743"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId744"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId745"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId746"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId747"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId748"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId749"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId750"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId751"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId752"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId753"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId754"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId755"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId756"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId757"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId758"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId759"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId760"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId761"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId762"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId763"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId764"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId765"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId766"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId767"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId768"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId769"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId770"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId771"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId772"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId773"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId774"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId775"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId776"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId777"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId778"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId779"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId780"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId781"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId782"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId783"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId784"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId785"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId786"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId787"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId788"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId789"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId790"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId791"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId792"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId793"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId794"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId795"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId796"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId797"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId798"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId799"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId800"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId801"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId802"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId803"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId804"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId805"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId806"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId807"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId808"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId809"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId810"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId811"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId812"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId813"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId814"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId815"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId816"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId817"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId818"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId819"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId820"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId821"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId822"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId823"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId824"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId825"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId826"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId827"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId828"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId829"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId830"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId831"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId832"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId833"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId834"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId835"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId836"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId837"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId838"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId839"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId840"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId841"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId842"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId843"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId844"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId845"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId846"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId847"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId848"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId849"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId850"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId851"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId852"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId853"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId854"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId855"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId856"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId857"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId858"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId859"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId860"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId861"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId862"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId863"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId864"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId865"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId866"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId867"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId868"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId869"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId870"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId871"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId872"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId873"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId874"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId875"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId876"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId877"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId878"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId879"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId880"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId881"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId882"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId883"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId884"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId885"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId886"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId887"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId888"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId889"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId890"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId891"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId892"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId893"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId894"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId895"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId896"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId897"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId898"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId899"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId900"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId901"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId902"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId903"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId904"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId905"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId906"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId907"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId908"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId909"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId910"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId911"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId912"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId913"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId915"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId916"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId917"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId918"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId919"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId920"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I433" r:id="rId921"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId922"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId923"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId924"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId925"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId926"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId927"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId928"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId929"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId930"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId931"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId932"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId933"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId934"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId935"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId936"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId937"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId938"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId939"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId940"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId941"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId942"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId943"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId944"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId945"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId946"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId947"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId948"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId949"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId950"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId951"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId952"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId953"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId954"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId955"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId956"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId957"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId958"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId959"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId960"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId961"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId962"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId963"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId964"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId965"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId966"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId967"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId968"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId969"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId970"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId971"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId972"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId973"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId974"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId975"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId976"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId977"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId978"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId979"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId980"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId981"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId982"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId983"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId984"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId985"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId986"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId987"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId988"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId989"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId990"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId991"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId992"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId993"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId994"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId995"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId996"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId997"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId998"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId999"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId1000"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId1001"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId1002"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId1003"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId1004"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId1005"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId1006"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId1007"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId1008"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId1009"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId1010"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId1011"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId1012"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId1013"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId1014"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId1015"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId1016"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId1017"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId1018"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId1019"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId1020"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId1021"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId1022"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId1023"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId1024"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId1025"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1026"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId1027"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId1028"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId1029"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId1030"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId1031"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId1032"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId1033"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId1034"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1035"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId1036"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId1037"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId1038"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId1039"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId1040"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1041"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1042"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1043"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1044"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1045"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1046"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1047"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1048"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1049"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1050"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1051"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId1052"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1053"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1054"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1055"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1056"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1057"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId1058"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1059"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1060"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1061"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1062"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1063"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1064"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I507" r:id="rId1065"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1066"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1067"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1068"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1069"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1070"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1071"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1072"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1073"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1074"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1075"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1076"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1077"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1078"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1079"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1080"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1081"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1082"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1083"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1084"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1085"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1086"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1087"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1088"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1089"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1090"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1091"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1092"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1093"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1094"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1095"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1096"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1097"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I524" r:id="rId1098"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1099"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O25" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O32" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O34" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O35" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O38" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O41" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O42" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O44" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O49" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O51" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O52" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O55" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O57" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O58" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O59" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O61" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O62" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O63" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O64" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O65" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O66" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O67" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O71" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O73" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O74" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O77" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O78" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O79" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O83" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O87" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O99" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O100" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O101" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I102" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O104" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O105" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O106" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O109" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O110" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O111" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O112" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O113" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O114" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O115" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O116" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O117" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O118" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H121" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H122" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O122" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H123" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O123" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H124" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O124" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H125" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O125" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H126" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O126" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H127" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O127" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H128" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H129" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H130" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H131" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O131" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H132" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O132" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H133" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O133" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H134" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O134" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H135" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O135" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H136" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O136" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H137" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O137" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H138" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H139" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O139" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H140" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O140" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H141" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H142" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O142" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H143" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O143" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H144" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O144" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H145" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H146" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O146" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H147" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O147" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H148" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O148" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H149" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H150" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O150" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H151" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O151" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H152" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O152" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H153" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O153" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H154" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O154" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H155" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O155" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H156" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H157" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O157" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H158" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O158" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H159" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O159" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H160" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H161" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O161" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H162" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O162" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H163" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O163" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H164" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H165" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H166" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H167" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O167" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H168" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O168" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H169" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H170" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H171" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O171" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H172" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O172" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H173" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O173" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H174" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O174" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H175" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O175" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H176" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O176" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H177" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H178" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I178" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O178" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H179" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I179" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O179" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H180" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I180" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O180" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H181" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I181" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O181" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H182" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I182" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O182" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H183" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I183" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O183" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H184" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H185" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I185" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O185" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H186" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H187" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H188" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I188" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O188" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H189" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H190" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H191" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I191" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O191" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H192" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I192" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O192" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H193" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H194" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H195" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O195" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H196" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I196" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O196" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H197" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O197" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H198" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I198" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O198" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H199" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H200" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H201" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H202" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H203" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O203" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H204" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O204" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H205" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H206" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O206" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H207" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H208" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O208" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H209" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O209" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H210" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O210" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H211" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H212" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O212" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H213" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O213" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H214" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O214" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H215" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H216" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O216" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H217" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O217" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H218" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O218" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H219" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O219" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H220" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O220" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H221" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O221" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H222" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O222" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H223" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H224" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O224" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H225" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O225" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H226" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O226" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H227" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O227" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H228" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O228" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H229" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O229" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H230" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O230" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H231" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O231" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H232" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H233" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H234" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H235" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O235" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H236" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O236" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H237" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H238" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H239" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H240" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O240" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H241" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H242" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H243" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H244" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O244" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H245" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H246" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H247" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O247" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H248" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H249" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O249" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H250" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O250" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H251" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O251" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H252" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O252" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H253" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O253" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H254" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O254" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H255" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H256" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H257" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H258" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O258" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H259" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H260" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O260" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H261" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H262" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O262" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H263" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O263" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H264" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O264" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H265" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O265" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H266" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O266" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H267" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O267" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H268" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H269" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O269" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H270" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O270" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H271" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O271" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H272" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O272" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H273" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O273" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H274" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O274" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H275" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H276" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H277" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H278" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H279" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O279" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H280" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H281" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H282" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H283" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H284" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H285" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O285" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H286" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O286" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H287" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O287" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H288" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O288" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H289" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O289" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H290" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O290" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H291" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O291" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H292" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H293" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H294" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O294" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H295" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H296" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O296" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H297" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O297" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H298" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H299" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H300" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O300" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H301" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O301" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H302" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H303" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O303" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H304" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O304" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H305" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H306" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O306" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H307" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O307" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H308" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O308" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H309" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H310" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H311" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H312" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O312" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H313" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O313" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H314" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O314" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H315" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O315" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H316" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H317" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H318" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H319" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H320" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O320" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H321" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O321" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H322" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H323" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O323" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H324" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H325" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H326" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O326" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H327" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O327" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H328" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H329" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H330" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O330" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H331" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O331" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H332" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H333" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H334" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O334" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H335" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O335" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H336" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O336" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H337" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O337" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H338" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O338" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H339" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O339" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H340" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O340" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H341" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O341" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H342" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H343" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H344" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O344" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H345" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O345" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H346" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O346" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H347" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O347" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H348" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H349" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O349" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H350" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O350" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H351" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O351" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H352" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O352" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H353" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H354" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H355" r:id="rId746"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId747"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O355" r:id="rId748"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H356" r:id="rId749"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId750"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O356" r:id="rId751"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H357" r:id="rId752"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O357" r:id="rId753"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H358" r:id="rId754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId755"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O358" r:id="rId756"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H359" r:id="rId757"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId758"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O359" r:id="rId759"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H360" r:id="rId760"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId761"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O360" r:id="rId762"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H361" r:id="rId763"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O361" r:id="rId764"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H362" r:id="rId765"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O362" r:id="rId766"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H363" r:id="rId767"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId768"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O363" r:id="rId769"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H364" r:id="rId770"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H365" r:id="rId771"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H366" r:id="rId772"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId773"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O366" r:id="rId774"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H367" r:id="rId775"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H368" r:id="rId776"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H369" r:id="rId777"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H370" r:id="rId778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O370" r:id="rId779"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H371" r:id="rId780"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O371" r:id="rId781"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H372" r:id="rId782"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H373" r:id="rId783"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H374" r:id="rId784"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H375" r:id="rId785"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O375" r:id="rId786"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H376" r:id="rId787"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H377" r:id="rId788"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H378" r:id="rId789"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H379" r:id="rId790"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O379" r:id="rId791"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H380" r:id="rId792"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId793"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O380" r:id="rId794"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H381" r:id="rId795"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H382" r:id="rId796"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId797"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O382" r:id="rId798"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H383" r:id="rId799"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H384" r:id="rId800"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId801"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O384" r:id="rId802"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H385" r:id="rId803"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId804"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O385" r:id="rId805"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H386" r:id="rId806"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId807"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O386" r:id="rId808"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H387" r:id="rId809"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I387" r:id="rId810"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O387" r:id="rId811"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H388" r:id="rId812"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H389" r:id="rId813"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId814"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O389" r:id="rId815"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H390" r:id="rId816"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId817"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O390" r:id="rId818"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H391" r:id="rId819"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId820"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O391" r:id="rId821"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H392" r:id="rId822"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H393" r:id="rId823"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H394" r:id="rId824"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId825"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O394" r:id="rId826"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H395" r:id="rId827"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId828"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O395" r:id="rId829"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H396" r:id="rId830"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId831"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O396" r:id="rId832"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H397" r:id="rId833"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId834"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O397" r:id="rId835"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H398" r:id="rId836"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId837"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O398" r:id="rId838"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H399" r:id="rId839"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId840"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O399" r:id="rId841"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H400" r:id="rId842"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H401" r:id="rId843"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId844"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O401" r:id="rId845"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H402" r:id="rId846"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O402" r:id="rId847"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H403" r:id="rId848"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O403" r:id="rId849"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H404" r:id="rId850"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId851"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O404" r:id="rId852"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H405" r:id="rId853"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H406" r:id="rId854"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H407" r:id="rId855"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId856"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O407" r:id="rId857"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H408" r:id="rId858"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H409" r:id="rId859"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId860"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O409" r:id="rId861"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H410" r:id="rId862"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H411" r:id="rId863"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H412" r:id="rId864"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId865"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O412" r:id="rId866"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H413" r:id="rId867"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H414" r:id="rId868"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O414" r:id="rId869"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H415" r:id="rId870"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId871"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O415" r:id="rId872"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H416" r:id="rId873"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId874"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O416" r:id="rId875"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H417" r:id="rId876"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H418" r:id="rId877"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId878"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O418" r:id="rId879"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H419" r:id="rId880"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId881"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O419" r:id="rId882"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H420" r:id="rId883"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId884"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O420" r:id="rId885"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H421" r:id="rId886"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O421" r:id="rId887"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H422" r:id="rId888"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId889"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O422" r:id="rId890"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H423" r:id="rId891"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H424" r:id="rId892"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId893"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O424" r:id="rId894"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H425" r:id="rId895"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H426" r:id="rId896"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H427" r:id="rId897"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId898"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O427" r:id="rId899"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H428" r:id="rId900"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId901"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O428" r:id="rId902"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H429" r:id="rId903"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O429" r:id="rId904"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H430" r:id="rId905"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId906"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O430" r:id="rId907"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H431" r:id="rId908"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId909"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O431" r:id="rId910"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H432" r:id="rId911"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId912"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O432" r:id="rId913"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H433" r:id="rId914"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I433" r:id="rId915"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O433" r:id="rId916"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H434" r:id="rId917"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId918"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O434" r:id="rId919"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H435" r:id="rId920"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O435" r:id="rId921"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H436" r:id="rId922"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId923"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O436" r:id="rId924"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H437" r:id="rId925"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId926"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O437" r:id="rId927"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H438" r:id="rId928"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId929"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O438" r:id="rId930"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H439" r:id="rId931"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H440" r:id="rId932"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId933"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O440" r:id="rId934"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H441" r:id="rId935"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H442" r:id="rId936"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H443" r:id="rId937"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O443" r:id="rId938"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H444" r:id="rId939"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I444" r:id="rId940"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O444" r:id="rId941"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H445" r:id="rId942"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I445" r:id="rId943"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O445" r:id="rId944"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H446" r:id="rId945"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H447" r:id="rId946"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H448" r:id="rId947"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H449" r:id="rId948"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H450" r:id="rId949"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I450" r:id="rId950"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O450" r:id="rId951"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H451" r:id="rId952"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O451" r:id="rId953"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H452" r:id="rId954"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I452" r:id="rId955"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O452" r:id="rId956"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H453" r:id="rId957"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H454" r:id="rId958"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId959"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O454" r:id="rId960"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H455" r:id="rId961"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H456" r:id="rId962"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId963"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O456" r:id="rId964"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H457" r:id="rId965"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId966"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O457" r:id="rId967"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H458" r:id="rId968"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I458" r:id="rId969"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O458" r:id="rId970"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H459" r:id="rId971"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId972"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O459" r:id="rId973"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H460" r:id="rId974"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId975"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O460" r:id="rId976"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H461" r:id="rId977"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId978"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O461" r:id="rId979"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H462" r:id="rId980"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O462" r:id="rId981"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H463" r:id="rId982"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId983"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O463" r:id="rId984"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H464" r:id="rId985"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId986"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O464" r:id="rId987"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H465" r:id="rId988"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H466" r:id="rId989"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H467" r:id="rId990"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H468" r:id="rId991"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O468" r:id="rId992"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H469" r:id="rId993"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H470" r:id="rId994"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H471" r:id="rId995"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H472" r:id="rId996"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H473" r:id="rId997"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H474" r:id="rId998"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId999"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O474" r:id="rId1000"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H475" r:id="rId1001"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H476" r:id="rId1002"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId1003"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O476" r:id="rId1004"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H477" r:id="rId1005"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H478" r:id="rId1006"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId1007"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O478" r:id="rId1008"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H479" r:id="rId1009"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId1010"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O479" r:id="rId1011"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H480" r:id="rId1012"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId1013"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O480" r:id="rId1014"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H481" r:id="rId1015"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H482" r:id="rId1016"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O482" r:id="rId1017"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H483" r:id="rId1018"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H484" r:id="rId1019"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O484" r:id="rId1020"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H485" r:id="rId1021"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H486" r:id="rId1022"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H487" r:id="rId1023"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H488" r:id="rId1024"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H489" r:id="rId1025"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H490" r:id="rId1026"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H491" r:id="rId1027"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I491" r:id="rId1028"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O491" r:id="rId1029"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H492" r:id="rId1030"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H493" r:id="rId1031"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H494" r:id="rId1032"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H495" r:id="rId1033"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H496" r:id="rId1034"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O496" r:id="rId1035"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H497" r:id="rId1036"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I497" r:id="rId1037"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O497" r:id="rId1038"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H498" r:id="rId1039"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H499" r:id="rId1040"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H500" r:id="rId1041"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H501" r:id="rId1042"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I501" r:id="rId1043"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O501" r:id="rId1044"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H502" r:id="rId1045"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I502" r:id="rId1046"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O502" r:id="rId1047"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H503" r:id="rId1048"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I503" r:id="rId1049"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O503" r:id="rId1050"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H504" r:id="rId1051"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I504" r:id="rId1052"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O504" r:id="rId1053"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H505" r:id="rId1054"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H506" r:id="rId1055"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I506" r:id="rId1056"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O506" r:id="rId1057"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H507" r:id="rId1058"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I507" r:id="rId1059"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O507" r:id="rId1060"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H508" r:id="rId1061"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H509" r:id="rId1062"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H510" r:id="rId1063"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H511" r:id="rId1064"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I511" r:id="rId1065"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O511" r:id="rId1066"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H512" r:id="rId1067"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I512" r:id="rId1068"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O512" r:id="rId1069"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H513" r:id="rId1070"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I513" r:id="rId1071"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O513" r:id="rId1072"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H514" r:id="rId1073"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H515" r:id="rId1074"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H516" r:id="rId1075"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O516" r:id="rId1076"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H517" r:id="rId1077"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I517" r:id="rId1078"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O517" r:id="rId1079"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H518" r:id="rId1080"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H519" r:id="rId1081"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I519" r:id="rId1082"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O519" r:id="rId1083"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H520" r:id="rId1084"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I520" r:id="rId1085"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O520" r:id="rId1086"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H521" r:id="rId1087"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H522" r:id="rId1088"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H523" r:id="rId1089"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O523" r:id="rId1090"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H524" r:id="rId1091"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I524" r:id="rId1092"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O524" r:id="rId1093"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H525" r:id="rId1094"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I525" r:id="rId1095"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O525" r:id="rId1096"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H526" r:id="rId1097"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H527" r:id="rId1098"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O527" r:id="rId1099"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36520,7 +36418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -36544,7 +36442,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -36554,7 +36452,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4">
@@ -36564,7 +36462,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5">
@@ -36574,7 +36472,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -36594,7 +36492,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -36626,46 +36524,70 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Per-venue search coverage</t>
+          <t>Final review (2026-10-29)</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them; all 111 rows that remained ambiguous have had a second per-venue pass, and all of those still ambiguous a third pass that read the sources recorded in the 557-row Maps audit list; every row carries either a result or the reason none could be established</t>
+          <t>all 260 rows verified up to that point were re-checked. Six were put back to AMBIGUOUS: four whose handle came from this guide's earlier Visitor Essentials record rather than a link on the venue's own page (the sources behind that record are aggregator or media pages), one whose recorded handle was a booking platform's own account, and one whose profile evidence could not tell the venue from other bars in the same block. Two rows confirmed from a page of the venue's own now cite that page instead of the Instagram URL.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Why AMBIGUOUS exists</t>
+          <t>Constraint on re-checking</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>an account is printed on a directory or media page, or several official accounts are linked and none is identifiably this venue's</t>
+          <t>Instagram blocks unauthenticated profile reads, so a profile-based row cannot be re-opened and read again from here. Those rows were re-checked against what the research recorded at the time - whether a street address, a named station, a telephone number, an official marker or a branch name was written down - and rows without such a record were put back to AMBIGUOUS rather than left verified.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Why so many NOT_FOUND</t>
+          <t>Per-venue search coverage</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>no official website is on record for the venue, and Instagram blocks unauthenticated profile reads, so no admissible evidence exists</t>
+          <t>all 338 listings that the website pass left unresolved have had the per-venue Instagram search run on them; all 111 rows that remained ambiguous have had a second per-venue pass, and all of those still ambiguous a third pass that read the sources recorded in the 557-row Maps audit list; every row carries either a result or the reason none could be established</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>Why AMBIGUOUS exists</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>an account is printed on a directory or media page, or several official accounts are linked and none is identifiably this venue's</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Why so many NOT_FOUND</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>no official website is on record for the venue, and Instagram blocks unauthenticated profile reads, so no admissible evidence exists</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
           <t>Checked on</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
